--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2172" uniqueCount="724">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="734">
   <si>
     <t>ID</t>
   </si>
@@ -926,6 +926,15 @@
     <t>Riconoscimento materno di figlio infraquattordicenne gia' riconosciuto dal padre</t>
   </si>
   <si>
+    <t>12222401</t>
+  </si>
+  <si>
+    <t>Riconoscimento materno di maggiorenne gia' riconosciuto dal padre</t>
+  </si>
+  <si>
+    <t>2025-02-01 00:00:00.0</t>
+  </si>
+  <si>
     <t>12224123</t>
   </si>
   <si>
@@ -1211,6 +1220,21 @@
     <t>Trascrizione di nascita: Scelta del cognome del figlio di ignoti maggiorenne a seguito del riconoscimento da parte di uno o di entrambi i genitori  su istanza di ufficio</t>
   </si>
   <si>
+    <t>1368</t>
+  </si>
+  <si>
+    <t>Trascrizione provvedimento del Tribunale per il cambiamento del cognome del minore a seguito di riconoscimento art. 262</t>
+  </si>
+  <si>
+    <t>2026-02-24 16:19:54.0</t>
+  </si>
+  <si>
+    <t>2026-02-24 16:18:49.0</t>
+  </si>
+  <si>
+    <t>2026-02-24 16:18:38.0</t>
+  </si>
+  <si>
     <t>1381</t>
   </si>
   <si>
@@ -2148,6 +2172,12 @@
   </si>
   <si>
     <t>Trascrizione: Riacquisto per residenza in Italia, dichiarazione resa in Consolato italiano</t>
+  </si>
+  <si>
+    <t>52332</t>
+  </si>
+  <si>
+    <t>Riacquisto cittadinanza italiana art.17 L.91/1992 da Consolato</t>
   </si>
   <si>
     <t>52341</t>
@@ -2242,7 +2272,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G362"/>
+  <dimension ref="A1:G367"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.95703125" customWidth="true" bestFit="true"/>
@@ -5181,7 +5211,7 @@
         <v>305</v>
       </c>
       <c r="C147" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>9</v>
@@ -5195,10 +5225,10 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B148" s="2" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>8</v>
@@ -5215,10 +5245,10 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>8</v>
@@ -5235,10 +5265,10 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>8</v>
@@ -5255,10 +5285,10 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="B151" s="2" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>8</v>
@@ -5275,10 +5305,10 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>8</v>
@@ -5295,10 +5325,10 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>8</v>
@@ -5315,13 +5345,13 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D154" s="2" t="s">
         <v>9</v>
@@ -5341,7 +5371,7 @@
         <v>322</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -5355,10 +5385,10 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>8</v>
@@ -5370,7 +5400,7 @@
         <v>10</v>
       </c>
       <c r="F156" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="157">
@@ -5390,35 +5420,35 @@
         <v>10</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B158" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D158" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E158" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F158" s="2" t="s">
         <v>328</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>329</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D158" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E158" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F158" s="2" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C159" s="2" t="s">
         <v>8</v>
@@ -5430,18 +5460,18 @@
         <v>10</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D160" s="2" t="s">
         <v>9</v>
@@ -5450,18 +5480,18 @@
         <v>10</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>9</v>
@@ -5470,18 +5500,18 @@
         <v>10</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>338</v>
+        <v>323</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>9</v>
@@ -5490,7 +5520,7 @@
         <v>10</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="163">
@@ -5501,7 +5531,7 @@
         <v>340</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D163" s="2" t="s">
         <v>9</v>
@@ -5510,15 +5540,15 @@
         <v>10</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="C164" s="2" t="s">
         <v>8</v>
@@ -5530,15 +5560,15 @@
         <v>10</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="C165" s="2" t="s">
         <v>8</v>
@@ -5550,15 +5580,15 @@
         <v>10</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="C166" s="2" t="s">
         <v>8</v>
@@ -5570,15 +5600,15 @@
         <v>10</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C167" s="2" t="s">
         <v>8</v>
@@ -5590,15 +5620,15 @@
         <v>10</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="C168" s="2" t="s">
         <v>8</v>
@@ -5610,18 +5640,18 @@
         <v>10</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>353</v>
+        <v>8</v>
       </c>
       <c r="D169" s="2" t="s">
         <v>9</v>
@@ -5630,7 +5660,7 @@
         <v>10</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="170">
@@ -5650,7 +5680,7 @@
         <v>10</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="171">
@@ -5661,7 +5691,7 @@
         <v>358</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>320</v>
+        <v>359</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>9</v>
@@ -5670,18 +5700,18 @@
         <v>10</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>9</v>
@@ -5690,18 +5720,18 @@
         <v>10</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>9</v>
@@ -5710,15 +5740,15 @@
         <v>10</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>8</v>
@@ -5730,15 +5760,15 @@
         <v>10</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>8</v>
@@ -5750,15 +5780,15 @@
         <v>10</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>8</v>
@@ -5770,15 +5800,15 @@
         <v>10</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>8</v>
@@ -5790,15 +5820,15 @@
         <v>10</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>8</v>
@@ -5810,15 +5840,15 @@
         <v>10</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>8</v>
@@ -5830,15 +5860,15 @@
         <v>10</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>8</v>
@@ -5850,15 +5880,15 @@
         <v>10</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>8</v>
@@ -5870,18 +5900,18 @@
         <v>10</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>381</v>
+        <v>8</v>
       </c>
       <c r="D182" s="2" t="s">
         <v>9</v>
@@ -5890,7 +5920,7 @@
         <v>10</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="183">
@@ -5910,7 +5940,7 @@
         <v>10</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="184">
@@ -5921,7 +5951,7 @@
         <v>386</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>8</v>
+        <v>387</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>9</v>
@@ -5930,15 +5960,15 @@
         <v>10</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>8</v>
@@ -5950,15 +5980,15 @@
         <v>10</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>8</v>
@@ -5970,15 +6000,15 @@
         <v>10</v>
       </c>
       <c r="F186" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>8</v>
@@ -5990,15 +6020,15 @@
         <v>10</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>8</v>
@@ -6010,15 +6040,15 @@
         <v>10</v>
       </c>
       <c r="F188" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>8</v>
@@ -6030,15 +6060,15 @@
         <v>10</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>8</v>
@@ -6050,18 +6080,18 @@
         <v>10</v>
       </c>
       <c r="F190" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>401</v>
+        <v>8</v>
       </c>
       <c r="D191" s="2" t="s">
         <v>9</v>
@@ -6070,7 +6100,7 @@
         <v>10</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="192">
@@ -6081,7 +6111,7 @@
         <v>403</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>9</v>
@@ -6090,19 +6120,19 @@
         <v>10</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
-        <v>404</v>
+        <v>402</v>
       </c>
       <c r="B193" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C193" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D193" s="2" t="s">
         <v>9</v>
       </c>
@@ -6110,19 +6140,19 @@
         <v>10</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="B194" s="2" t="s">
+        <v>403</v>
+      </c>
+      <c r="C194" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="C194" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D194" s="2" t="s">
         <v>9</v>
       </c>
@@ -6130,19 +6160,19 @@
         <v>10</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
+        <v>407</v>
+      </c>
+      <c r="B195" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="C195" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>410</v>
-      </c>
-      <c r="C195" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D195" s="2" t="s">
         <v>9</v>
       </c>
@@ -6150,18 +6180,18 @@
         <v>10</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
+        <v>410</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="B196" s="2" t="s">
-        <v>412</v>
-      </c>
       <c r="C196" s="2" t="s">
-        <v>8</v>
+        <v>409</v>
       </c>
       <c r="D196" s="2" t="s">
         <v>9</v>
@@ -6170,16 +6200,16 @@
         <v>10</v>
       </c>
       <c r="F196" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
+        <v>412</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>414</v>
-      </c>
       <c r="C197" s="2" t="s">
         <v>8</v>
       </c>
@@ -6190,38 +6220,38 @@
         <v>10</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
+        <v>414</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="B198" s="2" t="s">
+      <c r="C198" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D198" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E198" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F198" s="2" t="s">
         <v>416</v>
-      </c>
-      <c r="C198" s="2" t="s">
-        <v>417</v>
-      </c>
-      <c r="D198" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E198" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F198" s="2" t="s">
-        <v>408</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>419</v>
-      </c>
       <c r="C199" s="2" t="s">
-        <v>420</v>
+        <v>8</v>
       </c>
       <c r="D199" s="2" t="s">
         <v>9</v>
@@ -6230,18 +6260,18 @@
         <v>10</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>422</v>
+        <v>420</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D200" s="2" t="s">
         <v>9</v>
@@ -6250,18 +6280,18 @@
         <v>10</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="B201" s="2" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>9</v>
@@ -6270,19 +6300,19 @@
         <v>10</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B202" s="2" t="s">
+        <v>424</v>
+      </c>
+      <c r="C202" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>426</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="D202" s="2" t="s">
         <v>9</v>
       </c>
@@ -6290,19 +6320,19 @@
         <v>10</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
+        <v>426</v>
+      </c>
+      <c r="B203" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="B203" s="2" t="s">
+      <c r="C203" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="C203" s="2" t="s">
-        <v>320</v>
-      </c>
       <c r="D203" s="2" t="s">
         <v>9</v>
       </c>
@@ -6310,7 +6340,7 @@
         <v>10</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="204">
@@ -6321,7 +6351,7 @@
         <v>430</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D204" s="2" t="s">
         <v>9</v>
@@ -6330,7 +6360,7 @@
         <v>10</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="205">
@@ -6338,10 +6368,10 @@
         <v>431</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>7</v>
+        <v>432</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>9</v>
@@ -6350,18 +6380,18 @@
         <v>10</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>9</v>
@@ -6370,18 +6400,18 @@
         <v>10</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>9</v>
@@ -6390,18 +6420,18 @@
         <v>10</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>9</v>
@@ -6410,15 +6440,15 @@
         <v>10</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>8</v>
@@ -6430,7 +6460,7 @@
         <v>10</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="210">
@@ -6441,7 +6471,7 @@
         <v>441</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="D210" s="2" t="s">
         <v>9</v>
@@ -6461,7 +6491,7 @@
         <v>443</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="D211" s="2" t="s">
         <v>9</v>
@@ -6481,7 +6511,7 @@
         <v>445</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D212" s="2" t="s">
         <v>9</v>
@@ -6521,7 +6551,7 @@
         <v>449</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>9</v>
@@ -6530,7 +6560,7 @@
         <v>10</v>
       </c>
       <c r="F214" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="215">
@@ -6541,7 +6571,7 @@
         <v>451</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>9</v>
@@ -6550,7 +6580,7 @@
         <v>10</v>
       </c>
       <c r="F215" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="216">
@@ -6561,7 +6591,7 @@
         <v>453</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>9</v>
@@ -6570,7 +6600,7 @@
         <v>10</v>
       </c>
       <c r="F216" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="217">
@@ -6581,27 +6611,27 @@
         <v>455</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D217" s="2" t="s">
-        <v>456</v>
+        <v>9</v>
       </c>
       <c r="E217" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B218" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>458</v>
-      </c>
       <c r="C218" s="2" t="s">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="D218" s="2" t="s">
         <v>9</v>
@@ -6610,16 +6640,16 @@
         <v>10</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="C219" s="2" t="s">
         <v>8</v>
       </c>
@@ -6630,16 +6660,16 @@
         <v>10</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B220" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="C220" s="2" t="s">
         <v>8</v>
       </c>
@@ -6650,27 +6680,27 @@
         <v>10</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B221" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B221" s="2" t="s">
+      <c r="C221" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D221" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="C221" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D221" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E221" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="222">
@@ -6681,7 +6711,7 @@
         <v>466</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>9</v>
@@ -6690,7 +6720,7 @@
         <v>10</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="223">
@@ -6701,7 +6731,7 @@
         <v>468</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>9</v>
@@ -6710,7 +6740,7 @@
         <v>10</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="224">
@@ -6730,7 +6760,7 @@
         <v>10</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="225">
@@ -6738,7 +6768,7 @@
         <v>471</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>407</v>
+        <v>472</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
@@ -6750,15 +6780,15 @@
         <v>10</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
@@ -6770,18 +6800,18 @@
         <v>10</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>412</v>
+        <v>476</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>9</v>
@@ -6790,15 +6820,15 @@
         <v>10</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>414</v>
+        <v>478</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
@@ -6810,18 +6840,18 @@
         <v>10</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>420</v>
+        <v>8</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>9</v>
@@ -6830,18 +6860,18 @@
         <v>10</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>422</v>
+        <v>481</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D230" s="2" t="s">
         <v>9</v>
@@ -6850,15 +6880,15 @@
         <v>10</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>7</v>
+        <v>420</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>8</v>
@@ -6870,15 +6900,15 @@
         <v>10</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>480</v>
+        <v>422</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>8</v>
@@ -6890,38 +6920,38 @@
         <v>10</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>482</v>
+        <v>427</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>320</v>
+        <v>428</v>
       </c>
       <c r="D233" s="2" t="s">
-        <v>483</v>
+        <v>9</v>
       </c>
       <c r="E233" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>485</v>
+        <v>430</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>9</v>
@@ -6930,7 +6960,7 @@
         <v>10</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="235">
@@ -6938,27 +6968,27 @@
         <v>486</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>487</v>
+        <v>7</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D235" s="2" t="s">
-        <v>483</v>
+        <v>9</v>
       </c>
       <c r="E235" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>8</v>
@@ -6975,16 +7005,16 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="C237" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D237" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>10</v>
@@ -7021,10 +7051,10 @@
         <v>495</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>9</v>
+        <v>491</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>10</v>
@@ -7121,7 +7151,7 @@
         <v>505</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D244" s="2" t="s">
         <v>9</v>
@@ -7201,7 +7231,7 @@
         <v>513</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>9</v>
@@ -7215,13 +7245,13 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D249" s="2" t="s">
         <v>9</v>
@@ -7235,10 +7265,10 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>8</v>
@@ -7255,10 +7285,10 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
@@ -7270,18 +7300,18 @@
         <v>10</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>9</v>
@@ -7290,7 +7320,7 @@
         <v>10</v>
       </c>
       <c r="F252" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="253">
@@ -7301,7 +7331,7 @@
         <v>521</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>9</v>
@@ -7310,7 +7340,7 @@
         <v>10</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="254">
@@ -7330,7 +7360,7 @@
         <v>10</v>
       </c>
       <c r="F254" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="255">
@@ -7350,7 +7380,7 @@
         <v>10</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="256">
@@ -7361,7 +7391,7 @@
         <v>527</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>528</v>
+        <v>8</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>9</v>
@@ -7370,16 +7400,16 @@
         <v>10</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
       </c>
@@ -7390,16 +7420,16 @@
         <v>10</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>532</v>
-      </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
       </c>
@@ -7410,16 +7440,16 @@
         <v>10</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
       </c>
@@ -7430,19 +7460,19 @@
         <v>10</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B260" s="2" t="s">
+      <c r="C260" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="C260" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D260" s="2" t="s">
         <v>9</v>
       </c>
@@ -7450,7 +7480,7 @@
         <v>10</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="261">
@@ -7470,7 +7500,7 @@
         <v>10</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="262">
@@ -7541,10 +7571,10 @@
         <v>546</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D265" s="2" t="s">
-        <v>547</v>
+        <v>9</v>
       </c>
       <c r="E265" s="2" t="s">
         <v>10</v>
@@ -7555,10 +7585,10 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -7575,10 +7605,10 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -7595,10 +7625,10 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -7615,22 +7645,22 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B269" s="2" t="s">
+      <c r="C269" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D269" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="C269" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D269" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E269" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>408</v>
+        <v>14</v>
       </c>
     </row>
     <row r="270">
@@ -7638,7 +7668,7 @@
         <v>556</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>407</v>
+        <v>557</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
@@ -7650,15 +7680,15 @@
         <v>10</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>408</v>
+        <v>14</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>473</v>
+        <v>559</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>8</v>
@@ -7670,15 +7700,15 @@
         <v>10</v>
       </c>
       <c r="F271" s="2" t="s">
-        <v>408</v>
+        <v>14</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>412</v>
+        <v>561</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -7690,18 +7720,18 @@
         <v>10</v>
       </c>
       <c r="F272" s="2" t="s">
-        <v>408</v>
+        <v>14</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>414</v>
+        <v>563</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>9</v>
@@ -7710,18 +7740,18 @@
         <v>10</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>420</v>
+        <v>8</v>
       </c>
       <c r="D274" s="2" t="s">
         <v>9</v>
@@ -7730,18 +7760,18 @@
         <v>10</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>422</v>
+        <v>481</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
@@ -7750,15 +7780,15 @@
         <v>10</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>7</v>
+        <v>420</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>8</v>
@@ -7770,15 +7800,15 @@
         <v>10</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>564</v>
+        <v>422</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>8</v>
@@ -7790,18 +7820,18 @@
         <v>10</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>566</v>
+        <v>427</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>8</v>
+        <v>428</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>9</v>
@@ -7810,18 +7840,18 @@
         <v>10</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>568</v>
+        <v>430</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>9</v>
@@ -7830,15 +7860,15 @@
         <v>10</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>570</v>
+        <v>7</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>8</v>
@@ -7850,7 +7880,7 @@
         <v>10</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="281">
@@ -7910,7 +7940,7 @@
         <v>10</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="284">
@@ -7930,7 +7960,7 @@
         <v>10</v>
       </c>
       <c r="F284" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="285">
@@ -7950,7 +7980,7 @@
         <v>10</v>
       </c>
       <c r="F285" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="286">
@@ -7970,7 +8000,7 @@
         <v>10</v>
       </c>
       <c r="F286" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="287">
@@ -7981,7 +8011,7 @@
         <v>584</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D287" s="2" t="s">
         <v>9</v>
@@ -7990,7 +8020,7 @@
         <v>10</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="288">
@@ -8010,7 +8040,7 @@
         <v>10</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="289">
@@ -8030,7 +8060,7 @@
         <v>10</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="290">
@@ -8050,7 +8080,7 @@
         <v>10</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="291">
@@ -8061,7 +8091,7 @@
         <v>592</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>9</v>
@@ -8070,7 +8100,7 @@
         <v>10</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="292">
@@ -8090,7 +8120,7 @@
         <v>10</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="293">
@@ -8121,7 +8151,7 @@
         <v>598</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>9</v>
@@ -8141,7 +8171,7 @@
         <v>600</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>9</v>
@@ -8150,7 +8180,7 @@
         <v>10</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="296">
@@ -8161,7 +8191,7 @@
         <v>602</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>603</v>
+        <v>8</v>
       </c>
       <c r="D296" s="2" t="s">
         <v>9</v>
@@ -8170,15 +8200,15 @@
         <v>10</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>604</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -8195,13 +8225,13 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>606</v>
       </c>
-      <c r="B298" s="2" t="s">
-        <v>407</v>
-      </c>
       <c r="C298" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>9</v>
@@ -8210,7 +8240,7 @@
         <v>10</v>
       </c>
       <c r="F298" s="2" t="s">
-        <v>408</v>
+        <v>14</v>
       </c>
     </row>
     <row r="299">
@@ -8218,10 +8248,10 @@
         <v>607</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>473</v>
+        <v>608</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>9</v>
@@ -8230,18 +8260,18 @@
         <v>10</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>412</v>
+        <v>610</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>8</v>
+        <v>611</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>9</v>
@@ -8250,15 +8280,15 @@
         <v>10</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>414</v>
+        <v>613</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>8</v>
@@ -8270,18 +8300,18 @@
         <v>10</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>408</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>419</v>
+        <v>415</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>420</v>
+        <v>8</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
@@ -8290,18 +8320,18 @@
         <v>10</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>422</v>
+        <v>481</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>9</v>
@@ -8310,18 +8340,18 @@
         <v>10</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>613</v>
+        <v>420</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>614</v>
+        <v>8</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>9</v>
@@ -8330,15 +8360,15 @@
         <v>10</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>408</v>
+        <v>416</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>7</v>
+        <v>422</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -8350,18 +8380,18 @@
         <v>10</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>617</v>
+        <v>427</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>8</v>
+        <v>428</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>9</v>
@@ -8370,18 +8400,18 @@
         <v>10</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>619</v>
+        <v>430</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>9</v>
@@ -8390,7 +8420,7 @@
         <v>10</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="308">
@@ -8401,7 +8431,7 @@
         <v>621</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>8</v>
+        <v>622</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>9</v>
@@ -8410,15 +8440,15 @@
         <v>10</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>623</v>
+        <v>7</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>8</v>
@@ -8430,7 +8460,7 @@
         <v>10</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="310">
@@ -8521,7 +8551,7 @@
         <v>633</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D314" s="2" t="s">
         <v>9</v>
@@ -8541,7 +8571,7 @@
         <v>635</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D315" s="2" t="s">
         <v>9</v>
@@ -8601,7 +8631,7 @@
         <v>641</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>9</v>
@@ -8621,7 +8651,7 @@
         <v>643</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>9</v>
@@ -8721,7 +8751,7 @@
         <v>653</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>9</v>
@@ -8770,7 +8800,7 @@
         <v>10</v>
       </c>
       <c r="F326" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="327">
@@ -8790,7 +8820,7 @@
         <v>10</v>
       </c>
       <c r="F327" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="328">
@@ -8801,7 +8831,7 @@
         <v>661</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>9</v>
@@ -8810,7 +8840,7 @@
         <v>10</v>
       </c>
       <c r="F328" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="329">
@@ -8830,7 +8860,7 @@
         <v>10</v>
       </c>
       <c r="F329" s="2" t="s">
-        <v>325</v>
+        <v>14</v>
       </c>
     </row>
     <row r="330">
@@ -8850,7 +8880,7 @@
         <v>10</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="331">
@@ -8870,7 +8900,7 @@
         <v>10</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="332">
@@ -8890,7 +8920,7 @@
         <v>10</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="333">
@@ -8910,7 +8940,7 @@
         <v>10</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="334">
@@ -8930,7 +8960,7 @@
         <v>10</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="335">
@@ -8950,7 +8980,7 @@
         <v>10</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="336">
@@ -8970,7 +9000,7 @@
         <v>10</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="337">
@@ -8981,7 +9011,7 @@
         <v>679</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>338</v>
+        <v>8</v>
       </c>
       <c r="D337" s="2" t="s">
         <v>9</v>
@@ -8990,7 +9020,7 @@
         <v>10</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="338">
@@ -9001,7 +9031,7 @@
         <v>681</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>320</v>
+        <v>8</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>9</v>
@@ -9010,7 +9040,7 @@
         <v>10</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="339">
@@ -9030,7 +9060,7 @@
         <v>10</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="340">
@@ -9050,7 +9080,7 @@
         <v>10</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="341">
@@ -9061,7 +9091,7 @@
         <v>687</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>9</v>
@@ -9070,7 +9100,7 @@
         <v>10</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="342">
@@ -9081,7 +9111,7 @@
         <v>689</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -9090,7 +9120,7 @@
         <v>10</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="343">
@@ -9110,7 +9140,7 @@
         <v>10</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="344">
@@ -9130,7 +9160,7 @@
         <v>10</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="345">
@@ -9150,7 +9180,7 @@
         <v>10</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="346">
@@ -9170,7 +9200,7 @@
         <v>10</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="347">
@@ -9190,7 +9220,7 @@
         <v>10</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="348">
@@ -9210,7 +9240,7 @@
         <v>10</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="349">
@@ -9230,7 +9260,7 @@
         <v>10</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="350">
@@ -9250,7 +9280,7 @@
         <v>10</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="351">
@@ -9270,7 +9300,7 @@
         <v>10</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="352">
@@ -9290,7 +9320,7 @@
         <v>10</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="353">
@@ -9310,7 +9340,7 @@
         <v>10</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="354">
@@ -9330,7 +9360,7 @@
         <v>10</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="355">
@@ -9341,7 +9371,7 @@
         <v>715</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>401</v>
+        <v>8</v>
       </c>
       <c r="D355" s="2" t="s">
         <v>9</v>
@@ -9350,7 +9380,7 @@
         <v>10</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="356">
@@ -9370,7 +9400,7 @@
         <v>10</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="357">
@@ -9378,7 +9408,7 @@
         <v>718</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>407</v>
+        <v>719</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -9390,18 +9420,18 @@
         <v>10</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>473</v>
+        <v>721</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>9</v>
@@ -9410,15 +9440,15 @@
         <v>10</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>412</v>
+        <v>723</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -9430,18 +9460,18 @@
         <v>10</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>414</v>
+        <v>725</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>8</v>
+        <v>409</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>9</v>
@@ -9450,18 +9480,18 @@
         <v>10</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>419</v>
+        <v>727</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>420</v>
+        <v>8</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>9</v>
@@ -9470,27 +9500,127 @@
         <v>10</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>408</v>
+        <v>328</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B362" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D362" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E362" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F362" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" s="2" t="s">
+        <v>729</v>
+      </c>
+      <c r="B363" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C363" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D363" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E363" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F363" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B364" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C364" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D364" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E364" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F364" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="B365" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C362" s="2" t="s">
-        <v>320</v>
-      </c>
-      <c r="D362" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E362" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F362" s="2" t="s">
-        <v>408</v>
+      <c r="C365" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D365" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E365" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F365" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B366" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D366" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E366" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F366" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F367" s="2" t="s">
+        <v>416</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="734">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="744">
   <si>
     <t>ID</t>
   </si>
@@ -1181,7 +1181,7 @@
     <t>1361</t>
   </si>
   <si>
-    <t>Formazione dell'atto di nascita su autorizzazione tribunale in caso di omessa denuncia</t>
+    <t>Formazione atto nascita su autorizzazione tribunale (art. 32 e art 95)</t>
   </si>
   <si>
     <t>1362</t>
@@ -2009,55 +2009,67 @@
     <t>52111</t>
   </si>
   <si>
-    <t>Trascrizione: Acquisto alla nascita per iure soli: figlio di genitori che non trasmettono la cittadinanza italiana</t>
+    <t>Attestazione di acquisto alla nascita per iure soli: figlio di genitori che non trasmettono la cittadinanza italiana</t>
   </si>
   <si>
     <t>52112</t>
   </si>
   <si>
-    <t>Trascrizione: Straniero o apolide, del quale il padre o la madre o uno dei ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto mediante prestazione del servizio militare per lo Stato italiano</t>
+    <t>Accertamento positivo: straniero o apolide, del quale il padre o la madre o uno dei ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto mediante prestazione del servizio militare per lo Stato italiano</t>
   </si>
   <si>
     <t>52114</t>
   </si>
   <si>
-    <t>Trascrizione: Straniero o dell'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto assunzione di pubblico impiego alle dipendenze dello Stato</t>
+    <t>Accertamento positivo: straniero o dell'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto assunzione di pubblico impiego alle dipendenze dello Stato</t>
+  </si>
+  <si>
+    <t>52115</t>
+  </si>
+  <si>
+    <t>Acquisto automatico di cittadina straniera che si sposa con cittadino italiano fino al 27 aprile 1983</t>
   </si>
   <si>
     <t>52121</t>
   </si>
   <si>
-    <t>Trascrizione: Straniero o dall'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita, il quale, al raggiungimento della maggiore eta', risiede legalmente da almeno due anni nel territorio della Repubblica</t>
+    <t>Accertamento positivo: straniero o dall'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita, il quale, al raggiungimento della maggiore eta', risiede legalmente da almeno due anni nel territorio della Repubblica</t>
   </si>
   <si>
     <t>52122</t>
   </si>
   <si>
-    <t xml:space="preserve">Trascrizione: Straniero nato in Italia che vi abbia risieduto legalmente senza interruzioni fino alla maggiore eta' </t>
+    <t>Accertamento positivo: straniero nato in Italia che vi abbia risieduto legalmente senza interruzioni fino alla maggiore eta'</t>
   </si>
   <si>
     <t>52123</t>
   </si>
   <si>
-    <t>Trascrizione: Straniero riconosciuto durante la maggiore eta' da cittadino italiano</t>
+    <t>Accertamento positivo: straniero riconosciuto durante la maggiore eta' da cittadino italiano</t>
   </si>
   <si>
     <t>52141</t>
   </si>
   <si>
-    <t>Trascrizione: Figlio minore riconosciuto da cittadino italiano</t>
+    <t>Attestazione di figlio minore riconosciuto da cittadino italiano</t>
   </si>
   <si>
     <t>52142</t>
   </si>
   <si>
-    <t>Trascrizione: Adozione di minore in casi particolari art. 44 l. 184/1983 o adozione nazionale art 25 l. 184/1983 e art. 35 comma 4</t>
+    <t>Attestazione di acquisto cittadinanza in seguito ad adozione di minore (art 25 l. 184/1983 e art. 35 comma 4)</t>
   </si>
   <si>
     <t>52143</t>
   </si>
   <si>
-    <t>Trascrizione: Figlio minore di chi ha acquista la cittadinanza italiana</t>
+    <t>Attestazione di figlio minore di chi ha acquistato la cittadinanza italiana</t>
+  </si>
+  <si>
+    <t>52144</t>
+  </si>
+  <si>
+    <t>Attestazione di acquisto cittadinanza in seguito ad adozione in casi particolari di minorenne o maggiorenne (art. 44 l. 184/1983)</t>
   </si>
   <si>
     <t>52153</t>
@@ -2084,6 +2096,12 @@
     <t>Esito di accertamento per articolo 4 comma 1-bis</t>
   </si>
   <si>
+    <t>52157</t>
+  </si>
+  <si>
+    <t>Esito negativo di accertamento cittadinanza</t>
+  </si>
+  <si>
     <t>52211</t>
   </si>
   <si>
@@ -2184,6 +2202,18 @@
   </si>
   <si>
     <t>Trascrizione: Riacquisto per un anno di residenza in Italia</t>
+  </si>
+  <si>
+    <t>52711</t>
+  </si>
+  <si>
+    <t>Attestazione negativa</t>
+  </si>
+  <si>
+    <t>52712</t>
+  </si>
+  <si>
+    <t>Attestazione negativa per adozione legittimante</t>
   </si>
   <si>
     <t>52821</t>
@@ -2272,11 +2302,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G367"/>
+  <dimension ref="A1:G372"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.95703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="242.46875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="250.47265625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="21.33984375" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="15.55859375" customWidth="true" bestFit="true"/>
@@ -8931,7 +8961,7 @@
         <v>671</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>9</v>
@@ -9071,7 +9101,7 @@
         <v>685</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>9</v>
@@ -9091,7 +9121,7 @@
         <v>687</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="D341" s="2" t="s">
         <v>9</v>
@@ -9111,7 +9141,7 @@
         <v>689</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -9131,7 +9161,7 @@
         <v>691</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>9</v>
@@ -9151,7 +9181,7 @@
         <v>693</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>9</v>
@@ -9171,7 +9201,7 @@
         <v>695</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>9</v>
@@ -9431,7 +9461,7 @@
         <v>721</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="D358" s="2" t="s">
         <v>9</v>
@@ -9471,7 +9501,7 @@
         <v>725</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>409</v>
+        <v>8</v>
       </c>
       <c r="D360" s="2" t="s">
         <v>9</v>
@@ -9491,7 +9521,7 @@
         <v>727</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>9</v>
@@ -9508,7 +9538,7 @@
         <v>728</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>415</v>
+        <v>729</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -9520,18 +9550,18 @@
         <v>10</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>481</v>
+        <v>731</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>9</v>
@@ -9540,18 +9570,18 @@
         <v>10</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>420</v>
+        <v>733</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>9</v>
@@ -9560,18 +9590,18 @@
         <v>10</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>422</v>
+        <v>735</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>8</v>
+        <v>409</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>9</v>
@@ -9580,18 +9610,18 @@
         <v>10</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>427</v>
+        <v>737</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>428</v>
+        <v>8</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>9</v>
@@ -9600,26 +9630,126 @@
         <v>10</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>733</v>
+        <v>738</v>
       </c>
       <c r="B367" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D367" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E367" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F367" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="B368" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="C368" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D368" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E368" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F368" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B369" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D369" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E369" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F369" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" s="2" t="s">
+        <v>741</v>
+      </c>
+      <c r="B370" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D370" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E370" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F370" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D371" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E371" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F371" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B372" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C367" s="2" t="s">
+      <c r="C372" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D367" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E367" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F367" s="2" t="s">
+      <c r="D372" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F372" s="2" t="s">
         <v>416</v>
       </c>
     </row>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2232" uniqueCount="744">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="750">
   <si>
     <t>ID</t>
   </si>
@@ -1313,6 +1313,15 @@
     <t>Annotazione modificativa per cambio sesso</t>
   </si>
   <si>
+    <t>14880000</t>
+  </si>
+  <si>
+    <t>Annotazione per riconoscimento</t>
+  </si>
+  <si>
+    <t>2026-03-26 00:00:00.0</t>
+  </si>
+  <si>
     <t>14950000</t>
   </si>
   <si>
@@ -1413,6 +1422,15 @@
   </si>
   <si>
     <t>Trascrizione di decesso reso da pubblica autorita'</t>
+  </si>
+  <si>
+    <t>2216</t>
+  </si>
+  <si>
+    <t>Trascrizione atto di morte pervenuto da comune estero di decesso</t>
+  </si>
+  <si>
+    <t>2026-04-27 17:26:41.0</t>
   </si>
   <si>
     <t>2221</t>
@@ -2302,7 +2320,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G372"/>
+  <dimension ref="A1:G374"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.95703125" customWidth="true" bestFit="true"/>
@@ -6421,7 +6439,7 @@
         <v>434</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>323</v>
+        <v>435</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>9</v>
@@ -6435,10 +6453,10 @@
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C207" s="2" t="s">
         <v>323</v>
@@ -6455,10 +6473,10 @@
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="C208" s="2" t="s">
         <v>323</v>
@@ -6475,13 +6493,13 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>7</v>
+        <v>441</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>9</v>
@@ -6490,15 +6508,15 @@
         <v>10</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>441</v>
+        <v>7</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>8</v>
@@ -6510,15 +6528,15 @@
         <v>10</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>8</v>
@@ -6535,10 +6553,10 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>8</v>
@@ -6555,10 +6573,10 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="C213" s="2" t="s">
         <v>8</v>
@@ -6575,13 +6593,13 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>9</v>
@@ -6595,10 +6613,10 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="C215" s="2" t="s">
         <v>341</v>
@@ -6615,13 +6633,13 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="B216" s="2" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="C216" s="2" t="s">
-        <v>323</v>
+        <v>341</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>9</v>
@@ -6635,13 +6653,13 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B217" s="2" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C217" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>9</v>
@@ -6655,10 +6673,10 @@
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="B218" s="2" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="C218" s="2" t="s">
         <v>8</v>
@@ -6670,15 +6688,15 @@
         <v>10</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="B219" s="2" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="C219" s="2" t="s">
         <v>8</v>
@@ -6695,10 +6713,10 @@
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B220" s="2" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="C220" s="2" t="s">
         <v>8</v>
@@ -6715,16 +6733,16 @@
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B221" s="2" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D221" s="2" t="s">
-        <v>464</v>
+        <v>9</v>
       </c>
       <c r="E221" s="2" t="s">
         <v>10</v>
@@ -6741,10 +6759,10 @@
         <v>466</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>341</v>
+        <v>323</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>9</v>
+        <v>467</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>10</v>
@@ -6755,13 +6773,13 @@
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="B223" s="2" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>9</v>
@@ -6775,13 +6793,13 @@
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B224" s="2" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>8</v>
+        <v>472</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>9</v>
@@ -6795,10 +6813,10 @@
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B225" s="2" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
@@ -6815,10 +6833,10 @@
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
@@ -6835,13 +6853,13 @@
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>9</v>
@@ -6855,10 +6873,10 @@
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
@@ -6875,13 +6893,13 @@
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>415</v>
+        <v>482</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>9</v>
@@ -6890,15 +6908,15 @@
         <v>10</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>8</v>
@@ -6910,15 +6928,15 @@
         <v>10</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>8</v>
@@ -6935,10 +6953,10 @@
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>422</v>
+        <v>487</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>8</v>
@@ -6955,13 +6973,13 @@
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>428</v>
+        <v>8</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>9</v>
@@ -6975,13 +6993,13 @@
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>9</v>
@@ -6995,13 +7013,13 @@
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>7</v>
+        <v>427</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>8</v>
+        <v>428</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>9</v>
@@ -7010,18 +7028,18 @@
         <v>10</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>488</v>
+        <v>430</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>9</v>
@@ -7030,35 +7048,35 @@
         <v>10</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>490</v>
+        <v>7</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D237" s="2" t="s">
-        <v>491</v>
+        <v>9</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>8</v>
@@ -7075,16 +7093,16 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="C239" s="2" t="s">
         <v>323</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>10</v>
@@ -7095,10 +7113,10 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>8</v>
@@ -7115,16 +7133,16 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>9</v>
+        <v>497</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>10</v>
@@ -7135,10 +7153,10 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>8</v>
@@ -7155,10 +7173,10 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>8</v>
@@ -7175,10 +7193,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>8</v>
@@ -7195,10 +7213,10 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>8</v>
@@ -7215,10 +7233,10 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>8</v>
@@ -7235,10 +7253,10 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>8</v>
@@ -7255,13 +7273,13 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>9</v>
@@ -7275,10 +7293,10 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>8</v>
@@ -7295,13 +7313,13 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>9</v>
@@ -7315,10 +7333,10 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
@@ -7335,13 +7353,13 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D252" s="2" t="s">
         <v>9</v>
@@ -7355,13 +7373,13 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D253" s="2" t="s">
         <v>9</v>
@@ -7375,13 +7393,13 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>9</v>
@@ -7395,13 +7413,13 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>9</v>
@@ -7410,15 +7428,15 @@
         <v>10</v>
       </c>
       <c r="F255" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -7430,15 +7448,15 @@
         <v>10</v>
       </c>
       <c r="F256" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
@@ -7455,10 +7473,10 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
@@ -7475,10 +7493,10 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
@@ -7495,13 +7513,13 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>536</v>
+        <v>8</v>
       </c>
       <c r="D260" s="2" t="s">
         <v>9</v>
@@ -7515,10 +7533,10 @@
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
@@ -7535,13 +7553,13 @@
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>8</v>
+        <v>542</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>9</v>
@@ -7550,15 +7568,15 @@
         <v>10</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
@@ -7570,15 +7588,15 @@
         <v>10</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -7595,10 +7613,10 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -7615,10 +7633,10 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -7635,10 +7653,10 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -7655,10 +7673,10 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -7675,30 +7693,30 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D269" s="2" t="s">
-        <v>555</v>
+        <v>9</v>
       </c>
       <c r="E269" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
@@ -7710,21 +7728,21 @@
         <v>10</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>9</v>
+        <v>561</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>10</v>
@@ -7735,10 +7753,10 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -7755,13 +7773,13 @@
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D273" s="2" t="s">
         <v>9</v>
@@ -7770,15 +7788,15 @@
         <v>10</v>
       </c>
       <c r="F273" s="2" t="s">
-        <v>416</v>
+        <v>14</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>415</v>
+        <v>567</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -7790,18 +7808,18 @@
         <v>10</v>
       </c>
       <c r="F274" s="2" t="s">
-        <v>416</v>
+        <v>14</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>481</v>
+        <v>569</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
@@ -7815,10 +7833,10 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>8</v>
@@ -7835,10 +7853,10 @@
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>422</v>
+        <v>487</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>8</v>
@@ -7855,13 +7873,13 @@
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>428</v>
+        <v>8</v>
       </c>
       <c r="D278" s="2" t="s">
         <v>9</v>
@@ -7875,13 +7893,13 @@
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D279" s="2" t="s">
         <v>9</v>
@@ -7895,13 +7913,13 @@
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>7</v>
+        <v>427</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>8</v>
+        <v>428</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>9</v>
@@ -7910,18 +7928,18 @@
         <v>10</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>572</v>
+        <v>430</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>9</v>
@@ -7930,15 +7948,15 @@
         <v>10</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>574</v>
+        <v>7</v>
       </c>
       <c r="C282" s="2" t="s">
         <v>8</v>
@@ -7950,15 +7968,15 @@
         <v>10</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>8</v>
@@ -7975,10 +7993,10 @@
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -7995,10 +8013,10 @@
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -8015,10 +8033,10 @@
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -8035,10 +8053,10 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -8050,15 +8068,15 @@
         <v>10</v>
       </c>
       <c r="F287" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -8070,15 +8088,15 @@
         <v>10</v>
       </c>
       <c r="F288" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -8095,10 +8113,10 @@
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
@@ -8115,13 +8133,13 @@
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D291" s="2" t="s">
         <v>9</v>
@@ -8135,10 +8153,10 @@
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
@@ -8155,13 +8173,13 @@
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>9</v>
@@ -8170,15 +8188,15 @@
         <v>10</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>8</v>
@@ -8190,15 +8208,15 @@
         <v>10</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>8</v>
@@ -8215,10 +8233,10 @@
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -8235,10 +8253,10 @@
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -8255,13 +8273,13 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D298" s="2" t="s">
         <v>9</v>
@@ -8275,13 +8293,13 @@
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="D299" s="2" t="s">
         <v>9</v>
@@ -8290,18 +8308,18 @@
         <v>10</v>
       </c>
       <c r="F299" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>611</v>
+        <v>323</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>9</v>
@@ -8310,18 +8328,18 @@
         <v>10</v>
       </c>
       <c r="F300" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>8</v>
+        <v>341</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>9</v>
@@ -8330,18 +8348,18 @@
         <v>10</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>14</v>
+        <v>328</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>415</v>
+        <v>616</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>8</v>
+        <v>617</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
@@ -8350,15 +8368,15 @@
         <v>10</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>481</v>
+        <v>619</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>8</v>
@@ -8370,15 +8388,15 @@
         <v>10</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>416</v>
+        <v>14</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>8</v>
@@ -8395,10 +8413,10 @@
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>422</v>
+        <v>487</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -8415,13 +8433,13 @@
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>428</v>
+        <v>8</v>
       </c>
       <c r="D306" s="2" t="s">
         <v>9</v>
@@ -8435,13 +8453,13 @@
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>430</v>
+        <v>422</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D307" s="2" t="s">
         <v>9</v>
@@ -8455,13 +8473,13 @@
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>621</v>
+        <v>427</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>622</v>
+        <v>428</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>9</v>
@@ -8475,13 +8493,13 @@
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>7</v>
+        <v>430</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>9</v>
@@ -8490,18 +8508,18 @@
         <v>10</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>11</v>
+        <v>416</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>8</v>
+        <v>628</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>9</v>
@@ -8510,15 +8528,15 @@
         <v>10</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>14</v>
+        <v>416</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>627</v>
+        <v>7</v>
       </c>
       <c r="C311" s="2" t="s">
         <v>8</v>
@@ -8530,15 +8548,15 @@
         <v>10</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>8</v>
@@ -8555,10 +8573,10 @@
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>8</v>
@@ -8575,10 +8593,10 @@
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>8</v>
@@ -8595,10 +8613,10 @@
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -8615,10 +8633,10 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -8635,10 +8653,10 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -8655,13 +8673,13 @@
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D318" s="2" t="s">
         <v>9</v>
@@ -8675,13 +8693,13 @@
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D319" s="2" t="s">
         <v>9</v>
@@ -8695,13 +8713,13 @@
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>9</v>
@@ -8715,13 +8733,13 @@
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>9</v>
@@ -8735,10 +8753,10 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -8755,10 +8773,10 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>8</v>
@@ -8775,10 +8793,10 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>8</v>
@@ -8795,10 +8813,10 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -8815,10 +8833,10 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -8835,10 +8853,10 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -8855,13 +8873,13 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D328" s="2" t="s">
         <v>9</v>
@@ -8875,10 +8893,10 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -8895,13 +8913,13 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>9</v>
@@ -8910,15 +8928,15 @@
         <v>10</v>
       </c>
       <c r="F330" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -8930,15 +8948,15 @@
         <v>10</v>
       </c>
       <c r="F331" s="2" t="s">
-        <v>328</v>
+        <v>14</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -8955,13 +8973,13 @@
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>9</v>
@@ -8975,10 +8993,10 @@
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -8995,13 +9013,13 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>9</v>
@@ -9015,10 +9033,10 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
@@ -9035,10 +9053,10 @@
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -9055,10 +9073,10 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>8</v>
@@ -9075,10 +9093,10 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -9095,13 +9113,13 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="D340" s="2" t="s">
         <v>9</v>
@@ -9115,10 +9133,10 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
@@ -9135,13 +9153,13 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -9155,13 +9173,13 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="D343" s="2" t="s">
         <v>9</v>
@@ -9175,13 +9193,13 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D344" s="2" t="s">
         <v>9</v>
@@ -9195,13 +9213,13 @@
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>306</v>
+        <v>341</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>9</v>
@@ -9215,13 +9233,13 @@
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>8</v>
+        <v>323</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>9</v>
@@ -9235,13 +9253,13 @@
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>9</v>
@@ -9255,10 +9273,10 @@
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>8</v>
@@ -9275,10 +9293,10 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>8</v>
@@ -9295,10 +9313,10 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>8</v>
@@ -9315,10 +9333,10 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>8</v>
@@ -9335,10 +9353,10 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
@@ -9355,10 +9373,10 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -9375,10 +9393,10 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -9395,10 +9413,10 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
@@ -9415,10 +9433,10 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
@@ -9435,10 +9453,10 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -9455,10 +9473,10 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
@@ -9475,10 +9493,10 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -9495,10 +9513,10 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
@@ -9515,13 +9533,13 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="D361" s="2" t="s">
         <v>9</v>
@@ -9535,10 +9553,10 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -9555,10 +9573,10 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>306</v>
@@ -9575,13 +9593,13 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>306</v>
+        <v>8</v>
       </c>
       <c r="D364" s="2" t="s">
         <v>9</v>
@@ -9595,13 +9613,13 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>409</v>
+        <v>306</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>9</v>
@@ -9615,13 +9633,13 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>8</v>
+        <v>306</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>9</v>
@@ -9635,13 +9653,13 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>415</v>
+        <v>741</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>8</v>
+        <v>409</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>9</v>
@@ -9650,15 +9668,15 @@
         <v>10</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>481</v>
+        <v>743</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
@@ -9670,15 +9688,15 @@
         <v>10</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>416</v>
+        <v>328</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>8</v>
@@ -9695,10 +9713,10 @@
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>422</v>
+        <v>487</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>8</v>
@@ -9715,13 +9733,13 @@
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>427</v>
+        <v>420</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>428</v>
+        <v>8</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>9</v>
@@ -9735,21 +9753,61 @@
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
       <c r="B372" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D372" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E372" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F372" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="B373" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F373" s="2" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B374" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C372" s="2" t="s">
+      <c r="C374" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="D372" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E372" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F372" s="2" t="s">
+      <c r="D374" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F374" s="2" t="s">
         <v>416</v>
       </c>
     </row>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="750">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="743">
   <si>
     <t>ID</t>
   </si>
@@ -53,7 +53,7 @@
     <t>11111000</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione entro i 10 giorni - resa dal padre </t>
+    <t xml:space="preserve">Dichiarazione entro i 10 giorni - resa dal padre </t>
   </si>
   <si>
     <t>1</t>
@@ -68,7 +68,7 @@
     <t>11111200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione nel matrimonio resa dal padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione nei termini di filiazione nel matrimonio resa dal padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11112000</t>
@@ -86,13 +86,13 @@
     <t>11112200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione nel matrimonio resa dalla madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione nei termini di filiazione nel matrimonio resa dalla madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11113000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione entro i 10 giorni - resa dal padre con presenza madre</t>
+    <t>Dichiarazione entro i 10 giorni - resa dal padre con presenza madre</t>
   </si>
   <si>
     <t>11113100</t>
@@ -104,7 +104,7 @@
     <t>11113200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione nel matrimonio resa dal padre con presenza madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione nei termini di filiazione nel matrimonio resa dal padre con presenza madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11114000</t>
@@ -122,7 +122,7 @@
     <t>11114200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione nel matrimonio resa dal procuratore del padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione nei termini di filiazione nel matrimonio resa dal procuratore del padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11115000</t>
@@ -140,13 +140,13 @@
     <t>11115200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione nel matrimonio resa da sanitario/ostetrica all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione nei termini di filiazione nel matrimonio resa da sanitario/ostetrica all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11116000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione entro i 10 giorni - resa dalla madre con presenza padre</t>
+    <t>Dichiarazione entro i 10 giorni - resa dalla madre con presenza padre</t>
   </si>
   <si>
     <t>11116100</t>
@@ -158,7 +158,7 @@
     <t>11116200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione nel matrimonio resa dalla madre con presenza padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione nei termini di filiazione nel matrimonio resa dalla madre con presenza padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11117000</t>
@@ -176,133 +176,133 @@
     <t>11117200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione nel matrimonio resa dal procuratore della madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione nei termini di filiazione nel matrimonio resa dal procuratore della madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11121000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal padre</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal padre</t>
   </si>
   <si>
     <t>11121100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal padre all'USC di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal padre all'USC di bimbo nato morto</t>
   </si>
   <si>
     <t>11121200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11122000</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dalla madre </t>
+    <t xml:space="preserve">Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dalla madre </t>
   </si>
   <si>
     <t>11122100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre all'USC di filiazione di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre all'USC di filiazione di bimbo nato morto</t>
   </si>
   <si>
     <t>11122200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11123000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal padre con presenza madre</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal padre con presenza madre</t>
   </si>
   <si>
     <t>11123100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal padre con presenza madre all'USC di filiazione di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal padre con presenza madre all'USC di filiazione di bimbo nato morto</t>
   </si>
   <si>
     <t>11123200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal padre con presenza madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal padre con presenza madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11124000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal procuratore del padre</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal procuratore del padre</t>
   </si>
   <si>
     <t>11124100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore del padre all'USC di filiazione di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore del padre all'USC di filiazione di bimbo nato morto</t>
   </si>
   <si>
     <t>11124200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore del padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore del padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11125000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto</t>
   </si>
   <si>
     <t>11125100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC da ostetrica o altro sanitario di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa all'USC da ostetrica o altro sanitario di bimbo nato morto</t>
   </si>
   <si>
     <t>11125200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa da sanitario all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa da sanitario all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11126000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dalla madre con presenza padre</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dalla madre con presenza padre</t>
   </si>
   <si>
     <t>11126100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre con presenza padre all'USC di filiazione di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre con presenza padre all'USC di filiazione di bimbo nato morto</t>
   </si>
   <si>
     <t>11126200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre con presenza padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dalla madre con presenza padre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11127000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal procuratore della madre</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa all'USC dal procuratore della madre</t>
   </si>
   <si>
     <t>11127100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore della madre all'USC di filiazione di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore della madre all'USC di filiazione di bimbo nato morto</t>
   </si>
   <si>
     <t>11127200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore della madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione nel matrimonio resa dal procuratore della madre all'USC di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11211001</t>
@@ -326,7 +326,7 @@
     <t>11211104</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con consenso materno espresso con atto notarile di bimbo nato morto</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con consenso materno espresso con atto notarile di bimbo nato morto</t>
   </si>
   <si>
     <t>11211201</t>
@@ -341,7 +341,7 @@
     <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con consenso materno espresso con atto notarile di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
-    <t>2024-10-29 22:31:11.0</t>
+    <t>2024-11-04 08:18:09.0</t>
   </si>
   <si>
     <t>11212002</t>
@@ -359,43 +359,43 @@
     <t>11212102</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno di bimbo nato morto</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno di bimbo nato morto</t>
   </si>
   <si>
     <t>11212103</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con consenso paterno espresso con atto notarile di bimbo nato morto </t>
+    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con consenso paterno espresso con atto notarile di bimbo nato morto </t>
   </si>
   <si>
     <t>11212202</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre senza consenso paterno di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre senza consenso paterno di bimbo nato vivo ma morto prima della denuncia di nascita </t>
   </si>
   <si>
     <t>11212203</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con consenso paterno espresso con atto notarile di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con consenso paterno espresso con atto notarile di bimbo nato vivo ma morto prima della denuncia di nascita </t>
   </si>
   <si>
     <t>11213000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre</t>
   </si>
   <si>
     <t>11213100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato morto</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato morto</t>
   </si>
   <si>
     <t>11213200</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
   </si>
   <si>
     <t>11214000</t>
@@ -407,31 +407,31 @@
     <t>11214100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato morto</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato morto</t>
   </si>
   <si>
     <t>11214200</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
   </si>
   <si>
     <t>11216000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre</t>
   </si>
   <si>
     <t>11216100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato morto</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato morto</t>
   </si>
   <si>
     <t>11216200</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
   </si>
   <si>
     <t>11217000</t>
@@ -443,13 +443,13 @@
     <t>11217100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato morto</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato morto</t>
   </si>
   <si>
     <t>11217200</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
   </si>
   <si>
     <t>11218000</t>
@@ -458,7 +458,7 @@
     <t>Dichiarazione entro i 10 giorni - resa dal procuratore del padre con presenza della madre - Filiazione fuori dal matrimonio</t>
   </si>
   <si>
-    <t>2024-10-29 22:30:14.0</t>
+    <t>2024-11-04 08:19:08.0</t>
   </si>
   <si>
     <t>11218100</t>
@@ -494,145 +494,145 @@
     <t>11221001</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre senza il consenso materno </t>
+    <t xml:space="preserve">Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre senza il consenso materno </t>
   </si>
   <si>
     <t>11221004</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con il consenso materno espresso con atto notarile </t>
+    <t xml:space="preserve">Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con il consenso materno espresso con atto notarile </t>
   </si>
   <si>
     <t>11221101</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre senza consenso materno di bimbo nato morto </t>
+    <t xml:space="preserve">Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre senza consenso materno di bimbo nato morto </t>
   </si>
   <si>
     <t>11221104</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con consenso materno espresso con atto notarile di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con consenso materno espresso con atto notarile di bimbo nato morto</t>
   </si>
   <si>
     <t>11221201</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre senza consenso materno di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre senza consenso materno di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11221204</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con consenso materno espresso con atto notarile di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con consenso materno espresso con atto notarile di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11222002</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno</t>
   </si>
   <si>
     <t>11222003</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno espresso con atto notarile</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno espresso con atto notarile</t>
   </si>
   <si>
     <t>11222102</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno di bimbo nato morto</t>
   </si>
   <si>
     <t>11222103</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno di bimbo nato morto</t>
   </si>
   <si>
     <t>11222202</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre senza il consenso paterno di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11222203</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11223000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre</t>
   </si>
   <si>
     <t>11223100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato morto</t>
   </si>
   <si>
     <t>11223200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal padre con presenza madre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11224000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre</t>
   </si>
   <si>
     <t>11224100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato morto</t>
   </si>
   <si>
     <t>11224200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato vivo ma morto prima della dichiarazione</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore del padre di bimbo nato vivo ma morto prima della dichiarazione</t>
   </si>
   <si>
     <t>11226000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre</t>
   </si>
   <si>
     <t>11226100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato morto</t>
   </si>
   <si>
     <t>11226200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11227000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre con consenso del padre ad essere nominato</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre con consenso del padre ad essere nominato</t>
   </si>
   <si>
     <t>11227100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato morto</t>
   </si>
   <si>
     <t>11227200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11228000</t>
@@ -671,181 +671,178 @@
     <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dal procuratore della madre con presenza del padre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
-    <t>2024-10-29 22:30:15.0</t>
-  </si>
-  <si>
     <t>11315000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione resa da ostetrica o altro - fuori matrimonio</t>
+    <t>Dichiarazione resa da ostetrica o altro - fuori matrimonio</t>
   </si>
   <si>
     <t>11315100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei temini di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato morto</t>
+    <t>Dichiarazione nei temini di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato morto</t>
   </si>
   <si>
     <t>11315200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato vivo ma morto prima della dichiarazione</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato vivo ma morto prima della dichiarazione</t>
   </si>
   <si>
     <t>11325000</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato vivo</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato vivo</t>
   </si>
   <si>
     <t>11325100</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato morto</t>
   </si>
   <si>
     <t>11325200</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato vivo ma morto prima della dichiarazione</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC da ostetrica o altro sanitario che ha assistito al parto - nato vivo ma morto prima della dichiarazione</t>
   </si>
   <si>
     <t>11411010</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione fuori del matrimonio nei termini di legge resa dal padre, di bimbo riconosciuto da entrambi i genitori prima della nascita</t>
+    <t>Dichiarazione fuori del matrimonio nei termini di legge resa dal padre, di bimbo riconosciuto da entrambi i genitori prima della nascita</t>
   </si>
   <si>
     <t>11411024</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal padre con atto pubblico di consenso della madre, di bimbo riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal padre con atto pubblico di consenso della madre, di bimbo riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11412010</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio nei termini di legge, resa dalla madre di bimbo riconosciuto prima della nascita da parte di entrambi i genitori</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio nei termini di legge, resa dalla madre di bimbo riconosciuto prima della nascita da parte di entrambi i genitori</t>
   </si>
   <si>
     <t>11412020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio nei termini di legge, resa dalla madre di bimbo riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio nei termini di legge, resa dalla madre di bimbo riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11413020</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio nei termini di legge resa dal padre con presenza madre di bimbo riconosciuto dalla madre prima della nascita </t>
+    <t xml:space="preserve">Dichiarazione di filiazione fuori del matrimonio nei termini di legge resa dal padre con presenza madre di bimbo riconosciuto dalla madre prima della nascita </t>
   </si>
   <si>
     <t>11414010</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal procuratore del padre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal procuratore del padre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
   </si>
   <si>
     <t>11414020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal procuratore del padre, di bimbo riconosciuto da parte della madre prima della nascita</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal procuratore del padre, di bimbo riconosciuto da parte della madre prima della nascita</t>
   </si>
   <si>
     <t>11415010</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio nei termini di legge, resa dall'ostetrica o sanitario o altra persona che ha assistito al parto di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio nei termini di legge, resa dall'ostetrica o sanitario o altra persona che ha assistito al parto di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
   </si>
   <si>
     <t>11415020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiiazione fuori del matrimonio nei termini di legge resa dall'ostetrica o da sanitario o da altra persona che ha assistito al parto, di bimbo che e' stato riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione di filiiazione fuori del matrimonio nei termini di legge resa dall'ostetrica o da sanitario o da altra persona che ha assistito al parto, di bimbo che e' stato riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11416020</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio nei termini di legge resa dalla madre con presenza padre di bimbo riconosciuto dalla madre prima della nascita </t>
+    <t xml:space="preserve">Dichiarazione di filiazione fuori del matrimonio nei termini di legge resa dalla madre con presenza padre di bimbo riconosciuto dalla madre prima della nascita </t>
   </si>
   <si>
     <t>11417010</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa da procuratore speciale della madre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa da procuratore speciale della madre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
   </si>
   <si>
     <t>11417020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal procuratore della madre, di bimbo riconosciuto da parte della madre prima della nascita</t>
+    <t>Dichiarazione di filiazione fuori del matrimonio, nei termini di legge, resa dal procuratore della madre, di bimbo riconosciuto da parte della madre prima della nascita</t>
   </si>
   <si>
     <t>11421010</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio,  resa dal padre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori del matrimonio,  resa dal padre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
   </si>
   <si>
     <t>11421024</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal padre mediante atto pubblico di consenso della madre, di bimbo riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal padre mediante atto pubblico di consenso della madre, di bimbo riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11422010</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva, di filiazione fuori del matrimonio, resa dalla madre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
+    <t>Dichiarazione tardiva, di filiazione fuori del matrimonio, resa dalla madre, di bimbo riconosciuto da parte di entrambi i genitori prima della nascita</t>
   </si>
   <si>
     <t>11422020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dalla madre di bimbo riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori del matrimonio, resa dalla madre di bimbo riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11423020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal padre con presenza madre di bimbo riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal padre con presenza madre di bimbo riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11424020</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal procuratore del padre di bimbo riconosciuto dalla madre prima della nascita </t>
+    <t xml:space="preserve">Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal procuratore del padre di bimbo riconosciuto dalla madre prima della nascita </t>
   </si>
   <si>
     <t>11425010</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dall'ostetrica o sanitario o altra persona che ha assistito al parto di bimbo riconosciuto da parte di entrambi i genitori prima della nascita </t>
+    <t xml:space="preserve">Dichiarazione tardiva di filiazione fuori del matrimonio, resa dall'ostetrica o sanitario o altra persona che ha assistito al parto di bimbo riconosciuto da parte di entrambi i genitori prima della nascita </t>
   </si>
   <si>
     <t>11425020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dall'ostetrica o sanitario o altra persona che ha assistito al parto di bimbo riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori del matrimonio, resa dall'ostetrica o sanitario o altra persona che ha assistito al parto di bimbo riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11426020</t>
   </si>
   <si>
-    <t>Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dall madre con presenza padre di bimbo riconosciuto dalla madre prima della nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori del matrimonio, resa dall madre con presenza padre di bimbo riconosciuto dalla madre prima della nascita</t>
   </si>
   <si>
     <t>11427020</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nascita: Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal procuratore della madre di bimbo riconosciuto dalla madre prima della nascita </t>
+    <t xml:space="preserve">Dichiarazione tardiva di filiazione fuori del matrimonio, resa dal procuratore della madre di bimbo riconosciuto dalla madre prima della nascita </t>
   </si>
   <si>
     <t>11999999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio dichiarazioni nascita</t>
+    <t>Caso d'uso di servizio (dichiarazioni nascita)</t>
   </si>
   <si>
     <t>12211312</t>
@@ -962,19 +959,19 @@
     <t>12323100</t>
   </si>
   <si>
-    <t>Riconoscimento: Assenso al riconoscimento da parte del figlio ultraquattordicenne</t>
+    <t>Assenso al riconoscimento da parte del figlio ultraquattordicenne</t>
   </si>
   <si>
     <t>12421200</t>
   </si>
   <si>
-    <t>Riconoscimento: Consenso paterno al riconoscimento materno del figlio infraquattordicenne</t>
+    <t>Consenso paterno al riconoscimento materno del figlio infraquattordicenne</t>
   </si>
   <si>
     <t>12422200</t>
   </si>
   <si>
-    <t>Riconoscimento: Consenso materno al riconoscimento paterno del figlio infraquattordicenne</t>
+    <t>Consenso materno al riconoscimento paterno del figlio infraquattordicenne</t>
   </si>
   <si>
     <t>12422300</t>
@@ -989,13 +986,13 @@
     <t>12999999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio riconoscimenti</t>
+    <t>Caso d'uso di servizio (riconoscimenti)</t>
   </si>
   <si>
     <t>1311</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione di atto di nascita avvenuta all'estero su richiesta dell'autorita' diplomatica o consolare</t>
+    <t>Trascrizione di atto di nascita avvenuta all'estero su richiesta dell'autorita' diplomatica o consolare</t>
   </si>
   <si>
     <t>3</t>
@@ -1004,19 +1001,19 @@
     <t>1312</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione di atto di nascita avvenuta all estero su richiesta di chi ha interesse alla trascrizione</t>
+    <t>Trascrizione di atto di nascita avvenuta all estero su richiesta di chi ha interesse alla trascrizione</t>
   </si>
   <si>
     <t>1313</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione dichiarazione di nascita avvenuta durante un viaggio in mare, aereo, treno</t>
+    <t>Trascrizione dichiarazione di nascita avvenuta durante un viaggio in mare, aereo, treno</t>
   </si>
   <si>
     <t>1314</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione atto di nascita resa alla direzione sanitaria</t>
+    <t>Trascrizione atto di nascita resa alla direzione sanitaria</t>
   </si>
   <si>
     <t>1315</t>
@@ -1043,37 +1040,37 @@
     <t>1321</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza straniera di dichiarazione giudiziale di maternita' richiesta dall'interessato</t>
+    <t>Trascrizione della sentenza straniera di dichiarazione giudiziale di maternita' richiesta dall'interessato</t>
   </si>
   <si>
     <t>1322</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza straniera di dichiarazione giudiziale di paternita' richiesta dall'interessato</t>
+    <t>Trascrizione della sentenza straniera di dichiarazione giudiziale di paternita' richiesta dall'interessato</t>
   </si>
   <si>
     <t>1323</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza straniera di dichiarazione giudiziale di paternita' o maternita' su richiesta dell'autorita' diplomatica o consolare</t>
+    <t>Trascrizione della sentenza straniera di dichiarazione giudiziale di paternita' o maternita' su richiesta dell'autorita' diplomatica o consolare</t>
   </si>
   <si>
     <t>1324</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione richiesta dall'interessato della sentenza straniera di disconoscimento di paternita'</t>
+    <t>Trascrizione richiesta dall'interessato della sentenza straniera di disconoscimento di paternita'</t>
   </si>
   <si>
     <t>1325</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza straniera di disconoscimento di paternita' su richiesta dell'autorita' diplomatica o consolare</t>
+    <t>Trascrizione della sentenza straniera di disconoscimento di paternita' su richiesta dell'autorita' diplomatica o consolare</t>
   </si>
   <si>
     <t>1331</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione del decreto prefettizio di cambiamento del nome e cognome</t>
+    <t>Trascrizione del decreto prefettizio di cambiamento del nome e cognome</t>
   </si>
   <si>
     <t>1332</t>
@@ -1082,7 +1079,7 @@
     <t>Trascrizione del decreto prefettizio o sentenza di cambiamento del nome e cognome su richiesta dell'autorita' pubblica o consolare</t>
   </si>
   <si>
-    <t>2024-11-26 19:04:34.0</t>
+    <t>2024-11-29 12:22:03.0</t>
   </si>
   <si>
     <t>1333</t>
@@ -1091,9 +1088,6 @@
     <t>Trascrizione decreto prefettizio cambio cognome multi intestatari</t>
   </si>
   <si>
-    <t>2024-11-26 19:05:04.0</t>
-  </si>
-  <si>
     <t>1334</t>
   </si>
   <si>
@@ -1109,31 +1103,31 @@
     <t>1341</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza di adozione di minore emessa dal Tribunale dei minori</t>
+    <t>Trascrizione della sentenza di adozione di minore emessa dal Tribunale dei minori</t>
   </si>
   <si>
     <t>1342</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza di adozione di minore in casi particolari emessa dal Tribunale dei minori</t>
+    <t>Trascrizione della sentenza di adozione di minore in casi particolari emessa dal Tribunale dei minori</t>
   </si>
   <si>
     <t>1343</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza di revoca della adozione di minore in casi particolari</t>
+    <t>Trascrizione della sentenza di revoca della adozione di minore in casi particolari</t>
   </si>
   <si>
     <t>1344</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della sentenza di adozione di maggiorenne emessa dal Tribunale</t>
+    <t>Trascrizione della sentenza di adozione di maggiorenne emessa dal Tribunale</t>
   </si>
   <si>
     <t>1345</t>
   </si>
   <si>
-    <t xml:space="preserve">Trascrizione di nascita: Trascrizione della sentenza di revoca della adozione di maggiorenne </t>
+    <t xml:space="preserve">Trascrizione della sentenza di revoca della adozione di maggiorenne </t>
   </si>
   <si>
     <t>1351</t>
@@ -1145,19 +1139,19 @@
     <t>1352</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione del provvedimento straniero di adozione di minore riconosciuto valido dal Tribunale dei minori convenzione Aja 29.5.1993</t>
+    <t>Trascrizione del provvedimento straniero di adozione di minore riconosciuto valido dal Tribunale dei minori (convenzione Aja 29.5.1993)</t>
   </si>
   <si>
     <t>1353</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione di provvedimento straniero adozione di minorenne o maggiorenne in casi particolari richiesta da un privato</t>
+    <t>Trascrizione di provvedimento straniero adozione di minorenne o maggiorenne in casi particolari richiesta da un privato</t>
   </si>
   <si>
     <t>1354</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione di provvedimento straniero adozione di minorenne o maggiorenne in casi particolari richiesta dall'autorita' diplomatica o consolare</t>
+    <t>Trascrizione di provvedimento straniero adozione di minorenne o maggiorenne in casi particolari richiesta dall'autorita' diplomatica o consolare</t>
   </si>
   <si>
     <t>1355</t>
@@ -1166,16 +1160,13 @@
     <t>Trascrizione sentenza tribunale dei minori che dichiara efficace il provvedimento straniero di adozione (fuori convenzione Aja)</t>
   </si>
   <si>
-    <t>2024-11-26 19:03:04.0</t>
-  </si>
-  <si>
     <t>1356</t>
   </si>
   <si>
     <t>Trascrizione di provvedimento straniero di cambio sesso</t>
   </si>
   <si>
-    <t>2025-06-25 12:06:42.0</t>
+    <t>2025-06-29 23:45:35.0</t>
   </si>
   <si>
     <t>1361</t>
@@ -1187,37 +1178,37 @@
     <t>1362</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Scelta del cognome del figlio maggiorenne il cui genitore ha cambiato o modificato il cognome su istanza di parte</t>
+    <t>Scelta del cognome del figlio maggiorenne il cui genitore ha cambiato o modificato il cognome su istanza di parte</t>
   </si>
   <si>
     <t>1363</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Scelta del cognome del figlio maggiorenne il cui genitore ha cambiato o modificato il cognome su istanza di ufficio</t>
+    <t>Scelta del cognome del figlio maggiorenne il cui genitore ha cambiato o modificato il cognome su istanza di ufficio</t>
   </si>
   <si>
     <t>1364</t>
   </si>
   <si>
-    <t xml:space="preserve">Trascrizione di nascita: Scelta del cognome del figlio maggiorenne a seguito di accertamento o riconoscimento della paternita' successivamente al riconoscimento materno </t>
+    <t xml:space="preserve">Scelta del cognome del figlio maggiorenne a seguito di accertamento o riconoscimento della paternita' successivamente al riconoscimento materno </t>
   </si>
   <si>
     <t>1365</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Trascrizione della comunicazione scritta trasmessa dal direttore dell'istituto che accoglie un minore abbandonato</t>
+    <t>Trascrizione della comunicazione scritta trasmessa dal direttore dell'istituto che accoglie un minore abbandonato</t>
   </si>
   <si>
     <t>1366</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Scelta del cognome del figlio di ignoti maggiorenne a seguito del riconoscimento da parte di uno o di entrambi i genitori  su istanza di parte</t>
+    <t>Scelta del cognome del figlio di ignoti maggiorenne a seguito del riconoscimento da parte di uno o di entrambi i genitori  su istanza di parte</t>
   </si>
   <si>
     <t>1367</t>
   </si>
   <si>
-    <t>Trascrizione di nascita: Scelta del cognome del figlio di ignoti maggiorenne a seguito del riconoscimento da parte di uno o di entrambi i genitori  su istanza di ufficio</t>
+    <t>Scelta del cognome del figlio di ignoti maggiorenne a seguito del riconoscimento da parte di uno o di entrambi i genitori  su istanza di ufficio</t>
   </si>
   <si>
     <t>1368</t>
@@ -1226,40 +1217,34 @@
     <t>Trascrizione provvedimento del Tribunale per il cambiamento del cognome del minore a seguito di riconoscimento art. 262</t>
   </si>
   <si>
-    <t>2026-02-24 16:19:54.0</t>
-  </si>
-  <si>
-    <t>2026-02-24 16:18:49.0</t>
-  </si>
-  <si>
-    <t>2026-02-24 16:18:38.0</t>
+    <t>2026-03-02 08:14:30.0</t>
   </si>
   <si>
     <t>1381</t>
   </si>
   <si>
-    <t>Trascrizione atti multipli adozioni</t>
-  </si>
-  <si>
-    <t>2024-10-29 22:30:43.0</t>
+    <t>Trascrizione atti multipli di adozione di minore</t>
+  </si>
+  <si>
+    <t>2024-11-04 08:17:34.0</t>
   </si>
   <si>
     <t>1382</t>
   </si>
   <si>
-    <t>Trascrizione atti multipli adozioni nazionali</t>
+    <t>Trascrizione atti multipli di adozione di maggiorenne o casi particolari</t>
   </si>
   <si>
     <t>1399</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio trascrizioni nascita</t>
+    <t>Caso d'uso di servizio (trascrizioni nascita)</t>
   </si>
   <si>
     <t>14400000</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio annotazione comunicazione da altri comuni</t>
+    <t>Caso d'uso di servizio annotazione (comunicazione da altri comuni)</t>
   </si>
   <si>
     <t>2</t>
@@ -1268,7 +1253,7 @@
     <t>14500000</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio  annotazione comunicazione da altre amministrazioni</t>
+    <t>Caso d'uso di servizio  annotazione (comunicazione da altre amministrazioni)</t>
   </si>
   <si>
     <t>14630000</t>
@@ -1298,7 +1283,7 @@
     <t>Annotazione modificativa generica</t>
   </si>
   <si>
-    <t>2023-12-21 09:54:27.0</t>
+    <t>2023-12-20 16:46:56.0</t>
   </si>
   <si>
     <t>14860000</t>
@@ -1346,25 +1331,25 @@
     <t>2101</t>
   </si>
   <si>
-    <t>Dichiarazione di morte: Decesso in abitazione o in luogo pubblico</t>
+    <t>Decesso in abitazione o in luogo pubblico</t>
   </si>
   <si>
     <t>2102</t>
   </si>
   <si>
-    <t>Dichiarazione di morte: Decesso in ospedale o casa di cura</t>
+    <t>Decesso in ospedale o casa di cura</t>
   </si>
   <si>
     <t>2103</t>
   </si>
   <si>
-    <t>Dichiarazione di morte: Decesso in caso di morte violenta</t>
+    <t>Decesso in caso di morte violenta</t>
   </si>
   <si>
     <t>2104</t>
   </si>
   <si>
-    <t>Dichiarazione di morte: Decesso relativo a cadavere rinvenuto non identificato</t>
+    <t>Decesso relativo a cadavere rinvenuto non identificato</t>
   </si>
   <si>
     <t>2105</t>
@@ -1388,25 +1373,25 @@
     <t>2199</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio dichiarazioni di morte</t>
+    <t>Caso d'uso di servizio (dichiarazioni di morte)</t>
   </si>
   <si>
     <t>2211</t>
   </si>
   <si>
-    <t>Trascrizione di morte: Decesso durante il viaggio in treno o aereo o nave</t>
+    <t>Decesso durante il viaggio in treno o aereo o nave</t>
   </si>
   <si>
     <t>2212</t>
   </si>
   <si>
-    <t>Trascrizione di morte: Richiesta trascrizione atto di morte all'estero richiesto da privati con istanza scritta</t>
+    <t>Richiesta trascrizione atto di morte all'estero richiesto da privati con istanza scritta</t>
   </si>
   <si>
     <t>2213</t>
   </si>
   <si>
-    <t>Trascrizione di morte: Richiesta trascrizione atto di morte all'estero richiesto da pubblica autorita'</t>
+    <t>Richiesta trascrizione atto di morte all'estero richiesto da pubblica autorita'</t>
   </si>
   <si>
     <t>2214</t>
@@ -1415,7 +1400,7 @@
     <t>Trascrizione atto morte su richiesta dell'interessato per art. 19</t>
   </si>
   <si>
-    <t>2024-06-25 00:00:00.0</t>
+    <t>2024-06-27 00:00:00.0</t>
   </si>
   <si>
     <t>2215</t>
@@ -1430,31 +1415,31 @@
     <t>Trascrizione atto di morte pervenuto da comune estero di decesso</t>
   </si>
   <si>
-    <t>2026-04-27 17:26:41.0</t>
+    <t>2026-05-04 10:32:03.0</t>
   </si>
   <si>
     <t>2221</t>
   </si>
   <si>
-    <t xml:space="preserve">Trascrizione di morte: Trascrizioni di sentenza dichiarazione di scomparsa per disastri aerei o a bordo di navi </t>
+    <t xml:space="preserve">Trascrizioni di sentenza dichiarazione di scomparsa per disastri aerei o a bordo di navi </t>
   </si>
   <si>
     <t>2222</t>
   </si>
   <si>
-    <t>Trascrizione di morte: Trascrizioni di sentenze estera di morte presunta o scomparsa o assenza richiesta da pubblica autorita'</t>
+    <t>Trascrizioni di sentenze estera di morte presunta o scomparsa o assenza richiesta da pubblica autorita'</t>
   </si>
   <si>
     <t>2223</t>
   </si>
   <si>
-    <t>Trascrizione di morte: Trascrizioni di sentenze estera di morte presunta o scomparsa o assenza richiesta da privato</t>
+    <t>Trascrizioni di sentenze estera di morte presunta o scomparsa o assenza richiesta da privato</t>
   </si>
   <si>
     <t>2224</t>
   </si>
   <si>
-    <t>Trascrizione di morte: Trascrizioni di sentenze di accertamento morte gia' dichiarata presunta</t>
+    <t>Trascrizioni di sentenze di accertamento morte gia' dichiarata presunta</t>
   </si>
   <si>
     <t>2225</t>
@@ -1466,7 +1451,7 @@
     <t>2299</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio trascrizioni di morte</t>
+    <t>Caso d'uso di servizio (trascrizioni di morte)</t>
   </si>
   <si>
     <t>2310</t>
@@ -1475,7 +1460,7 @@
     <t>2320</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio annotazione comunicazione da altre amministrazioni</t>
+    <t>Caso d'uso di servizio annotazione (comunicazione da altre amministrazioni)</t>
   </si>
   <si>
     <t>2341</t>
@@ -1496,7 +1481,7 @@
     <t>311111</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile nella casa comunale</t>
+    <t>Matrimonio con Rito Civile nella casa comunale</t>
   </si>
   <si>
     <t>311112</t>
@@ -1511,7 +1496,7 @@
     <t>311121</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile nella casa comunale con riconoscimento di uno o piu' figli</t>
+    <t>Matrimonio con Rito Civile nella casa comunale con riconoscimento di uno o piu' figli</t>
   </si>
   <si>
     <t>311122</t>
@@ -1523,73 +1508,85 @@
     <t>311211</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile fuori dalla casa comunale</t>
+    <t>Matrimonio con Rito Civile fuori dalla casa comunale</t>
   </si>
   <si>
     <t>311212</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile fuori dalla casa comunale in Imminente Pericolo di Vita</t>
+    <t>Matrimonio con Rito Civile fuori dalla casa comunale in Imminente Pericolo di Vita</t>
   </si>
   <si>
     <t>311221</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile fuori dalla casa comunale con Riconoscimento di uno o piu' figli</t>
+    <t>Matrimonio con Rito Civile fuori dalla casa comunale con Riconoscimento di uno o piu' figli</t>
   </si>
   <si>
     <t>311222</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile fuori dalla casa comunale in Imminente Pericolo di Vita con Riconoscimento di uno o piu' figli</t>
+    <t>Matrimonio con Rito Civile fuori dalla casa comunale in Imminente Pericolo di Vita con Riconoscimento di uno o piu' figli</t>
   </si>
   <si>
     <t>312111</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile con delega di altro Comune nella casa comunale</t>
+    <t>Matrimonio con Rito Civile con delega di altro Comune nella casa comunale</t>
   </si>
   <si>
     <t>312121</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile con Delega di altro Comune nella casa comunale con Riconoscimento di uno o piu' figli</t>
+    <t>Matrimonio con Rito Civile con Delega di altro Comune nella casa comunale con Riconoscimento di uno o piu' figli</t>
   </si>
   <si>
     <t>312211</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile con delega di altro Comune fuori dalla casa comunale</t>
+    <t>Matrimonio con Rito Civile con delega di altro Comune fuori dalla casa comunale</t>
   </si>
   <si>
     <t>312221</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Civile con Delega di altro Comune fuori dalla casa comunale con Riconoscimento di uno o piu' figli</t>
+    <t>Matrimonio con Rito Civile con Delega di altro Comune fuori dalla casa comunale con Riconoscimento di uno o piu' figli</t>
   </si>
   <si>
     <t>313111</t>
   </si>
   <si>
-    <t>Matrimonio con Rito Civile di stranieri non domiciliati nÃ© residenti</t>
+    <t>Matrimonio con Rito Civile di stranieri non domiciliati né residenti</t>
   </si>
   <si>
     <t>319999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio matrimoni con rito civile</t>
+    <t>Caso d'uso di servizio (matrimoni con rito civile)</t>
   </si>
   <si>
     <t>321311</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Religioso Cattolico</t>
+    <t>Matrimonio con Rito Religioso Cattolico</t>
+  </si>
+  <si>
+    <t>321321</t>
+  </si>
+  <si>
+    <t>Matrimonio con Rito Religioso Cattolico con Riconoscimento di uno o piu' figli</t>
   </si>
   <si>
     <t>321411</t>
   </si>
   <si>
-    <t>Dichiarazione: Matrimonio con Rito Religioso Acattolico</t>
+    <t>Matrimonio con Rito Religioso Acattolico</t>
+  </si>
+  <si>
+    <t>321421</t>
+  </si>
+  <si>
+    <t>Matrimonio con Rito Religioso Acattolico con riconoscimento di uno o piu' figli</t>
   </si>
   <si>
     <t>323111</t>
@@ -1601,13 +1598,13 @@
     <t>329999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio matrimoni con rito religioso</t>
+    <t>Caso d'uso di servizio (matrimoni con rito religioso)</t>
   </si>
   <si>
     <t>331000</t>
   </si>
   <si>
-    <t>Trascrizione matrimoni dall'estero - richiesta di trascrizione da parte dell'interessato</t>
+    <t xml:space="preserve">Trascrizione matrimoni dall'estero - richiesta di trascrizione da parte dell'interessato       </t>
   </si>
   <si>
     <t>332000</t>
@@ -1625,7 +1622,7 @@
     <t>334000</t>
   </si>
   <si>
-    <t>Trascrizione sentenze di Tribunali stranieri - richiesta di trascrizione da parte dell'interessato</t>
+    <t xml:space="preserve">Trascrizione sentenze di Tribunali stranieri - richiesta di trascrizione da parte dell'interessato       </t>
   </si>
   <si>
     <t>335003</t>
@@ -1640,55 +1637,55 @@
     <t>Trascrizione matrimoni dall'estero - Richiesta di trascrizione da parte dell'interessato art. 19</t>
   </si>
   <si>
-    <t>2024-03-25 00:00:00.0</t>
+    <t>2024-03-27 00:00:00.0</t>
   </si>
   <si>
     <t>339999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio trascrizioni matrimonio</t>
+    <t>Caso d'uso di servizio (trascrizioni matrimonio)</t>
   </si>
   <si>
     <t>341000</t>
   </si>
   <si>
-    <t xml:space="preserve">Separazioni e divorzi: Accordo di separazione personale dei coniugi </t>
+    <t xml:space="preserve">Accordo di separazione personale dei coniugi </t>
   </si>
   <si>
     <t>342000</t>
   </si>
   <si>
-    <t>Separazioni e divorzi: Accordo di scioglimento o di cessazione degli effetti civili del matrimonio divorzio</t>
+    <t>Accordo di scioglimento (o di cessazione degli effetti civili) del matrimonio (divorzio)</t>
   </si>
   <si>
     <t>343000</t>
   </si>
   <si>
-    <t>Separazioni e divorzi: Conferma di accordo di separazione o divorzio</t>
+    <t>Conferma di accordo di separazione o divorzio</t>
   </si>
   <si>
     <t>344000</t>
   </si>
   <si>
-    <t>Separazioni e divorzi: Accordo di modifica delle condizioni di separazione o divorzio</t>
+    <t>Accordo di modifica delle condizioni di separazione o divorzio</t>
   </si>
   <si>
     <t>345000</t>
   </si>
   <si>
-    <t>Separazioni e divorzi: Trascrizione della convenzione di negoziazione assistita ai sensi dell'art.6 Decreto-legge n.132/2014 convertito con Legge 10.11.2014 n.162</t>
+    <t>Trascrizione della convenzione di negoziazione assistita ai sensi dell'art.6 Decreto-legge n.132/2014 convertito con Legge 10.11.2014 n.162</t>
   </si>
   <si>
     <t>346000</t>
   </si>
   <si>
-    <t>Separazioni e divorzi: Trascrizione delle sentenze di deliberazione, da parte della Corte d'Appello, delle sentenze di nullita' del matrimonio pronunciate dai Tribunali Ecclesiastici</t>
+    <t>Trascrizione delle sentenze di deliberazione, da parte della Corte d'Appello, delle sentenze di nullita' del matrimonio pronunciate dai Tribunali Ecclesiastici</t>
   </si>
   <si>
     <t>347000</t>
   </si>
   <si>
-    <t>Separazioni e divorzi: Trascrizione provvedimenti esteri in materia matrimoniale.</t>
+    <t>Trascrizione provvedimenti esteri in materia matrimoniale.</t>
   </si>
   <si>
     <t>348000</t>
@@ -1703,19 +1700,19 @@
     <t>349999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio separazioni e divorzi</t>
+    <t>Caso d'uso di servizio (separazioni e divorzi)</t>
   </si>
   <si>
     <t>350000</t>
   </si>
   <si>
-    <t>Riconciliazione: Dichiarazione di riconciliazione</t>
+    <t>Dichiarazione di riconciliazione</t>
   </si>
   <si>
     <t>359999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio riconciliazioni</t>
+    <t>Caso d'uso di servizio (riconciliazioni)</t>
   </si>
   <si>
     <t>365699</t>
@@ -1748,43 +1745,43 @@
     <t>411111</t>
   </si>
   <si>
-    <t>Dichiarazione: Unione civile nella casa comunale</t>
+    <t>Unione civile nella casa comunale</t>
   </si>
   <si>
     <t>411211</t>
   </si>
   <si>
-    <t>Dichiarazione: Unione civile fuori dalla casa comunale</t>
+    <t>Unione civile fuori dalla casa comunale</t>
   </si>
   <si>
     <t>411212</t>
   </si>
   <si>
-    <t>Dichiarazione: Unione civile fuori dalla casa comunale in imminente pericolo di vita</t>
+    <t>Unione civile fuori dalla casa comunale in imminente pericolo di vita</t>
   </si>
   <si>
     <t>412111</t>
   </si>
   <si>
-    <t>Dichiarazione: Unione civile con delega di altro Comune nella casa comunale</t>
+    <t>Unione civile con delega di altro Comune nella casa comunale</t>
   </si>
   <si>
     <t>412211</t>
   </si>
   <si>
-    <t>Dichiarazione: Unione civile con delega di altro Comune fuori dalla casa comunale</t>
+    <t>Unione civile con delega di altro Comune fuori dalla casa comunale</t>
   </si>
   <si>
     <t>419999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio unioni civili</t>
+    <t>Caso d'uso di servizio (unioni civili)</t>
   </si>
   <si>
     <t>431000</t>
   </si>
   <si>
-    <t>Trascrizione unione civile dall'estero - richiesta di trascrizione da parte dell'interessato</t>
+    <t xml:space="preserve">Trascrizione unione civile dall'estero - richiesta di trascrizione da parte dell'interessato       </t>
   </si>
   <si>
     <t>432000</t>
@@ -1814,7 +1811,7 @@
     <t>439999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio trascrizioni unioni civili</t>
+    <t>Caso d'uso di servizio (trascrizioni unioni civili)</t>
   </si>
   <si>
     <t>441000</t>
@@ -1871,7 +1868,7 @@
     <t>449999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio scioglimenti</t>
+    <t>Caso d'uso di servizio (scioglimenti)</t>
   </si>
   <si>
     <t>456999</t>
@@ -1898,58 +1895,55 @@
     <t>Annotazione modificativa per cambio regime patrimoniale</t>
   </si>
   <si>
-    <t>2024-11-29 11:28:52.0</t>
-  </si>
-  <si>
     <t>50000000</t>
   </si>
   <si>
     <t>51101</t>
   </si>
   <si>
-    <t>Dichiarazione: Straniero o apolide, del quale il padre o la madre o uno dei ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto mediante prestazione del servizio militare per lo Stato italiano</t>
+    <t>Straniero o apolide, del quale il padre o la madre o uno dei ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto mediante prestazione del servizio militare per lo Stato italiano</t>
   </si>
   <si>
     <t>51102</t>
   </si>
   <si>
-    <t>Dichiarazione: Straniero o dall'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita, il quale, al raggiungimento della maggiore eta', risiede legalmente da almeno due anni nel territorio della Repubblica</t>
+    <t>Straniero o dall'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita, il quale, al raggiungimento della maggiore eta', risiede legalmente da almeno due anni nel territorio della Repubblica</t>
   </si>
   <si>
     <t>51103</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione: Straniero nato in Italia che vi abbia risieduto legalmente senza interruzioni fino alla maggiore eta' </t>
+    <t xml:space="preserve">Straniero nato in Italia che vi abbia risieduto legalmente senza interruzioni fino alla maggiore eta' </t>
   </si>
   <si>
     <t>51104</t>
   </si>
   <si>
-    <t>Dichiarazione: Straniero riconosciuto durante la maggiore eta' da cittadino italiano</t>
+    <t>Straniero riconosciuto durante la maggiore eta' da cittadino italiano</t>
   </si>
   <si>
     <t>51105</t>
   </si>
   <si>
-    <t>Dichiarazione: Acquisto automatico di cittadina straniera che si sposa con cittadino italiano fino al 27 aprile 1983</t>
+    <t>Acquisto automatico di cittadina straniera che si sposa con cittadino italiano fino al 27 aprile 1983</t>
   </si>
   <si>
     <t>51106</t>
   </si>
   <si>
-    <t>Dichiarazione: Prestazione di giuramento a seguito di decreto abile</t>
+    <t>Prestazione di giuramento a seguito di decreto (abile)</t>
   </si>
   <si>
     <t>51107</t>
   </si>
   <si>
-    <t>Dichiarazione: Prestazione di giuramento a seguito di decreto con impedimenti</t>
+    <t>Prestazione di giuramento a seguito di decreto (con impedimenti)</t>
   </si>
   <si>
     <t>51108</t>
   </si>
   <si>
-    <t>Dichiarazione: Straniero o dell'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto assunzione di pubblico impiego alle dipendenze dello Stato</t>
+    <t>Straniero o dell'apolide, del quale il padre o la madre o uno degli ascendenti in linea retta di secondo grado sono stati cittadini per nascita: acquisto assunzione di pubblico impiego alle dipendenze dello Stato</t>
   </si>
   <si>
     <t>51111</t>
@@ -1967,49 +1961,49 @@
     <t>51201</t>
   </si>
   <si>
-    <t>Dichiarazione: Rinuncia del maggiorenne che aveva acquistato la cittadinanza per convivenza con il genitore art. 14</t>
+    <t>Rinuncia del maggiorenne che aveva acquistato la cittadinanza per convivenza con il genitore art. 14</t>
   </si>
   <si>
     <t>51202</t>
   </si>
   <si>
-    <t>Dichiarazione: Revoca dell'adozione per il fatto dell'adottante, rinuncia espressa cittadinanza entro un anno dalla revoca adozione</t>
+    <t>Revoca dell'adozione per il fatto dell'adottante, rinuncia espressa cittadinanza entro un anno dalla revoca adozione</t>
   </si>
   <si>
     <t>51301</t>
   </si>
   <si>
-    <t>Dichiarazione: Dichiarazione fatta da chi, avendo perduto la cittadinanza italiana,intende riacquistarla mediante prestazione del servizio militare per lo stato italiano</t>
+    <t>Dichiarazione fatta da chi, avendo perduto la cittadinanza italiana,intende riacquistarla mediante prestazione del servizio militare per lo stato italiano</t>
   </si>
   <si>
     <t>51302</t>
   </si>
   <si>
-    <t>Dichiarazione: Dichiarazione fatta da chi, avendo perduto la cittadinanza italiana, intende riacquistarla per l'assunzione di pubblico impiego alle dipendenze dello Stato italiano</t>
+    <t>Dichiarazione fatta da chi, avendo perduto la cittadinanza italiana, intende riacquistarla per l'assunzione di pubblico impiego alle dipendenze dello Stato italiano</t>
   </si>
   <si>
     <t>51303</t>
   </si>
   <si>
-    <t>Dichiarazione: Riacquisto per residenza in Italia</t>
+    <t>Riacquisto per residenza in Italia</t>
   </si>
   <si>
     <t>51304</t>
   </si>
   <si>
-    <t>Dichiarazione: Riacquisto per abbandono dei servigi allo stato estero</t>
+    <t>Riacquisto per abbandono dei servigi allo stato estero</t>
   </si>
   <si>
     <t>51305</t>
   </si>
   <si>
-    <t>Dichiarazione: Rinuncia al riacquisto della cittadinaza entro un anno dalla richiesta di residenza</t>
+    <t>Rinuncia al riacquisto della cittadinaza entro un anno dalla richiesta di residenza</t>
   </si>
   <si>
     <t>51306</t>
   </si>
   <si>
-    <t>Dichiarazione: Donna che, avendo perduto, anteriormente al 1 gennaio 1948, la cittadinanza italiana per effetto di matrimonio con uno straniero o di mutamento di cittadinanza da parte del marito, intende riacquistarla</t>
+    <t>Donna che, avendo perduto, anteriormente al 1 gennaio 1948, la cittadinanza italiana per effetto di matrimonio con uno straniero o di mutamento di cittadinanza da parte del marito, intende riacquistarla</t>
   </si>
   <si>
     <t>51307</t>
@@ -2021,7 +2015,7 @@
     <t>51999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio dichiarazioni di cittadinanza</t>
+    <t>Caso d'uso di servizio (dichiarazioni di cittadinanza)</t>
   </si>
   <si>
     <t>52111</t>
@@ -2045,7 +2039,7 @@
     <t>52115</t>
   </si>
   <si>
-    <t>Acquisto automatico di cittadina straniera che si sposa con cittadino italiano fino al 27 aprile 1983</t>
+    <t>Acquisto automatico di cittadina straniera residente che si sposa con cittadino italiano fino al 27 aprile 1983</t>
   </si>
   <si>
     <t>52121</t>
@@ -2087,25 +2081,25 @@
     <t>52144</t>
   </si>
   <si>
-    <t>Attestazione di acquisto cittadinanza in seguito ad adozione in casi particolari di minorenne o maggiorenne (art. 44 l. 184/1983)</t>
+    <t>Attestazione di adozione non legittimante di minore o maggiorenne in casi particolari art. 44 l. 184/1983 o adozione nazionale art 25 l. 184/1983 e art. 35 comma 4</t>
   </si>
   <si>
     <t>52153</t>
   </si>
   <si>
-    <t>Trascrizione: Trascrizione del decreto per matrimonio-unione civile-naturalizzazione-presentazione cittadino</t>
+    <t>Trascrizione del decreto per matrimonio-unione civile-naturalizzazione-presentazione cittadino</t>
   </si>
   <si>
     <t>52154</t>
   </si>
   <si>
-    <t>Trascrizione: Trascrizione del decreto per matrimonio-unione civile-naturalizzazione-da consolato</t>
+    <t>Trascrizione del decreto per matrimonio-unione civile-naturalizzazione-da consolato</t>
   </si>
   <si>
     <t>52155</t>
   </si>
   <si>
-    <t>Acquisto di cittadinanza jure sanguinis per decreto di autorita' giudiziaria o amministrativa</t>
+    <t>Provvedimenti amministrativi di competenza dell'Autorita' consolare di riconoscimento della cittadinanza italiana jure sanguinis</t>
   </si>
   <si>
     <t>52156</t>
@@ -2123,91 +2117,76 @@
     <t>52211</t>
   </si>
   <si>
-    <t>Trascrizione: Reso servigi ad uno Stato estero</t>
+    <t>Reso servigi ad uno Stato estero</t>
   </si>
   <si>
     <t>52221</t>
   </si>
   <si>
-    <t>Trascrizione: Rinuncia del maggiorenne che aveva acquistato la cittadinanza per convivenza con il genitore art. 14</t>
-  </si>
-  <si>
     <t>52222</t>
   </si>
   <si>
-    <t>Trascrizione: Revoca dell'adozione per il fatto dell'adottante, rinuncia espressa cittadinanza entro un anno dalla revoca adozione</t>
-  </si>
-  <si>
     <t>52241</t>
   </si>
   <si>
-    <t>Trascrizione: Disconoscimento da parte del genitore italiano</t>
+    <t>Disconoscimento da parte del genitore italiano</t>
   </si>
   <si>
     <t>52242</t>
   </si>
   <si>
-    <t>Trascrizione: Perdita per naturalizzazione straniera</t>
+    <t>Perdita per naturalizzazione straniera</t>
   </si>
   <si>
     <t>52251</t>
   </si>
   <si>
-    <t>Trascrizione: Revoca: cittadinanza italiana acquisita ai sensi degli articoli  4, comma 2, 5 e 9, e' revocata in caso  di  condanna  definitiva  per  i reati previsti dall'articolo 407, comma 2, lettera  a,  n.  4,  del codice di procedura penale</t>
+    <t>Revoca: cittadinanza italiana acquisita ai sensi degli articoli  4, comma 2, 5 e 9, e' revocata in caso  di  condanna  definitiva  per  i reati previsti dall'articolo 407, comma 2, lettera  a),  n.  4),  del codice di procedura penale</t>
   </si>
   <si>
     <t>52261</t>
   </si>
   <si>
-    <t>Trascrizione: Rinuncia espressa</t>
+    <t>Rinuncia espressa</t>
   </si>
   <si>
     <t>52271</t>
   </si>
   <si>
-    <t>Trascrizione: Revoca dell'adozione per il fatto dell'adottato</t>
+    <t>Revoca dell'adozione per il fatto dell'adottato</t>
   </si>
   <si>
     <t>52311</t>
   </si>
   <si>
-    <t>Trascrizione: Esito dell'accertamento per chi avendo perduto la cittadinanza intende riacquistarla mediante prestazione del servizio militare per lo stato italiano</t>
+    <t>Esito dell'accertamento per chi avendo perduto la cittadinanza intende riacquistarla mediante prestazione del servizio militare per lo stato italiano</t>
   </si>
   <si>
     <t>52312</t>
   </si>
   <si>
-    <t>Trascrizione: Esito dell'accertamento per chi, avendo perduto la cittadinanza italiana, intende riacquistarla per l'assunzione di pubblico impiego alle dipendenze dello Stato italiano</t>
+    <t>Esito dell'accertamento per chi, avendo perduto la cittadinanza italiana, intende riacquistarla per l'assunzione di pubblico impiego alle dipendenze dello Stato italiano</t>
   </si>
   <si>
     <t>52321</t>
   </si>
   <si>
-    <t>Trascrizione: Riacquisto per residenza in Italia esito dell'accertamento</t>
+    <t>Riacquisto per residenza in Italia esito dell'accertamento</t>
   </si>
   <si>
     <t>52322</t>
   </si>
   <si>
-    <t>Trascrizione: Riacquisto per abbandono dei servigi allo stato estero</t>
-  </si>
-  <si>
     <t>52323</t>
   </si>
   <si>
-    <t>Trascrizione: Rinuncia al riacquisto della cittadinaza entro un anno dalla richiesta di residenza</t>
-  </si>
-  <si>
     <t>52324</t>
   </si>
   <si>
-    <t>Trascrizione: Donna che, avendo perduto, anteriormente al 1 gennaio 1948, la cittadinanza italiana per effetto di matrimonio con uno straniero o di mutamento di cittadinanza da parte del marito, intende riacquistarla</t>
-  </si>
-  <si>
     <t>52331</t>
   </si>
   <si>
-    <t>Trascrizione: Riacquisto per residenza in Italia, dichiarazione resa in Consolato italiano</t>
+    <t>Riacquisto per residenza in Italia, dichiarazione resa in Consolato italiano</t>
   </si>
   <si>
     <t>52332</t>
@@ -2219,7 +2198,7 @@
     <t>52341</t>
   </si>
   <si>
-    <t>Trascrizione: Riacquisto per un anno di residenza in Italia</t>
+    <t>Riacquisto per un anno di residenza in Italia</t>
   </si>
   <si>
     <t>52711</t>
@@ -2243,7 +2222,7 @@
     <t>52999</t>
   </si>
   <si>
-    <t>Caso d'uso di servizio trascrizioni di cittadinanza</t>
+    <t>Caso d'uso di servizio (trascrizioni di cittadinanza)</t>
   </si>
   <si>
     <t>53599</t>
@@ -4399,7 +4378,7 @@
         <v>218</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>219</v>
+        <v>148</v>
       </c>
       <c r="D104" s="2" t="s">
         <v>9</v>
@@ -4413,10 +4392,10 @@
     </row>
     <row r="105">
       <c r="A105" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="B105" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="B105" s="2" t="s">
-        <v>221</v>
       </c>
       <c r="C105" s="2" t="s">
         <v>8</v>
@@ -4433,10 +4412,10 @@
     </row>
     <row r="106">
       <c r="A106" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="B106" s="2" t="s">
         <v>222</v>
-      </c>
-      <c r="B106" s="2" t="s">
-        <v>223</v>
       </c>
       <c r="C106" s="2" t="s">
         <v>8</v>
@@ -4453,10 +4432,10 @@
     </row>
     <row r="107">
       <c r="A107" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="B107" s="2" t="s">
         <v>224</v>
-      </c>
-      <c r="B107" s="2" t="s">
-        <v>225</v>
       </c>
       <c r="C107" s="2" t="s">
         <v>8</v>
@@ -4473,10 +4452,10 @@
     </row>
     <row r="108">
       <c r="A108" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="B108" s="2" t="s">
         <v>226</v>
-      </c>
-      <c r="B108" s="2" t="s">
-        <v>227</v>
       </c>
       <c r="C108" s="2" t="s">
         <v>8</v>
@@ -4493,10 +4472,10 @@
     </row>
     <row r="109">
       <c r="A109" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="B109" s="2" t="s">
         <v>228</v>
-      </c>
-      <c r="B109" s="2" t="s">
-        <v>229</v>
       </c>
       <c r="C109" s="2" t="s">
         <v>8</v>
@@ -4513,10 +4492,10 @@
     </row>
     <row r="110">
       <c r="A110" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="B110" s="2" t="s">
         <v>230</v>
-      </c>
-      <c r="B110" s="2" t="s">
-        <v>231</v>
       </c>
       <c r="C110" s="2" t="s">
         <v>8</v>
@@ -4533,10 +4512,10 @@
     </row>
     <row r="111">
       <c r="A111" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="B111" s="2" t="s">
         <v>232</v>
-      </c>
-      <c r="B111" s="2" t="s">
-        <v>233</v>
       </c>
       <c r="C111" s="2" t="s">
         <v>8</v>
@@ -4553,10 +4532,10 @@
     </row>
     <row r="112">
       <c r="A112" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="B112" s="2" t="s">
         <v>234</v>
-      </c>
-      <c r="B112" s="2" t="s">
-        <v>235</v>
       </c>
       <c r="C112" s="2" t="s">
         <v>8</v>
@@ -4573,10 +4552,10 @@
     </row>
     <row r="113">
       <c r="A113" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="B113" s="2" t="s">
         <v>236</v>
-      </c>
-      <c r="B113" s="2" t="s">
-        <v>237</v>
       </c>
       <c r="C113" s="2" t="s">
         <v>8</v>
@@ -4593,10 +4572,10 @@
     </row>
     <row r="114">
       <c r="A114" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="B114" s="2" t="s">
         <v>238</v>
-      </c>
-      <c r="B114" s="2" t="s">
-        <v>239</v>
       </c>
       <c r="C114" s="2" t="s">
         <v>8</v>
@@ -4613,10 +4592,10 @@
     </row>
     <row r="115">
       <c r="A115" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="B115" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="B115" s="2" t="s">
-        <v>241</v>
       </c>
       <c r="C115" s="2" t="s">
         <v>8</v>
@@ -4633,10 +4612,10 @@
     </row>
     <row r="116">
       <c r="A116" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="B116" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="B116" s="2" t="s">
-        <v>243</v>
       </c>
       <c r="C116" s="2" t="s">
         <v>8</v>
@@ -4653,10 +4632,10 @@
     </row>
     <row r="117">
       <c r="A117" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="B117" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="B117" s="2" t="s">
-        <v>245</v>
       </c>
       <c r="C117" s="2" t="s">
         <v>8</v>
@@ -4673,10 +4652,10 @@
     </row>
     <row r="118">
       <c r="A118" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="B118" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="B118" s="2" t="s">
-        <v>247</v>
       </c>
       <c r="C118" s="2" t="s">
         <v>8</v>
@@ -4693,10 +4672,10 @@
     </row>
     <row r="119">
       <c r="A119" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="B119" s="2" t="s">
         <v>248</v>
-      </c>
-      <c r="B119" s="2" t="s">
-        <v>249</v>
       </c>
       <c r="C119" s="2" t="s">
         <v>8</v>
@@ -4713,10 +4692,10 @@
     </row>
     <row r="120">
       <c r="A120" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="B120" s="2" t="s">
         <v>250</v>
-      </c>
-      <c r="B120" s="2" t="s">
-        <v>251</v>
       </c>
       <c r="C120" s="2" t="s">
         <v>8</v>
@@ -4733,10 +4712,10 @@
     </row>
     <row r="121">
       <c r="A121" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="B121" s="2" t="s">
         <v>252</v>
-      </c>
-      <c r="B121" s="2" t="s">
-        <v>253</v>
       </c>
       <c r="C121" s="2" t="s">
         <v>8</v>
@@ -4753,10 +4732,10 @@
     </row>
     <row r="122">
       <c r="A122" s="2" t="s">
+        <v>253</v>
+      </c>
+      <c r="B122" s="2" t="s">
         <v>254</v>
-      </c>
-      <c r="B122" s="2" t="s">
-        <v>255</v>
       </c>
       <c r="C122" s="2" t="s">
         <v>8</v>
@@ -4773,10 +4752,10 @@
     </row>
     <row r="123">
       <c r="A123" s="2" t="s">
+        <v>255</v>
+      </c>
+      <c r="B123" s="2" t="s">
         <v>256</v>
-      </c>
-      <c r="B123" s="2" t="s">
-        <v>257</v>
       </c>
       <c r="C123" s="2" t="s">
         <v>8</v>
@@ -4793,10 +4772,10 @@
     </row>
     <row r="124">
       <c r="A124" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="B124" s="2" t="s">
         <v>258</v>
-      </c>
-      <c r="B124" s="2" t="s">
-        <v>259</v>
       </c>
       <c r="C124" s="2" t="s">
         <v>8</v>
@@ -4813,10 +4792,10 @@
     </row>
     <row r="125">
       <c r="A125" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="B125" s="2" t="s">
         <v>260</v>
-      </c>
-      <c r="B125" s="2" t="s">
-        <v>261</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>8</v>
@@ -4833,10 +4812,10 @@
     </row>
     <row r="126">
       <c r="A126" s="2" t="s">
+        <v>261</v>
+      </c>
+      <c r="B126" s="2" t="s">
         <v>262</v>
-      </c>
-      <c r="B126" s="2" t="s">
-        <v>263</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>8</v>
@@ -4853,10 +4832,10 @@
     </row>
     <row r="127">
       <c r="A127" s="2" t="s">
+        <v>263</v>
+      </c>
+      <c r="B127" s="2" t="s">
         <v>264</v>
-      </c>
-      <c r="B127" s="2" t="s">
-        <v>265</v>
       </c>
       <c r="C127" s="2" t="s">
         <v>8</v>
@@ -4873,10 +4852,10 @@
     </row>
     <row r="128">
       <c r="A128" s="2" t="s">
+        <v>265</v>
+      </c>
+      <c r="B128" s="2" t="s">
         <v>266</v>
-      </c>
-      <c r="B128" s="2" t="s">
-        <v>267</v>
       </c>
       <c r="C128" s="2" t="s">
         <v>8</v>
@@ -4893,10 +4872,10 @@
     </row>
     <row r="129">
       <c r="A129" s="2" t="s">
+        <v>267</v>
+      </c>
+      <c r="B129" s="2" t="s">
         <v>268</v>
-      </c>
-      <c r="B129" s="2" t="s">
-        <v>269</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>8</v>
@@ -4913,10 +4892,10 @@
     </row>
     <row r="130">
       <c r="A130" s="2" t="s">
+        <v>269</v>
+      </c>
+      <c r="B130" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="B130" s="2" t="s">
-        <v>271</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>8</v>
@@ -4933,10 +4912,10 @@
     </row>
     <row r="131">
       <c r="A131" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="B131" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="B131" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="C131" s="2" t="s">
         <v>8</v>
@@ -4953,10 +4932,10 @@
     </row>
     <row r="132">
       <c r="A132" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="B132" s="2" t="s">
         <v>274</v>
-      </c>
-      <c r="B132" s="2" t="s">
-        <v>275</v>
       </c>
       <c r="C132" s="2" t="s">
         <v>8</v>
@@ -4973,10 +4952,10 @@
     </row>
     <row r="133">
       <c r="A133" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="B133" s="2" t="s">
         <v>276</v>
-      </c>
-      <c r="B133" s="2" t="s">
-        <v>277</v>
       </c>
       <c r="C133" s="2" t="s">
         <v>8</v>
@@ -4993,10 +4972,10 @@
     </row>
     <row r="134">
       <c r="A134" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="B134" s="2" t="s">
         <v>278</v>
-      </c>
-      <c r="B134" s="2" t="s">
-        <v>279</v>
       </c>
       <c r="C134" s="2" t="s">
         <v>8</v>
@@ -5013,10 +4992,10 @@
     </row>
     <row r="135">
       <c r="A135" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="B135" s="2" t="s">
         <v>280</v>
-      </c>
-      <c r="B135" s="2" t="s">
-        <v>281</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>8</v>
@@ -5033,10 +5012,10 @@
     </row>
     <row r="136">
       <c r="A136" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="B136" s="2" t="s">
         <v>282</v>
-      </c>
-      <c r="B136" s="2" t="s">
-        <v>283</v>
       </c>
       <c r="C136" s="2" t="s">
         <v>8</v>
@@ -5053,10 +5032,10 @@
     </row>
     <row r="137">
       <c r="A137" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="B137" s="2" t="s">
         <v>284</v>
-      </c>
-      <c r="B137" s="2" t="s">
-        <v>285</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>8</v>
@@ -5073,10 +5052,10 @@
     </row>
     <row r="138">
       <c r="A138" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="B138" s="2" t="s">
         <v>286</v>
-      </c>
-      <c r="B138" s="2" t="s">
-        <v>287</v>
       </c>
       <c r="C138" s="2" t="s">
         <v>8</v>
@@ -5093,10 +5072,10 @@
     </row>
     <row r="139">
       <c r="A139" s="2" t="s">
+        <v>287</v>
+      </c>
+      <c r="B139" s="2" t="s">
         <v>288</v>
-      </c>
-      <c r="B139" s="2" t="s">
-        <v>289</v>
       </c>
       <c r="C139" s="2" t="s">
         <v>8</v>
@@ -5113,10 +5092,10 @@
     </row>
     <row r="140">
       <c r="A140" s="2" t="s">
+        <v>289</v>
+      </c>
+      <c r="B140" s="2" t="s">
         <v>290</v>
-      </c>
-      <c r="B140" s="2" t="s">
-        <v>291</v>
       </c>
       <c r="C140" s="2" t="s">
         <v>8</v>
@@ -5133,10 +5112,10 @@
     </row>
     <row r="141">
       <c r="A141" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="B141" s="2" t="s">
         <v>292</v>
-      </c>
-      <c r="B141" s="2" t="s">
-        <v>293</v>
       </c>
       <c r="C141" s="2" t="s">
         <v>8</v>
@@ -5153,10 +5132,10 @@
     </row>
     <row r="142">
       <c r="A142" s="2" t="s">
+        <v>293</v>
+      </c>
+      <c r="B142" s="2" t="s">
         <v>294</v>
-      </c>
-      <c r="B142" s="2" t="s">
-        <v>295</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>8</v>
@@ -5173,10 +5152,10 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
+        <v>295</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>296</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>297</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>8</v>
@@ -5193,10 +5172,10 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
+        <v>297</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>298</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>299</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>8</v>
@@ -5213,10 +5192,10 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
+        <v>299</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>300</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>301</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>8</v>
@@ -5233,10 +5212,10 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
+        <v>301</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>302</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>303</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>8</v>
@@ -5253,13 +5232,13 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
+        <v>303</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>305</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>306</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>9</v>
@@ -5273,10 +5252,10 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
+        <v>306</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>307</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>308</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>8</v>
@@ -5293,10 +5272,10 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
+        <v>308</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>309</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>310</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>8</v>
@@ -5313,10 +5292,10 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
+        <v>310</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>311</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>312</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>8</v>
@@ -5333,10 +5312,10 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>313</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>314</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>8</v>
@@ -5353,10 +5332,10 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
+        <v>314</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>315</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>316</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>8</v>
@@ -5373,10 +5352,10 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
+        <v>316</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>317</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>318</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>8</v>
@@ -5393,10 +5372,10 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
+        <v>318</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>319</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>320</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>8</v>
@@ -5413,13 +5392,13 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
+        <v>320</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>322</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>323</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -5433,10 +5412,10 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
+        <v>323</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>324</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>325</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>8</v>
@@ -5453,11 +5432,11 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
+        <v>325</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>327</v>
-      </c>
       <c r="C157" s="2" t="s">
         <v>8</v>
       </c>
@@ -5468,16 +5447,16 @@
         <v>10</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
+        <v>328</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>330</v>
-      </c>
       <c r="C158" s="2" t="s">
         <v>8</v>
       </c>
@@ -5488,16 +5467,16 @@
         <v>10</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
+        <v>330</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>332</v>
-      </c>
       <c r="C159" s="2" t="s">
         <v>8</v>
       </c>
@@ -5508,16 +5487,16 @@
         <v>10</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>334</v>
-      </c>
       <c r="C160" s="2" t="s">
         <v>8</v>
       </c>
@@ -5528,18 +5507,18 @@
         <v>10</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
+        <v>334</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>336</v>
-      </c>
       <c r="C161" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>9</v>
@@ -5548,18 +5527,18 @@
         <v>10</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
+        <v>336</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>338</v>
-      </c>
       <c r="C162" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>9</v>
@@ -5568,19 +5547,19 @@
         <v>10</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
+        <v>338</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>341</v>
-      </c>
       <c r="D163" s="2" t="s">
         <v>9</v>
       </c>
@@ -5588,16 +5567,16 @@
         <v>10</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
+        <v>341</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>343</v>
-      </c>
       <c r="C164" s="2" t="s">
         <v>8</v>
       </c>
@@ -5608,16 +5587,16 @@
         <v>10</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
+        <v>343</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>345</v>
-      </c>
       <c r="C165" s="2" t="s">
         <v>8</v>
       </c>
@@ -5628,16 +5607,16 @@
         <v>10</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
+        <v>345</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>347</v>
-      </c>
       <c r="C166" s="2" t="s">
         <v>8</v>
       </c>
@@ -5648,16 +5627,16 @@
         <v>10</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>349</v>
-      </c>
       <c r="C167" s="2" t="s">
         <v>8</v>
       </c>
@@ -5668,16 +5647,16 @@
         <v>10</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
+        <v>349</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>351</v>
-      </c>
       <c r="C168" s="2" t="s">
         <v>8</v>
       </c>
@@ -5688,16 +5667,16 @@
         <v>10</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
+        <v>351</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>353</v>
-      </c>
       <c r="C169" s="2" t="s">
         <v>8</v>
       </c>
@@ -5708,19 +5687,19 @@
         <v>10</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
+        <v>353</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="C170" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>356</v>
-      </c>
       <c r="D170" s="2" t="s">
         <v>9</v>
       </c>
@@ -5728,18 +5707,18 @@
         <v>10</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
+        <v>356</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>358</v>
-      </c>
       <c r="C171" s="2" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>9</v>
@@ -5748,18 +5727,18 @@
         <v>10</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>9</v>
@@ -5768,18 +5747,18 @@
         <v>10</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>9</v>
@@ -5788,15 +5767,15 @@
         <v>10</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="C174" s="2" t="s">
         <v>8</v>
@@ -5808,15 +5787,15 @@
         <v>10</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="C175" s="2" t="s">
         <v>8</v>
@@ -5828,15 +5807,15 @@
         <v>10</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C176" s="2" t="s">
         <v>8</v>
@@ -5848,15 +5827,15 @@
         <v>10</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="C177" s="2" t="s">
         <v>8</v>
@@ -5868,15 +5847,15 @@
         <v>10</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="C178" s="2" t="s">
         <v>8</v>
@@ -5888,15 +5867,15 @@
         <v>10</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C179" s="2" t="s">
         <v>8</v>
@@ -5908,15 +5887,15 @@
         <v>10</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
       <c r="C180" s="2" t="s">
         <v>8</v>
@@ -5928,15 +5907,15 @@
         <v>10</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="C181" s="2" t="s">
         <v>8</v>
@@ -5948,15 +5927,15 @@
         <v>10</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>381</v>
+        <v>379</v>
       </c>
       <c r="C182" s="2" t="s">
         <v>8</v>
@@ -5968,18 +5947,18 @@
         <v>10</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="B183" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="C183" s="2" t="s">
-        <v>384</v>
+        <v>355</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>9</v>
@@ -5988,18 +5967,18 @@
         <v>10</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
       <c r="B184" s="2" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="C184" s="2" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="D184" s="2" t="s">
         <v>9</v>
@@ -6008,15 +5987,15 @@
         <v>10</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
       <c r="B185" s="2" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C185" s="2" t="s">
         <v>8</v>
@@ -6028,15 +6007,15 @@
         <v>10</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>8</v>
@@ -6053,10 +6032,10 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="C187" s="2" t="s">
         <v>8</v>
@@ -6068,15 +6047,15 @@
         <v>10</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>8</v>
@@ -6093,10 +6072,10 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C189" s="2" t="s">
         <v>8</v>
@@ -6108,15 +6087,15 @@
         <v>10</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>8</v>
@@ -6133,10 +6112,10 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="C191" s="2" t="s">
         <v>8</v>
@@ -6148,18 +6127,18 @@
         <v>10</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
       <c r="D192" s="2" t="s">
         <v>9</v>
@@ -6168,7 +6147,7 @@
         <v>10</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="193">
@@ -6179,7 +6158,7 @@
         <v>403</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="D193" s="2" t="s">
         <v>9</v>
@@ -6188,18 +6167,18 @@
         <v>10</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>406</v>
+        <v>404</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>9</v>
@@ -6208,7 +6187,7 @@
         <v>10</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="195">
@@ -6219,7 +6198,7 @@
         <v>408</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>409</v>
+        <v>8</v>
       </c>
       <c r="D195" s="2" t="s">
         <v>9</v>
@@ -6228,27 +6207,27 @@
         <v>10</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="C196" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>411</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>409</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="197">
@@ -6268,7 +6247,7 @@
         <v>10</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>328</v>
+        <v>411</v>
       </c>
     </row>
     <row r="198">
@@ -6288,16 +6267,16 @@
         <v>10</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
+        <v>416</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>418</v>
-      </c>
       <c r="C199" s="2" t="s">
         <v>8</v>
       </c>
@@ -6308,19 +6287,19 @@
         <v>10</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
+        <v>418</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="C200" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="C200" s="2" t="s">
-        <v>8</v>
-      </c>
       <c r="D200" s="2" t="s">
         <v>9</v>
       </c>
@@ -6328,7 +6307,7 @@
         <v>10</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="201">
@@ -6339,7 +6318,7 @@
         <v>422</v>
       </c>
       <c r="C201" s="2" t="s">
-        <v>8</v>
+        <v>423</v>
       </c>
       <c r="D201" s="2" t="s">
         <v>9</v>
@@ -6348,18 +6327,18 @@
         <v>10</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B202" s="2" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C202" s="2" t="s">
-        <v>425</v>
+        <v>322</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>9</v>
@@ -6368,7 +6347,7 @@
         <v>10</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="203">
@@ -6379,7 +6358,7 @@
         <v>427</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>428</v>
+        <v>322</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>9</v>
@@ -6388,19 +6367,19 @@
         <v>10</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
+        <v>428</v>
+      </c>
+      <c r="B204" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="C204" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>323</v>
-      </c>
       <c r="D204" s="2" t="s">
         <v>9</v>
       </c>
@@ -6408,7 +6387,7 @@
         <v>10</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="205">
@@ -6419,7 +6398,7 @@
         <v>432</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>9</v>
@@ -6428,7 +6407,7 @@
         <v>10</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="206">
@@ -6439,7 +6418,7 @@
         <v>434</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>435</v>
+        <v>322</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>9</v>
@@ -6448,18 +6427,18 @@
         <v>10</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
+        <v>435</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>437</v>
-      </c>
       <c r="C207" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>9</v>
@@ -6468,18 +6447,18 @@
         <v>10</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>439</v>
+        <v>7</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D208" s="2" t="s">
         <v>9</v>
@@ -6488,18 +6467,18 @@
         <v>10</v>
       </c>
       <c r="F208" s="2" t="s">
-        <v>416</v>
+        <v>11</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>441</v>
+        <v>439</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D209" s="2" t="s">
         <v>9</v>
@@ -6508,15 +6487,15 @@
         <v>10</v>
       </c>
       <c r="F209" s="2" t="s">
-        <v>416</v>
+        <v>14</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
-        <v>442</v>
+        <v>440</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>7</v>
+        <v>441</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>8</v>
@@ -6528,15 +6507,15 @@
         <v>10</v>
       </c>
       <c r="F210" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
+        <v>442</v>
+      </c>
+      <c r="B211" s="2" t="s">
         <v>443</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>444</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>8</v>
@@ -6553,10 +6532,10 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
+        <v>444</v>
+      </c>
+      <c r="B212" s="2" t="s">
         <v>445</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>446</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>8</v>
@@ -6573,13 +6552,13 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
+        <v>446</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>448</v>
-      </c>
       <c r="C213" s="2" t="s">
-        <v>8</v>
+        <v>340</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>9</v>
@@ -6593,13 +6572,13 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>450</v>
-      </c>
       <c r="C214" s="2" t="s">
-        <v>8</v>
+        <v>340</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>9</v>
@@ -6613,13 +6592,13 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
+        <v>450</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>452</v>
-      </c>
       <c r="C215" s="2" t="s">
-        <v>341</v>
+        <v>322</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>9</v>
@@ -6633,13 +6612,13 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
+        <v>452</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="B216" s="2" t="s">
-        <v>454</v>
-      </c>
       <c r="C216" s="2" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>9</v>
@@ -6653,13 +6632,13 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
+        <v>454</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>456</v>
-      </c>
       <c r="C217" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>9</v>
@@ -6668,16 +6647,16 @@
         <v>10</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>14</v>
+        <v>327</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
+        <v>456</v>
+      </c>
+      <c r="B218" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>458</v>
-      </c>
       <c r="C218" s="2" t="s">
         <v>8</v>
       </c>
@@ -6688,16 +6667,16 @@
         <v>10</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>14</v>
+        <v>327</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
+        <v>458</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>460</v>
-      </c>
       <c r="C219" s="2" t="s">
         <v>8</v>
       </c>
@@ -6708,27 +6687,27 @@
         <v>10</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
+        <v>460</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="C220" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D220" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="C220" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E220" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="221">
@@ -6739,7 +6718,7 @@
         <v>464</v>
       </c>
       <c r="C221" s="2" t="s">
-        <v>8</v>
+        <v>340</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>9</v>
@@ -6748,7 +6727,7 @@
         <v>10</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="222">
@@ -6759,16 +6738,16 @@
         <v>466</v>
       </c>
       <c r="C222" s="2" t="s">
-        <v>323</v>
+        <v>467</v>
       </c>
       <c r="D222" s="2" t="s">
-        <v>467</v>
+        <v>9</v>
       </c>
       <c r="E222" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="223">
@@ -6779,7 +6758,7 @@
         <v>469</v>
       </c>
       <c r="C223" s="2" t="s">
-        <v>341</v>
+        <v>8</v>
       </c>
       <c r="D223" s="2" t="s">
         <v>9</v>
@@ -6788,7 +6767,7 @@
         <v>10</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="224">
@@ -6799,7 +6778,7 @@
         <v>471</v>
       </c>
       <c r="C224" s="2" t="s">
-        <v>472</v>
+        <v>8</v>
       </c>
       <c r="D224" s="2" t="s">
         <v>9</v>
@@ -6808,16 +6787,16 @@
         <v>10</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
+        <v>472</v>
+      </c>
+      <c r="B225" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>474</v>
-      </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
       </c>
@@ -6828,16 +6807,16 @@
         <v>10</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
+        <v>474</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>476</v>
-      </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
       </c>
@@ -6848,18 +6827,18 @@
         <v>10</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
+        <v>476</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>477</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>478</v>
-      </c>
       <c r="C227" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>9</v>
@@ -6868,16 +6847,16 @@
         <v>10</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>479</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>480</v>
-      </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
       </c>
@@ -6888,18 +6867,18 @@
         <v>10</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>9</v>
@@ -6908,15 +6887,15 @@
         <v>10</v>
       </c>
       <c r="F229" s="2" t="s">
-        <v>328</v>
+        <v>411</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C230" s="2" t="s">
         <v>8</v>
@@ -6928,12 +6907,12 @@
         <v>10</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>328</v>
+        <v>411</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="B231" s="2" t="s">
         <v>415</v>
@@ -6948,15 +6927,15 @@
         <v>10</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>487</v>
+        <v>417</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>8</v>
@@ -6968,18 +6947,18 @@
         <v>10</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>488</v>
+        <v>485</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>8</v>
+        <v>423</v>
       </c>
       <c r="D233" s="2" t="s">
         <v>9</v>
@@ -6988,18 +6967,18 @@
         <v>10</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>9</v>
@@ -7008,18 +6987,18 @@
         <v>10</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>427</v>
+        <v>7</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>428</v>
+        <v>8</v>
       </c>
       <c r="D235" s="2" t="s">
         <v>9</v>
@@ -7028,18 +7007,18 @@
         <v>10</v>
       </c>
       <c r="F235" s="2" t="s">
-        <v>416</v>
+        <v>11</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
-        <v>491</v>
+        <v>488</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>430</v>
+        <v>489</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D236" s="2" t="s">
         <v>9</v>
@@ -7048,27 +7027,27 @@
         <v>10</v>
       </c>
       <c r="F236" s="2" t="s">
-        <v>416</v>
+        <v>14</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="B237" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="C237" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D237" s="2" t="s">
         <v>492</v>
       </c>
-      <c r="B237" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>9</v>
-      </c>
       <c r="E237" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F237" s="2" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="238">
@@ -7099,10 +7078,10 @@
         <v>496</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>10</v>
@@ -7113,10 +7092,10 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>498</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>499</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>8</v>
@@ -7133,16 +7112,16 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="B241" s="2" t="s">
         <v>500</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>501</v>
-      </c>
       <c r="C241" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>497</v>
+        <v>9</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>10</v>
@@ -7153,10 +7132,10 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="B242" s="2" t="s">
         <v>502</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>503</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>8</v>
@@ -7173,10 +7152,10 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="B243" s="2" t="s">
         <v>504</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>505</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>8</v>
@@ -7193,10 +7172,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="B244" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>507</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>8</v>
@@ -7213,10 +7192,10 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="B245" s="2" t="s">
         <v>508</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>509</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>8</v>
@@ -7233,10 +7212,10 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
+        <v>509</v>
+      </c>
+      <c r="B246" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>8</v>
@@ -7253,10 +7232,10 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="B247" s="2" t="s">
         <v>512</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>513</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>8</v>
@@ -7273,13 +7252,13 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>515</v>
-      </c>
       <c r="C248" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>9</v>
@@ -7293,10 +7272,10 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="B249" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>517</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>8</v>
@@ -7313,13 +7292,13 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
+        <v>517</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>518</v>
       </c>
-      <c r="B250" s="2" t="s">
-        <v>519</v>
-      </c>
       <c r="C250" s="2" t="s">
-        <v>323</v>
+        <v>8</v>
       </c>
       <c r="D250" s="2" t="s">
         <v>9</v>
@@ -7333,11 +7312,11 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>520</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>521</v>
-      </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
       </c>
@@ -7348,15 +7327,15 @@
         <v>10</v>
       </c>
       <c r="F251" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
+        <v>521</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>522</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>523</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>8</v>
@@ -7373,11 +7352,11 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="B253" s="2" t="s">
-        <v>525</v>
-      </c>
       <c r="C253" s="2" t="s">
         <v>8</v>
       </c>
@@ -7388,18 +7367,18 @@
         <v>10</v>
       </c>
       <c r="F253" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="C254" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>9</v>
@@ -7413,13 +7392,13 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
+        <v>525</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>526</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>527</v>
-      </c>
       <c r="C255" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>9</v>
@@ -7433,10 +7412,10 @@
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -7453,11 +7432,11 @@
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>530</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>531</v>
-      </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
       </c>
@@ -7468,16 +7447,16 @@
         <v>10</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
+        <v>531</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>532</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>533</v>
-      </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
       </c>
@@ -7488,16 +7467,16 @@
         <v>10</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>535</v>
-      </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
       </c>
@@ -7508,16 +7487,16 @@
         <v>10</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>537</v>
-      </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
       </c>
@@ -7528,16 +7507,16 @@
         <v>10</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
+        <v>537</v>
+      </c>
+      <c r="B261" s="2" t="s">
         <v>538</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>539</v>
-      </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
       </c>
@@ -7548,19 +7527,19 @@
         <v>10</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="C262" s="2" t="s">
         <v>541</v>
       </c>
-      <c r="C262" s="2" t="s">
-        <v>542</v>
-      </c>
       <c r="D262" s="2" t="s">
         <v>9</v>
       </c>
@@ -7568,16 +7547,16 @@
         <v>10</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="B263" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>544</v>
-      </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
       </c>
@@ -7588,15 +7567,15 @@
         <v>10</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="B264" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -7613,10 +7592,10 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="B265" s="2" t="s">
         <v>547</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>548</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -7633,10 +7612,10 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>550</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -7653,10 +7632,10 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>551</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>552</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -7673,10 +7652,10 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
+        <v>552</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -7693,11 +7672,11 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
+        <v>554</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>555</v>
       </c>
-      <c r="B269" s="2" t="s">
-        <v>556</v>
-      </c>
       <c r="C269" s="2" t="s">
         <v>8</v>
       </c>
@@ -7708,16 +7687,16 @@
         <v>10</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
+        <v>556</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>558</v>
-      </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
       </c>
@@ -7728,21 +7707,21 @@
         <v>10</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>559</v>
       </c>
-      <c r="B271" s="2" t="s">
+      <c r="C271" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="D271" s="2" t="s">
         <v>560</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>561</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>10</v>
@@ -7753,10 +7732,10 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
+        <v>561</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -7773,10 +7752,10 @@
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="B273" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>8</v>
@@ -7793,10 +7772,10 @@
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>566</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>567</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -7813,13 +7792,13 @@
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
+        <v>567</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="B275" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="C275" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
@@ -7828,15 +7807,15 @@
         <v>10</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>8</v>
@@ -7848,15 +7827,15 @@
         <v>10</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>8</v>
@@ -7868,15 +7847,15 @@
         <v>10</v>
       </c>
       <c r="F277" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>8</v>
@@ -7888,15 +7867,15 @@
         <v>10</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>8</v>
@@ -7908,18 +7887,18 @@
         <v>10</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>9</v>
@@ -7928,18 +7907,18 @@
         <v>10</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>9</v>
@@ -7948,12 +7927,12 @@
         <v>10</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>7</v>
@@ -7973,10 +7952,10 @@
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
+        <v>576</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="B283" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>8</v>
@@ -7993,10 +7972,10 @@
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -8013,10 +7992,10 @@
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -8033,10 +8012,10 @@
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -8053,10 +8032,10 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B287" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -8073,10 +8052,10 @@
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -8093,11 +8072,11 @@
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="B289" s="2" t="s">
-        <v>590</v>
-      </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
       </c>
@@ -8108,16 +8087,16 @@
         <v>10</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>592</v>
-      </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
       </c>
@@ -8128,16 +8107,16 @@
         <v>10</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
       </c>
@@ -8148,16 +8127,16 @@
         <v>10</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B292" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B292" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
       </c>
@@ -8168,18 +8147,18 @@
         <v>10</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B293" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>598</v>
-      </c>
       <c r="C293" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>9</v>
@@ -8188,16 +8167,16 @@
         <v>10</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>600</v>
-      </c>
       <c r="C294" s="2" t="s">
         <v>8</v>
       </c>
@@ -8208,15 +8187,15 @@
         <v>10</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>601</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>602</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>8</v>
@@ -8233,10 +8212,10 @@
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>603</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>604</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -8253,10 +8232,10 @@
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -8273,10 +8252,10 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -8293,10 +8272,10 @@
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B299" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -8313,13 +8292,13 @@
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>611</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>612</v>
-      </c>
       <c r="C300" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>9</v>
@@ -8333,13 +8312,13 @@
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>613</v>
       </c>
-      <c r="B301" s="2" t="s">
-        <v>614</v>
-      </c>
       <c r="C301" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>9</v>
@@ -8348,19 +8327,19 @@
         <v>10</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="B302" s="2" t="s">
+      <c r="C302" s="2" t="s">
         <v>616</v>
       </c>
-      <c r="C302" s="2" t="s">
-        <v>617</v>
-      </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
       </c>
@@ -8368,15 +8347,15 @@
         <v>10</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
+        <v>617</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>618</v>
-      </c>
-      <c r="B303" s="2" t="s">
-        <v>619</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>8</v>
@@ -8393,10 +8372,10 @@
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C304" s="2" t="s">
         <v>8</v>
@@ -8408,15 +8387,15 @@
         <v>10</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -8428,15 +8407,15 @@
         <v>10</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>8</v>
@@ -8448,15 +8427,15 @@
         <v>10</v>
       </c>
       <c r="F306" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>8</v>
@@ -8468,18 +8447,18 @@
         <v>10</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>9</v>
@@ -8488,18 +8467,18 @@
         <v>10</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>9</v>
@@ -8508,18 +8487,18 @@
         <v>10</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="B310" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="B310" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="C310" s="2" t="s">
-        <v>628</v>
+        <v>355</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>9</v>
@@ -8528,12 +8507,12 @@
         <v>10</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="B311" s="2" t="s">
         <v>7</v>
@@ -8553,10 +8532,10 @@
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="C312" s="2" t="s">
         <v>8</v>
@@ -8573,10 +8552,10 @@
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C313" s="2" t="s">
         <v>8</v>
@@ -8593,10 +8572,10 @@
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>8</v>
@@ -8613,10 +8592,10 @@
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -8633,10 +8612,10 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -8653,10 +8632,10 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -8673,10 +8652,10 @@
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>8</v>
@@ -8693,10 +8672,10 @@
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>8</v>
@@ -8713,13 +8692,13 @@
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>9</v>
@@ -8733,13 +8712,13 @@
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>9</v>
@@ -8753,10 +8732,10 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -8773,10 +8752,10 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="C323" s="2" t="s">
         <v>8</v>
@@ -8793,10 +8772,10 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C324" s="2" t="s">
         <v>8</v>
@@ -8813,10 +8792,10 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -8833,10 +8812,10 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -8853,10 +8832,10 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -8873,10 +8852,10 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>8</v>
@@ -8893,10 +8872,10 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -8913,13 +8892,13 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>9</v>
@@ -8933,10 +8912,10 @@
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -8953,10 +8932,10 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -8968,15 +8947,15 @@
         <v>10</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="C333" s="2" t="s">
         <v>8</v>
@@ -8988,15 +8967,15 @@
         <v>10</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -9008,18 +8987,18 @@
         <v>10</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>9</v>
@@ -9028,15 +9007,15 @@
         <v>10</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
@@ -9048,15 +9027,15 @@
         <v>10</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -9068,15 +9047,15 @@
         <v>10</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="C338" s="2" t="s">
         <v>8</v>
@@ -9088,15 +9067,15 @@
         <v>10</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -9108,15 +9087,15 @@
         <v>10</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
@@ -9128,15 +9107,15 @@
         <v>10</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
@@ -9148,18 +9127,18 @@
         <v>10</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -9168,15 +9147,15 @@
         <v>10</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>8</v>
@@ -9188,15 +9167,15 @@
         <v>10</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>8</v>
@@ -9208,18 +9187,18 @@
         <v>10</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>9</v>
@@ -9228,18 +9207,18 @@
         <v>10</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>9</v>
@@ -9248,18 +9227,18 @@
         <v>10</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>9</v>
@@ -9268,15 +9247,15 @@
         <v>10</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C348" s="2" t="s">
         <v>8</v>
@@ -9288,15 +9267,15 @@
         <v>10</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>705</v>
+        <v>649</v>
       </c>
       <c r="C349" s="2" t="s">
         <v>8</v>
@@ -9308,15 +9287,15 @@
         <v>10</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>707</v>
+        <v>651</v>
       </c>
       <c r="C350" s="2" t="s">
         <v>8</v>
@@ -9328,15 +9307,15 @@
         <v>10</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>708</v>
+        <v>704</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>709</v>
+        <v>705</v>
       </c>
       <c r="C351" s="2" t="s">
         <v>8</v>
@@ -9348,15 +9327,15 @@
         <v>10</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>710</v>
+        <v>706</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>711</v>
+        <v>707</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
@@ -9368,15 +9347,15 @@
         <v>10</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>712</v>
+        <v>708</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>713</v>
+        <v>709</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -9388,15 +9367,15 @@
         <v>10</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>714</v>
+        <v>710</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -9408,15 +9387,15 @@
         <v>10</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
@@ -9428,15 +9407,15 @@
         <v>10</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>719</v>
+        <v>715</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
@@ -9448,15 +9427,15 @@
         <v>10</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>720</v>
+        <v>716</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -9468,15 +9447,15 @@
         <v>10</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>723</v>
+        <v>719</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
@@ -9488,15 +9467,15 @@
         <v>10</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>724</v>
+        <v>720</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>725</v>
+        <v>659</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -9508,15 +9487,15 @@
         <v>10</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>727</v>
+        <v>661</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
@@ -9528,15 +9507,15 @@
         <v>10</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>729</v>
+        <v>663</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>8</v>
@@ -9548,15 +9527,15 @@
         <v>10</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -9568,18 +9547,18 @@
         <v>10</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>732</v>
+        <v>725</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>733</v>
+        <v>726</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>9</v>
@@ -9588,15 +9567,15 @@
         <v>10</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>734</v>
+        <v>727</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>8</v>
@@ -9608,18 +9587,18 @@
         <v>10</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>737</v>
+        <v>730</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>9</v>
@@ -9628,18 +9607,18 @@
         <v>10</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>739</v>
+        <v>732</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>9</v>
@@ -9648,18 +9627,18 @@
         <v>10</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>409</v>
+        <v>404</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>9</v>
@@ -9668,15 +9647,15 @@
         <v>10</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
@@ -9688,15 +9667,15 @@
         <v>10</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>744</v>
+        <v>737</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C369" s="2" t="s">
         <v>8</v>
@@ -9708,15 +9687,15 @@
         <v>10</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>745</v>
+        <v>738</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>487</v>
+        <v>482</v>
       </c>
       <c r="C370" s="2" t="s">
         <v>8</v>
@@ -9728,15 +9707,15 @@
         <v>10</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>746</v>
+        <v>739</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>420</v>
+        <v>415</v>
       </c>
       <c r="C371" s="2" t="s">
         <v>8</v>
@@ -9748,15 +9727,15 @@
         <v>10</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>747</v>
+        <v>740</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>8</v>
@@ -9768,18 +9747,18 @@
         <v>10</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>748</v>
+        <v>741</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>427</v>
+        <v>422</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>428</v>
+        <v>423</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>9</v>
@@ -9788,18 +9767,18 @@
         <v>10</v>
       </c>
       <c r="F373" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>749</v>
+        <v>742</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D374" s="2" t="s">
         <v>9</v>
@@ -9808,7 +9787,7 @@
         <v>10</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>416</v>
+        <v>411</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2244" uniqueCount="743">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="753">
   <si>
     <t>ID</t>
   </si>
@@ -1715,6 +1715,15 @@
     <t>Caso d'uso di servizio (riconciliazioni)</t>
   </si>
   <si>
+    <t>364000</t>
+  </si>
+  <si>
+    <t>Annotazione di convenzioni matrimoniali</t>
+  </si>
+  <si>
+    <t>2026-05-01 00:00:00.0</t>
+  </si>
+  <si>
     <t>365699</t>
   </si>
   <si>
@@ -1808,6 +1817,12 @@
     <t>Trascrizione atto unione civile su richiesta dell'interessato per art. 19</t>
   </si>
   <si>
+    <t>438100</t>
+  </si>
+  <si>
+    <t>Unione Civile tra persone dello stesso sesso (art. 134-bis, comma 2)</t>
+  </si>
+  <si>
     <t>439999</t>
   </si>
   <si>
@@ -1895,6 +1910,12 @@
     <t>Annotazione modificativa per cambio regime patrimoniale</t>
   </si>
   <si>
+    <t>461000</t>
+  </si>
+  <si>
+    <t>Scelta cognome comune</t>
+  </si>
+  <si>
     <t>50000000</t>
   </si>
   <si>
@@ -2112,6 +2133,15 @@
   </si>
   <si>
     <t>Esito negativo di accertamento cittadinanza</t>
+  </si>
+  <si>
+    <t>52158</t>
+  </si>
+  <si>
+    <t>Trascrizione esito accertamento da Consolato</t>
+  </si>
+  <si>
+    <t>2026-06-04 09:38:38.0</t>
   </si>
   <si>
     <t>52211</t>
@@ -2299,7 +2329,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G374"/>
+  <dimension ref="A1:G378"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="9.95703125" customWidth="true" bestFit="true"/>
@@ -7798,7 +7828,7 @@
         <v>568</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>322</v>
+        <v>569</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
@@ -7812,13 +7842,13 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>410</v>
+        <v>571</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>9</v>
@@ -7832,10 +7862,10 @@
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>482</v>
+        <v>410</v>
       </c>
       <c r="C277" s="2" t="s">
         <v>8</v>
@@ -7852,10 +7882,10 @@
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>415</v>
+        <v>482</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>8</v>
@@ -7872,10 +7902,10 @@
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>8</v>
@@ -7892,13 +7922,13 @@
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>422</v>
+        <v>417</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>423</v>
+        <v>8</v>
       </c>
       <c r="D280" s="2" t="s">
         <v>9</v>
@@ -7912,13 +7942,13 @@
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>322</v>
+        <v>423</v>
       </c>
       <c r="D281" s="2" t="s">
         <v>9</v>
@@ -7932,13 +7962,13 @@
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>7</v>
+        <v>425</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>9</v>
@@ -7947,15 +7977,15 @@
         <v>10</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>11</v>
+        <v>411</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>577</v>
+        <v>7</v>
       </c>
       <c r="C283" s="2" t="s">
         <v>8</v>
@@ -7967,15 +7997,15 @@
         <v>10</v>
       </c>
       <c r="F283" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -7992,10 +8022,10 @@
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -8012,10 +8042,10 @@
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -8032,10 +8062,10 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -8052,10 +8082,10 @@
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -8072,10 +8102,10 @@
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -8087,15 +8117,15 @@
         <v>10</v>
       </c>
       <c r="F289" s="2" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
@@ -8112,10 +8142,10 @@
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
@@ -8132,10 +8162,10 @@
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
@@ -8152,13 +8182,13 @@
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="D293" s="2" t="s">
         <v>9</v>
@@ -8172,13 +8202,13 @@
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>9</v>
@@ -8192,13 +8222,13 @@
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>9</v>
@@ -8207,15 +8237,15 @@
         <v>10</v>
       </c>
       <c r="F295" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -8227,15 +8257,15 @@
         <v>10</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>14</v>
+        <v>327</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -8252,10 +8282,10 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -8272,10 +8302,10 @@
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -8292,13 +8322,13 @@
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="D300" s="2" t="s">
         <v>9</v>
@@ -8312,13 +8342,13 @@
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>340</v>
+        <v>8</v>
       </c>
       <c r="D301" s="2" t="s">
         <v>9</v>
@@ -8327,18 +8357,18 @@
         <v>10</v>
       </c>
       <c r="F301" s="2" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>616</v>
+        <v>322</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
@@ -8347,7 +8377,7 @@
         <v>10</v>
       </c>
       <c r="F302" s="2" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
     </row>
     <row r="303">
@@ -8358,7 +8388,7 @@
         <v>618</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>8</v>
+        <v>340</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>9</v>
@@ -8367,7 +8397,7 @@
         <v>10</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>14</v>
+        <v>327</v>
       </c>
     </row>
     <row r="304">
@@ -8375,10 +8405,10 @@
         <v>619</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>410</v>
+        <v>620</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>8</v>
+        <v>621</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>9</v>
@@ -8387,15 +8417,15 @@
         <v>10</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>411</v>
+        <v>327</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>482</v>
+        <v>623</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -8407,15 +8437,15 @@
         <v>10</v>
       </c>
       <c r="F305" s="2" t="s">
-        <v>411</v>
+        <v>14</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>415</v>
+        <v>410</v>
       </c>
       <c r="C306" s="2" t="s">
         <v>8</v>
@@ -8432,10 +8462,10 @@
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>417</v>
+        <v>482</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>8</v>
@@ -8452,13 +8482,13 @@
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>422</v>
+        <v>415</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>423</v>
+        <v>8</v>
       </c>
       <c r="D308" s="2" t="s">
         <v>9</v>
@@ -8472,13 +8502,13 @@
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>425</v>
+        <v>417</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="D309" s="2" t="s">
         <v>9</v>
@@ -8492,13 +8522,13 @@
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>626</v>
+        <v>422</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>355</v>
+        <v>423</v>
       </c>
       <c r="D310" s="2" t="s">
         <v>9</v>
@@ -8512,13 +8542,13 @@
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>7</v>
+        <v>425</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>9</v>
@@ -8527,18 +8557,18 @@
         <v>10</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>11</v>
+        <v>411</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>8</v>
+        <v>355</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>9</v>
@@ -8547,18 +8577,18 @@
         <v>10</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>14</v>
+        <v>411</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>9</v>
@@ -8567,15 +8597,15 @@
         <v>10</v>
       </c>
       <c r="F313" s="2" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>633</v>
+        <v>7</v>
       </c>
       <c r="C314" s="2" t="s">
         <v>8</v>
@@ -8587,15 +8617,15 @@
         <v>10</v>
       </c>
       <c r="F314" s="2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -8612,10 +8642,10 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -8632,10 +8662,10 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -8652,10 +8682,10 @@
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>8</v>
@@ -8672,10 +8702,10 @@
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>8</v>
@@ -8692,13 +8722,13 @@
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="D320" s="2" t="s">
         <v>9</v>
@@ -8712,13 +8742,13 @@
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="D321" s="2" t="s">
         <v>9</v>
@@ -8732,10 +8762,10 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -8752,13 +8782,13 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>9</v>
@@ -8772,13 +8802,13 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>9</v>
@@ -8792,10 +8822,10 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -8812,10 +8842,10 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -8832,10 +8862,10 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -8852,10 +8882,10 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>8</v>
@@ -8872,10 +8902,10 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -8892,13 +8922,13 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="D330" s="2" t="s">
         <v>9</v>
@@ -8912,10 +8942,10 @@
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -8932,10 +8962,10 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -8947,18 +8977,18 @@
         <v>10</v>
       </c>
       <c r="F332" s="2" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>9</v>
@@ -8967,15 +8997,15 @@
         <v>10</v>
       </c>
       <c r="F333" s="2" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -8987,18 +9017,18 @@
         <v>10</v>
       </c>
       <c r="F334" s="2" t="s">
-        <v>327</v>
+        <v>14</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="D335" s="2" t="s">
         <v>9</v>
@@ -9012,10 +9042,10 @@
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
@@ -9032,10 +9062,10 @@
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
@@ -9052,13 +9082,13 @@
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>9</v>
@@ -9072,10 +9102,10 @@
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
@@ -9092,10 +9122,10 @@
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
@@ -9112,10 +9142,10 @@
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
@@ -9132,13 +9162,13 @@
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="D342" s="2" t="s">
         <v>9</v>
@@ -9152,10 +9182,10 @@
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C343" s="2" t="s">
         <v>8</v>
@@ -9172,10 +9202,10 @@
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C344" s="2" t="s">
         <v>8</v>
@@ -9192,13 +9222,13 @@
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>340</v>
+        <v>305</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>9</v>
@@ -9212,13 +9242,13 @@
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>322</v>
+        <v>8</v>
       </c>
       <c r="D346" s="2" t="s">
         <v>9</v>
@@ -9232,13 +9262,13 @@
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="D347" s="2" t="s">
         <v>9</v>
@@ -9252,13 +9282,13 @@
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>8</v>
+        <v>340</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>9</v>
@@ -9272,13 +9302,13 @@
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>649</v>
+        <v>704</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>8</v>
+        <v>322</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>9</v>
@@ -9292,13 +9322,13 @@
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>651</v>
+        <v>706</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>9</v>
@@ -9312,13 +9342,13 @@
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>8</v>
+        <v>709</v>
       </c>
       <c r="D351" s="2" t="s">
         <v>9</v>
@@ -9332,10 +9362,10 @@
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
@@ -9352,10 +9382,10 @@
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>709</v>
+        <v>656</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -9372,10 +9402,10 @@
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>711</v>
+        <v>658</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -9392,10 +9422,10 @@
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
@@ -9412,10 +9442,10 @@
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
@@ -9432,10 +9462,10 @@
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
@@ -9452,10 +9482,10 @@
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
@@ -9472,10 +9502,10 @@
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>659</v>
+        <v>723</v>
       </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
@@ -9492,10 +9522,10 @@
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>661</v>
+        <v>725</v>
       </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
@@ -9512,10 +9542,10 @@
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>663</v>
+        <v>727</v>
       </c>
       <c r="C361" s="2" t="s">
         <v>8</v>
@@ -9532,10 +9562,10 @@
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
-        <v>723</v>
+        <v>728</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>724</v>
+        <v>729</v>
       </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
@@ -9552,13 +9582,13 @@
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>725</v>
+        <v>730</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>726</v>
+        <v>666</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="D363" s="2" t="s">
         <v>9</v>
@@ -9572,10 +9602,10 @@
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>728</v>
+        <v>668</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>8</v>
@@ -9592,13 +9622,13 @@
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>730</v>
+        <v>670</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="D365" s="2" t="s">
         <v>9</v>
@@ -9612,13 +9642,13 @@
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>305</v>
+        <v>8</v>
       </c>
       <c r="D366" s="2" t="s">
         <v>9</v>
@@ -9632,13 +9662,13 @@
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>404</v>
+        <v>305</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>9</v>
@@ -9652,10 +9682,10 @@
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
@@ -9672,13 +9702,13 @@
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>410</v>
+        <v>740</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>9</v>
@@ -9687,18 +9717,18 @@
         <v>10</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>411</v>
+        <v>327</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>482</v>
+        <v>742</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>8</v>
+        <v>305</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>9</v>
@@ -9707,18 +9737,18 @@
         <v>10</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>411</v>
+        <v>327</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>415</v>
+        <v>744</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>8</v>
+        <v>404</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>9</v>
@@ -9727,15 +9757,15 @@
         <v>10</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>411</v>
+        <v>327</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
-        <v>740</v>
+        <v>745</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>417</v>
+        <v>746</v>
       </c>
       <c r="C372" s="2" t="s">
         <v>8</v>
@@ -9747,18 +9777,18 @@
         <v>10</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>411</v>
+        <v>327</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>741</v>
+        <v>747</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>422</v>
+        <v>410</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>423</v>
+        <v>8</v>
       </c>
       <c r="D373" s="2" t="s">
         <v>9</v>
@@ -9772,21 +9802,101 @@
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>742</v>
+        <v>748</v>
       </c>
       <c r="B374" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D374" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E374" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F374" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D375" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E375" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F375" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="2" t="s">
+        <v>750</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D376" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E376" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F376" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="2" t="s">
+        <v>751</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>422</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="D377" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E377" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F377" s="2" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="B378" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="C374" s="2" t="s">
+      <c r="C378" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="D374" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E374" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F374" s="2" t="s">
+      <c r="D378" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E378" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F378" s="2" t="s">
         <v>411</v>
       </c>
     </row>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2268" uniqueCount="752">
   <si>
     <t>ID</t>
   </si>
@@ -353,7 +353,7 @@
     <t>11212003</t>
   </si>
   <si>
-    <t>Dichiarazione entro i 10 giorni - resa dalla madre con il consenso del padre reso mediante atto notarile - filiazione fuori dal matrimonio</t>
+    <t>Dichiarazione entro i 10 giorni - resa dalla madre con il consenso del padre o altro genitore reso mediante atto notarile - filiazione fuori dal matrimonio</t>
   </si>
   <si>
     <t>11212102</t>
@@ -365,7 +365,7 @@
     <t>11212103</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con consenso paterno espresso con atto notarile di bimbo nato morto </t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con consenso paterno o di altro genitore espresso con atto notarile di bimbo nato morto</t>
   </si>
   <si>
     <t>11212202</t>
@@ -377,7 +377,7 @@
     <t>11212203</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con consenso paterno espresso con atto notarile di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa allUSC dalla madre con consenso paterno o di altro genitore espresso con atto notarile di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11213000</t>
@@ -419,19 +419,19 @@
     <t>11216000</t>
   </si>
   <si>
-    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre o altro genitore</t>
   </si>
   <si>
     <t>11216100</t>
   </si>
   <si>
-    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato morto</t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre o altro genitore di bimbo nato morto</t>
   </si>
   <si>
     <t>11216200</t>
   </si>
   <si>
-    <t xml:space="preserve">Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato vivo ma morto prima della denuncia di nascita </t>
+    <t>Dichiarazione nei termini di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre o altro genitore di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11217000</t>
@@ -536,7 +536,7 @@
     <t>11222003</t>
   </si>
   <si>
-    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno espresso con atto notarile</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno o di altro genitore espresso con atto notarile</t>
   </si>
   <si>
     <t>11222102</t>
@@ -548,7 +548,7 @@
     <t>11222103</t>
   </si>
   <si>
-    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno o di altro genitore di bimbo nato morto</t>
   </si>
   <si>
     <t>11222202</t>
@@ -560,7 +560,7 @@
     <t>11222203</t>
   </si>
   <si>
-    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con il consenso paterno o di altro genitore di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11223000</t>
@@ -602,19 +602,19 @@
     <t>11226000</t>
   </si>
   <si>
-    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre o altro genitore</t>
   </si>
   <si>
     <t>11226100</t>
   </si>
   <si>
-    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato morto</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre o altro genitore di bimbo nato morto</t>
   </si>
   <si>
     <t>11226200</t>
   </si>
   <si>
-    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre di bimbo nato vivo ma morto prima della denuncia di nascita</t>
+    <t>Dichiarazione tardiva di filiazione fuori dal matrimonio resa all'USC dalla madre con presenza padre o altro genitore di bimbo nato vivo ma morto prima della denuncia di nascita</t>
   </si>
   <si>
     <t>11227000</t>
@@ -860,19 +860,19 @@
     <t>12214300</t>
   </si>
   <si>
-    <t>Riconoscimento di nascituro da parte del padre con presenza della madre</t>
+    <t>Riconoscimento di nascituro da parte del padre o di altro genitore con presenza della madre</t>
   </si>
   <si>
     <t>12216300</t>
   </si>
   <si>
-    <t>Riconoscimento di nascituro da parte della madre con presenza del padre</t>
+    <t>Riconoscimento di nascituro da parte della madre con presenza del padre o di altro genitore</t>
   </si>
   <si>
     <t>12221122</t>
   </si>
   <si>
-    <t>Riconoscimento paterno di figlio ultraquattordicenne gia' riconosciuto dalla madre</t>
+    <t>Riconoscimento paterno o di altro genitore di figlio ultraquattordicenne già riconosciuto dalla madre</t>
   </si>
   <si>
     <t>12221123</t>
@@ -890,13 +890,10 @@
     <t>12221212</t>
   </si>
   <si>
-    <t>Riconoscimento paterno di figlio infraquattordicenne gia' riconosciuto dalla madre</t>
+    <t>Riconoscimento paterno o di altro genitore di figlio infraquattordicenne già riconosciuto dalla madre</t>
   </si>
   <si>
     <t>12221422</t>
-  </si>
-  <si>
-    <t>Riconoscimento paterno di figlio maggiorenne gia' riconosciuto dalla madre</t>
   </si>
   <si>
     <t>12222121</t>
@@ -5165,7 +5162,7 @@
         <v>293</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C142" s="2" t="s">
         <v>8</v>
@@ -5182,10 +5179,10 @@
     </row>
     <row r="143">
       <c r="A143" s="2" t="s">
+        <v>294</v>
+      </c>
+      <c r="B143" s="2" t="s">
         <v>295</v>
-      </c>
-      <c r="B143" s="2" t="s">
-        <v>296</v>
       </c>
       <c r="C143" s="2" t="s">
         <v>8</v>
@@ -5202,10 +5199,10 @@
     </row>
     <row r="144">
       <c r="A144" s="2" t="s">
+        <v>296</v>
+      </c>
+      <c r="B144" s="2" t="s">
         <v>297</v>
-      </c>
-      <c r="B144" s="2" t="s">
-        <v>298</v>
       </c>
       <c r="C144" s="2" t="s">
         <v>8</v>
@@ -5222,10 +5219,10 @@
     </row>
     <row r="145">
       <c r="A145" s="2" t="s">
+        <v>298</v>
+      </c>
+      <c r="B145" s="2" t="s">
         <v>299</v>
-      </c>
-      <c r="B145" s="2" t="s">
-        <v>300</v>
       </c>
       <c r="C145" s="2" t="s">
         <v>8</v>
@@ -5242,10 +5239,10 @@
     </row>
     <row r="146">
       <c r="A146" s="2" t="s">
+        <v>300</v>
+      </c>
+      <c r="B146" s="2" t="s">
         <v>301</v>
-      </c>
-      <c r="B146" s="2" t="s">
-        <v>302</v>
       </c>
       <c r="C146" s="2" t="s">
         <v>8</v>
@@ -5262,13 +5259,13 @@
     </row>
     <row r="147">
       <c r="A147" s="2" t="s">
+        <v>302</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="B147" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>304</v>
-      </c>
-      <c r="C147" s="2" t="s">
-        <v>305</v>
       </c>
       <c r="D147" s="2" t="s">
         <v>9</v>
@@ -5282,10 +5279,10 @@
     </row>
     <row r="148">
       <c r="A148" s="2" t="s">
+        <v>305</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>306</v>
-      </c>
-      <c r="B148" s="2" t="s">
-        <v>307</v>
       </c>
       <c r="C148" s="2" t="s">
         <v>8</v>
@@ -5302,10 +5299,10 @@
     </row>
     <row r="149">
       <c r="A149" s="2" t="s">
+        <v>307</v>
+      </c>
+      <c r="B149" s="2" t="s">
         <v>308</v>
-      </c>
-      <c r="B149" s="2" t="s">
-        <v>309</v>
       </c>
       <c r="C149" s="2" t="s">
         <v>8</v>
@@ -5322,10 +5319,10 @@
     </row>
     <row r="150">
       <c r="A150" s="2" t="s">
+        <v>309</v>
+      </c>
+      <c r="B150" s="2" t="s">
         <v>310</v>
-      </c>
-      <c r="B150" s="2" t="s">
-        <v>311</v>
       </c>
       <c r="C150" s="2" t="s">
         <v>8</v>
@@ -5342,10 +5339,10 @@
     </row>
     <row r="151">
       <c r="A151" s="2" t="s">
+        <v>311</v>
+      </c>
+      <c r="B151" s="2" t="s">
         <v>312</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>313</v>
       </c>
       <c r="C151" s="2" t="s">
         <v>8</v>
@@ -5362,10 +5359,10 @@
     </row>
     <row r="152">
       <c r="A152" s="2" t="s">
+        <v>313</v>
+      </c>
+      <c r="B152" s="2" t="s">
         <v>314</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>315</v>
       </c>
       <c r="C152" s="2" t="s">
         <v>8</v>
@@ -5382,10 +5379,10 @@
     </row>
     <row r="153">
       <c r="A153" s="2" t="s">
+        <v>315</v>
+      </c>
+      <c r="B153" s="2" t="s">
         <v>316</v>
-      </c>
-      <c r="B153" s="2" t="s">
-        <v>317</v>
       </c>
       <c r="C153" s="2" t="s">
         <v>8</v>
@@ -5402,10 +5399,10 @@
     </row>
     <row r="154">
       <c r="A154" s="2" t="s">
+        <v>317</v>
+      </c>
+      <c r="B154" s="2" t="s">
         <v>318</v>
-      </c>
-      <c r="B154" s="2" t="s">
-        <v>319</v>
       </c>
       <c r="C154" s="2" t="s">
         <v>8</v>
@@ -5422,13 +5419,13 @@
     </row>
     <row r="155">
       <c r="A155" s="2" t="s">
+        <v>319</v>
+      </c>
+      <c r="B155" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="B155" s="2" t="s">
+      <c r="C155" s="2" t="s">
         <v>321</v>
-      </c>
-      <c r="C155" s="2" t="s">
-        <v>322</v>
       </c>
       <c r="D155" s="2" t="s">
         <v>9</v>
@@ -5442,10 +5439,10 @@
     </row>
     <row r="156">
       <c r="A156" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="B156" s="2" t="s">
         <v>323</v>
-      </c>
-      <c r="B156" s="2" t="s">
-        <v>324</v>
       </c>
       <c r="C156" s="2" t="s">
         <v>8</v>
@@ -5462,11 +5459,11 @@
     </row>
     <row r="157">
       <c r="A157" s="2" t="s">
+        <v>324</v>
+      </c>
+      <c r="B157" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="B157" s="2" t="s">
-        <v>326</v>
-      </c>
       <c r="C157" s="2" t="s">
         <v>8</v>
       </c>
@@ -5477,16 +5474,16 @@
         <v>10</v>
       </c>
       <c r="F157" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="s">
+        <v>327</v>
+      </c>
+      <c r="B158" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="B158" s="2" t="s">
-        <v>329</v>
-      </c>
       <c r="C158" s="2" t="s">
         <v>8</v>
       </c>
@@ -5497,16 +5494,16 @@
         <v>10</v>
       </c>
       <c r="F158" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="s">
+        <v>329</v>
+      </c>
+      <c r="B159" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="B159" s="2" t="s">
-        <v>331</v>
-      </c>
       <c r="C159" s="2" t="s">
         <v>8</v>
       </c>
@@ -5517,16 +5514,16 @@
         <v>10</v>
       </c>
       <c r="F159" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="B160" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="B160" s="2" t="s">
-        <v>333</v>
-      </c>
       <c r="C160" s="2" t="s">
         <v>8</v>
       </c>
@@ -5537,18 +5534,18 @@
         <v>10</v>
       </c>
       <c r="F160" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="s">
+        <v>333</v>
+      </c>
+      <c r="B161" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="B161" s="2" t="s">
-        <v>335</v>
-      </c>
       <c r="C161" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D161" s="2" t="s">
         <v>9</v>
@@ -5557,18 +5554,18 @@
         <v>10</v>
       </c>
       <c r="F161" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="s">
+        <v>335</v>
+      </c>
+      <c r="B162" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="B162" s="2" t="s">
-        <v>337</v>
-      </c>
       <c r="C162" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D162" s="2" t="s">
         <v>9</v>
@@ -5577,19 +5574,19 @@
         <v>10</v>
       </c>
       <c r="F162" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="s">
+        <v>337</v>
+      </c>
+      <c r="B163" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="B163" s="2" t="s">
+      <c r="C163" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="C163" s="2" t="s">
-        <v>340</v>
-      </c>
       <c r="D163" s="2" t="s">
         <v>9</v>
       </c>
@@ -5597,16 +5594,16 @@
         <v>10</v>
       </c>
       <c r="F163" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="s">
+        <v>340</v>
+      </c>
+      <c r="B164" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="B164" s="2" t="s">
-        <v>342</v>
-      </c>
       <c r="C164" s="2" t="s">
         <v>8</v>
       </c>
@@ -5617,16 +5614,16 @@
         <v>10</v>
       </c>
       <c r="F164" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="s">
+        <v>342</v>
+      </c>
+      <c r="B165" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="B165" s="2" t="s">
-        <v>344</v>
-      </c>
       <c r="C165" s="2" t="s">
         <v>8</v>
       </c>
@@ -5637,16 +5634,16 @@
         <v>10</v>
       </c>
       <c r="F165" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="s">
+        <v>344</v>
+      </c>
+      <c r="B166" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="B166" s="2" t="s">
-        <v>346</v>
-      </c>
       <c r="C166" s="2" t="s">
         <v>8</v>
       </c>
@@ -5657,16 +5654,16 @@
         <v>10</v>
       </c>
       <c r="F166" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="s">
+        <v>346</v>
+      </c>
+      <c r="B167" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="B167" s="2" t="s">
-        <v>348</v>
-      </c>
       <c r="C167" s="2" t="s">
         <v>8</v>
       </c>
@@ -5677,16 +5674,16 @@
         <v>10</v>
       </c>
       <c r="F167" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="s">
+        <v>348</v>
+      </c>
+      <c r="B168" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B168" s="2" t="s">
-        <v>350</v>
-      </c>
       <c r="C168" s="2" t="s">
         <v>8</v>
       </c>
@@ -5697,16 +5694,16 @@
         <v>10</v>
       </c>
       <c r="F168" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="s">
+        <v>350</v>
+      </c>
+      <c r="B169" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="B169" s="2" t="s">
-        <v>352</v>
-      </c>
       <c r="C169" s="2" t="s">
         <v>8</v>
       </c>
@@ -5717,19 +5714,19 @@
         <v>10</v>
       </c>
       <c r="F169" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="s">
+        <v>352</v>
+      </c>
+      <c r="B170" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="B170" s="2" t="s">
+      <c r="C170" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="C170" s="2" t="s">
-        <v>355</v>
-      </c>
       <c r="D170" s="2" t="s">
         <v>9</v>
       </c>
@@ -5737,18 +5734,18 @@
         <v>10</v>
       </c>
       <c r="F170" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="s">
+        <v>355</v>
+      </c>
+      <c r="B171" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="B171" s="2" t="s">
-        <v>357</v>
-      </c>
       <c r="C171" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D171" s="2" t="s">
         <v>9</v>
@@ -5757,18 +5754,18 @@
         <v>10</v>
       </c>
       <c r="F171" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="s">
+        <v>357</v>
+      </c>
+      <c r="B172" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="B172" s="2" t="s">
-        <v>359</v>
-      </c>
       <c r="C172" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D172" s="2" t="s">
         <v>9</v>
@@ -5777,18 +5774,18 @@
         <v>10</v>
       </c>
       <c r="F172" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="s">
+        <v>359</v>
+      </c>
+      <c r="B173" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="B173" s="2" t="s">
-        <v>361</v>
-      </c>
       <c r="C173" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D173" s="2" t="s">
         <v>9</v>
@@ -5797,16 +5794,16 @@
         <v>10</v>
       </c>
       <c r="F173" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="B174" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="B174" s="2" t="s">
-        <v>363</v>
-      </c>
       <c r="C174" s="2" t="s">
         <v>8</v>
       </c>
@@ -5817,16 +5814,16 @@
         <v>10</v>
       </c>
       <c r="F174" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="s">
+        <v>363</v>
+      </c>
+      <c r="B175" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="B175" s="2" t="s">
-        <v>365</v>
-      </c>
       <c r="C175" s="2" t="s">
         <v>8</v>
       </c>
@@ -5837,16 +5834,16 @@
         <v>10</v>
       </c>
       <c r="F175" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="s">
+        <v>365</v>
+      </c>
+      <c r="B176" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="B176" s="2" t="s">
-        <v>367</v>
-      </c>
       <c r="C176" s="2" t="s">
         <v>8</v>
       </c>
@@ -5857,16 +5854,16 @@
         <v>10</v>
       </c>
       <c r="F176" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="s">
+        <v>367</v>
+      </c>
+      <c r="B177" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="B177" s="2" t="s">
-        <v>369</v>
-      </c>
       <c r="C177" s="2" t="s">
         <v>8</v>
       </c>
@@ -5877,16 +5874,16 @@
         <v>10</v>
       </c>
       <c r="F177" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="s">
+        <v>369</v>
+      </c>
+      <c r="B178" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="B178" s="2" t="s">
-        <v>371</v>
-      </c>
       <c r="C178" s="2" t="s">
         <v>8</v>
       </c>
@@ -5897,16 +5894,16 @@
         <v>10</v>
       </c>
       <c r="F178" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="s">
+        <v>371</v>
+      </c>
+      <c r="B179" s="2" t="s">
         <v>372</v>
       </c>
-      <c r="B179" s="2" t="s">
-        <v>373</v>
-      </c>
       <c r="C179" s="2" t="s">
         <v>8</v>
       </c>
@@ -5917,16 +5914,16 @@
         <v>10</v>
       </c>
       <c r="F179" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="B180" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="B180" s="2" t="s">
-        <v>375</v>
-      </c>
       <c r="C180" s="2" t="s">
         <v>8</v>
       </c>
@@ -5937,16 +5934,16 @@
         <v>10</v>
       </c>
       <c r="F180" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" s="2" t="s">
+        <v>375</v>
+      </c>
+      <c r="B181" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="B181" s="2" t="s">
-        <v>377</v>
-      </c>
       <c r="C181" s="2" t="s">
         <v>8</v>
       </c>
@@ -5957,16 +5954,16 @@
         <v>10</v>
       </c>
       <c r="F181" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" s="2" t="s">
+        <v>377</v>
+      </c>
+      <c r="B182" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="B182" s="2" t="s">
-        <v>379</v>
-      </c>
       <c r="C182" s="2" t="s">
         <v>8</v>
       </c>
@@ -5977,18 +5974,18 @@
         <v>10</v>
       </c>
       <c r="F182" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" s="2" t="s">
+        <v>379</v>
+      </c>
+      <c r="B183" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="B183" s="2" t="s">
-        <v>381</v>
-      </c>
       <c r="C183" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D183" s="2" t="s">
         <v>9</v>
@@ -5997,19 +5994,19 @@
         <v>10</v>
       </c>
       <c r="F183" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="B184" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="C184" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="C184" s="2" t="s">
-        <v>384</v>
-      </c>
       <c r="D184" s="2" t="s">
         <v>9</v>
       </c>
@@ -6017,16 +6014,16 @@
         <v>10</v>
       </c>
       <c r="F184" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" s="2" t="s">
+        <v>384</v>
+      </c>
+      <c r="B185" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="B185" s="2" t="s">
-        <v>386</v>
-      </c>
       <c r="C185" s="2" t="s">
         <v>8</v>
       </c>
@@ -6037,15 +6034,15 @@
         <v>10</v>
       </c>
       <c r="F185" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" s="2" t="s">
+        <v>386</v>
+      </c>
+      <c r="B186" s="2" t="s">
         <v>387</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>388</v>
       </c>
       <c r="C186" s="2" t="s">
         <v>8</v>
@@ -6062,11 +6059,11 @@
     </row>
     <row r="187">
       <c r="A187" s="2" t="s">
+        <v>388</v>
+      </c>
+      <c r="B187" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="B187" s="2" t="s">
-        <v>390</v>
-      </c>
       <c r="C187" s="2" t="s">
         <v>8</v>
       </c>
@@ -6077,15 +6074,15 @@
         <v>10</v>
       </c>
       <c r="F187" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" s="2" t="s">
+        <v>390</v>
+      </c>
+      <c r="B188" s="2" t="s">
         <v>391</v>
-      </c>
-      <c r="B188" s="2" t="s">
-        <v>392</v>
       </c>
       <c r="C188" s="2" t="s">
         <v>8</v>
@@ -6102,11 +6099,11 @@
     </row>
     <row r="189">
       <c r="A189" s="2" t="s">
+        <v>392</v>
+      </c>
+      <c r="B189" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="B189" s="2" t="s">
-        <v>394</v>
-      </c>
       <c r="C189" s="2" t="s">
         <v>8</v>
       </c>
@@ -6117,15 +6114,15 @@
         <v>10</v>
       </c>
       <c r="F189" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" s="2" t="s">
+        <v>394</v>
+      </c>
+      <c r="B190" s="2" t="s">
         <v>395</v>
-      </c>
-      <c r="B190" s="2" t="s">
-        <v>396</v>
       </c>
       <c r="C190" s="2" t="s">
         <v>8</v>
@@ -6142,11 +6139,11 @@
     </row>
     <row r="191">
       <c r="A191" s="2" t="s">
+        <v>396</v>
+      </c>
+      <c r="B191" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="B191" s="2" t="s">
-        <v>398</v>
-      </c>
       <c r="C191" s="2" t="s">
         <v>8</v>
       </c>
@@ -6157,19 +6154,19 @@
         <v>10</v>
       </c>
       <c r="F191" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" s="2" t="s">
+        <v>398</v>
+      </c>
+      <c r="B192" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="B192" s="2" t="s">
+      <c r="C192" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="C192" s="2" t="s">
-        <v>401</v>
-      </c>
       <c r="D192" s="2" t="s">
         <v>9</v>
       </c>
@@ -6177,19 +6174,19 @@
         <v>10</v>
       </c>
       <c r="F192" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="B193" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="B193" s="2" t="s">
+      <c r="C193" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="C193" s="2" t="s">
-        <v>404</v>
-      </c>
       <c r="D193" s="2" t="s">
         <v>9</v>
       </c>
@@ -6197,18 +6194,18 @@
         <v>10</v>
       </c>
       <c r="F193" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" s="2" t="s">
+        <v>404</v>
+      </c>
+      <c r="B194" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B194" s="2" t="s">
-        <v>406</v>
-      </c>
       <c r="C194" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D194" s="2" t="s">
         <v>9</v>
@@ -6217,16 +6214,16 @@
         <v>10</v>
       </c>
       <c r="F194" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" s="2" t="s">
+        <v>406</v>
+      </c>
+      <c r="B195" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="B195" s="2" t="s">
-        <v>408</v>
-      </c>
       <c r="C195" s="2" t="s">
         <v>8</v>
       </c>
@@ -6237,36 +6234,36 @@
         <v>10</v>
       </c>
       <c r="F195" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" s="2" t="s">
+        <v>408</v>
+      </c>
+      <c r="B196" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="B196" s="2" t="s">
+      <c r="C196" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D196" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E196" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F196" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C196" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D196" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E196" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F196" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" s="2" t="s">
+        <v>411</v>
+      </c>
+      <c r="B197" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="B197" s="2" t="s">
-        <v>413</v>
-      </c>
       <c r="C197" s="2" t="s">
         <v>8</v>
       </c>
@@ -6277,16 +6274,16 @@
         <v>10</v>
       </c>
       <c r="F197" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" s="2" t="s">
+        <v>413</v>
+      </c>
+      <c r="B198" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="B198" s="2" t="s">
-        <v>415</v>
-      </c>
       <c r="C198" s="2" t="s">
         <v>8</v>
       </c>
@@ -6297,16 +6294,16 @@
         <v>10</v>
       </c>
       <c r="F198" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" s="2" t="s">
+        <v>415</v>
+      </c>
+      <c r="B199" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="B199" s="2" t="s">
-        <v>417</v>
-      </c>
       <c r="C199" s="2" t="s">
         <v>8</v>
       </c>
@@ -6317,19 +6314,19 @@
         <v>10</v>
       </c>
       <c r="F199" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" s="2" t="s">
+        <v>417</v>
+      </c>
+      <c r="B200" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="B200" s="2" t="s">
+      <c r="C200" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="C200" s="2" t="s">
-        <v>420</v>
-      </c>
       <c r="D200" s="2" t="s">
         <v>9</v>
       </c>
@@ -6337,19 +6334,19 @@
         <v>10</v>
       </c>
       <c r="F200" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" s="2" t="s">
+        <v>420</v>
+      </c>
+      <c r="B201" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="B201" s="2" t="s">
+      <c r="C201" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C201" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="D201" s="2" t="s">
         <v>9</v>
       </c>
@@ -6357,18 +6354,18 @@
         <v>10</v>
       </c>
       <c r="F201" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" s="2" t="s">
+        <v>423</v>
+      </c>
+      <c r="B202" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="B202" s="2" t="s">
-        <v>425</v>
-      </c>
       <c r="C202" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D202" s="2" t="s">
         <v>9</v>
@@ -6377,18 +6374,18 @@
         <v>10</v>
       </c>
       <c r="F202" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" s="2" t="s">
+        <v>425</v>
+      </c>
+      <c r="B203" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="B203" s="2" t="s">
-        <v>427</v>
-      </c>
       <c r="C203" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D203" s="2" t="s">
         <v>9</v>
@@ -6397,19 +6394,19 @@
         <v>10</v>
       </c>
       <c r="F203" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" s="2" t="s">
+        <v>427</v>
+      </c>
+      <c r="B204" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="B204" s="2" t="s">
+      <c r="C204" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="C204" s="2" t="s">
-        <v>430</v>
-      </c>
       <c r="D204" s="2" t="s">
         <v>9</v>
       </c>
@@ -6417,18 +6414,18 @@
         <v>10</v>
       </c>
       <c r="F204" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" s="2" t="s">
+        <v>430</v>
+      </c>
+      <c r="B205" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="B205" s="2" t="s">
-        <v>432</v>
-      </c>
       <c r="C205" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D205" s="2" t="s">
         <v>9</v>
@@ -6437,18 +6434,18 @@
         <v>10</v>
       </c>
       <c r="F205" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" s="2" t="s">
+        <v>432</v>
+      </c>
+      <c r="B206" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>434</v>
-      </c>
       <c r="C206" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D206" s="2" t="s">
         <v>9</v>
@@ -6457,18 +6454,18 @@
         <v>10</v>
       </c>
       <c r="F206" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" s="2" t="s">
+        <v>434</v>
+      </c>
+      <c r="B207" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>436</v>
-      </c>
       <c r="C207" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D207" s="2" t="s">
         <v>9</v>
@@ -6477,12 +6474,12 @@
         <v>10</v>
       </c>
       <c r="F207" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" s="2" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="B208" s="2" t="s">
         <v>7</v>
@@ -6502,10 +6499,10 @@
     </row>
     <row r="209">
       <c r="A209" s="2" t="s">
+        <v>437</v>
+      </c>
+      <c r="B209" s="2" t="s">
         <v>438</v>
-      </c>
-      <c r="B209" s="2" t="s">
-        <v>439</v>
       </c>
       <c r="C209" s="2" t="s">
         <v>8</v>
@@ -6522,10 +6519,10 @@
     </row>
     <row r="210">
       <c r="A210" s="2" t="s">
+        <v>439</v>
+      </c>
+      <c r="B210" s="2" t="s">
         <v>440</v>
-      </c>
-      <c r="B210" s="2" t="s">
-        <v>441</v>
       </c>
       <c r="C210" s="2" t="s">
         <v>8</v>
@@ -6542,10 +6539,10 @@
     </row>
     <row r="211">
       <c r="A211" s="2" t="s">
+        <v>441</v>
+      </c>
+      <c r="B211" s="2" t="s">
         <v>442</v>
-      </c>
-      <c r="B211" s="2" t="s">
-        <v>443</v>
       </c>
       <c r="C211" s="2" t="s">
         <v>8</v>
@@ -6562,10 +6559,10 @@
     </row>
     <row r="212">
       <c r="A212" s="2" t="s">
+        <v>443</v>
+      </c>
+      <c r="B212" s="2" t="s">
         <v>444</v>
-      </c>
-      <c r="B212" s="2" t="s">
-        <v>445</v>
       </c>
       <c r="C212" s="2" t="s">
         <v>8</v>
@@ -6582,13 +6579,13 @@
     </row>
     <row r="213">
       <c r="A213" s="2" t="s">
+        <v>445</v>
+      </c>
+      <c r="B213" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="B213" s="2" t="s">
-        <v>447</v>
-      </c>
       <c r="C213" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D213" s="2" t="s">
         <v>9</v>
@@ -6602,13 +6599,13 @@
     </row>
     <row r="214">
       <c r="A214" s="2" t="s">
+        <v>447</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="B214" s="2" t="s">
-        <v>449</v>
-      </c>
       <c r="C214" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D214" s="2" t="s">
         <v>9</v>
@@ -6622,13 +6619,13 @@
     </row>
     <row r="215">
       <c r="A215" s="2" t="s">
+        <v>449</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="B215" s="2" t="s">
-        <v>451</v>
-      </c>
       <c r="C215" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D215" s="2" t="s">
         <v>9</v>
@@ -6642,10 +6639,10 @@
     </row>
     <row r="216">
       <c r="A216" s="2" t="s">
+        <v>451</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>452</v>
-      </c>
-      <c r="B216" s="2" t="s">
-        <v>453</v>
       </c>
       <c r="C216" s="2" t="s">
         <v>8</v>
@@ -6662,11 +6659,11 @@
     </row>
     <row r="217">
       <c r="A217" s="2" t="s">
+        <v>453</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="B217" s="2" t="s">
-        <v>455</v>
-      </c>
       <c r="C217" s="2" t="s">
         <v>8</v>
       </c>
@@ -6677,16 +6674,16 @@
         <v>10</v>
       </c>
       <c r="F217" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" s="2" t="s">
+        <v>455</v>
+      </c>
+      <c r="B218" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="B218" s="2" t="s">
-        <v>457</v>
-      </c>
       <c r="C218" s="2" t="s">
         <v>8</v>
       </c>
@@ -6697,16 +6694,16 @@
         <v>10</v>
       </c>
       <c r="F218" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" s="2" t="s">
+        <v>457</v>
+      </c>
+      <c r="B219" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="B219" s="2" t="s">
-        <v>459</v>
-      </c>
       <c r="C219" s="2" t="s">
         <v>8</v>
       </c>
@@ -6717,38 +6714,38 @@
         <v>10</v>
       </c>
       <c r="F219" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" s="2" t="s">
+        <v>459</v>
+      </c>
+      <c r="B220" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="B220" s="2" t="s">
+      <c r="C220" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D220" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="C220" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D220" s="2" t="s">
-        <v>462</v>
-      </c>
       <c r="E220" s="2" t="s">
         <v>10</v>
       </c>
       <c r="F220" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" s="2" t="s">
+        <v>462</v>
+      </c>
+      <c r="B221" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="B221" s="2" t="s">
-        <v>464</v>
-      </c>
       <c r="C221" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>9</v>
@@ -6757,19 +6754,19 @@
         <v>10</v>
       </c>
       <c r="F221" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" s="2" t="s">
+        <v>464</v>
+      </c>
+      <c r="B222" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="B222" s="2" t="s">
+      <c r="C222" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="C222" s="2" t="s">
-        <v>467</v>
-      </c>
       <c r="D222" s="2" t="s">
         <v>9</v>
       </c>
@@ -6777,16 +6774,16 @@
         <v>10</v>
       </c>
       <c r="F222" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" s="2" t="s">
+        <v>467</v>
+      </c>
+      <c r="B223" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="B223" s="2" t="s">
-        <v>469</v>
-      </c>
       <c r="C223" s="2" t="s">
         <v>8</v>
       </c>
@@ -6797,16 +6794,16 @@
         <v>10</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" s="2" t="s">
+        <v>469</v>
+      </c>
+      <c r="B224" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>471</v>
-      </c>
       <c r="C224" s="2" t="s">
         <v>8</v>
       </c>
@@ -6817,16 +6814,16 @@
         <v>10</v>
       </c>
       <c r="F224" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" s="2" t="s">
+        <v>471</v>
+      </c>
+      <c r="B225" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>473</v>
-      </c>
       <c r="C225" s="2" t="s">
         <v>8</v>
       </c>
@@ -6837,16 +6834,16 @@
         <v>10</v>
       </c>
       <c r="F225" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" s="2" t="s">
+        <v>473</v>
+      </c>
+      <c r="B226" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>475</v>
-      </c>
       <c r="C226" s="2" t="s">
         <v>8</v>
       </c>
@@ -6857,18 +6854,18 @@
         <v>10</v>
       </c>
       <c r="F226" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" s="2" t="s">
+        <v>475</v>
+      </c>
+      <c r="B227" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="B227" s="2" t="s">
-        <v>477</v>
-      </c>
       <c r="C227" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D227" s="2" t="s">
         <v>9</v>
@@ -6877,16 +6874,16 @@
         <v>10</v>
       </c>
       <c r="F227" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="B228" s="2" t="s">
         <v>478</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>479</v>
-      </c>
       <c r="C228" s="2" t="s">
         <v>8</v>
       </c>
@@ -6897,36 +6894,36 @@
         <v>10</v>
       </c>
       <c r="F228" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" s="2" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B229" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C229" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F229" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D229" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E229" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F229" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="B230" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="C230" s="2" t="s">
         <v>8</v>
       </c>
@@ -6937,15 +6934,15 @@
         <v>10</v>
       </c>
       <c r="F230" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" s="2" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C231" s="2" t="s">
         <v>8</v>
@@ -6957,15 +6954,15 @@
         <v>10</v>
       </c>
       <c r="F231" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" s="2" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C232" s="2" t="s">
         <v>8</v>
@@ -6977,19 +6974,19 @@
         <v>10</v>
       </c>
       <c r="F232" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" s="2" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B233" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C233" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C233" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="D233" s="2" t="s">
         <v>9</v>
       </c>
@@ -6997,18 +6994,18 @@
         <v>10</v>
       </c>
       <c r="F233" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" s="2" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D234" s="2" t="s">
         <v>9</v>
@@ -7017,12 +7014,12 @@
         <v>10</v>
       </c>
       <c r="F234" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" s="2" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B235" s="2" t="s">
         <v>7</v>
@@ -7042,10 +7039,10 @@
     </row>
     <row r="236">
       <c r="A236" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="B236" s="2" t="s">
         <v>488</v>
-      </c>
-      <c r="B236" s="2" t="s">
-        <v>489</v>
       </c>
       <c r="C236" s="2" t="s">
         <v>8</v>
@@ -7062,16 +7059,16 @@
     </row>
     <row r="237">
       <c r="A237" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="B237" s="2" t="s">
         <v>490</v>
       </c>
-      <c r="B237" s="2" t="s">
+      <c r="C237" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D237" s="2" t="s">
         <v>491</v>
-      </c>
-      <c r="C237" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D237" s="2" t="s">
-        <v>492</v>
       </c>
       <c r="E237" s="2" t="s">
         <v>10</v>
@@ -7082,10 +7079,10 @@
     </row>
     <row r="238">
       <c r="A238" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B238" s="2" t="s">
         <v>493</v>
-      </c>
-      <c r="B238" s="2" t="s">
-        <v>494</v>
       </c>
       <c r="C238" s="2" t="s">
         <v>8</v>
@@ -7102,16 +7099,16 @@
     </row>
     <row r="239">
       <c r="A239" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="B239" s="2" t="s">
         <v>495</v>
       </c>
-      <c r="B239" s="2" t="s">
-        <v>496</v>
-      </c>
       <c r="C239" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D239" s="2" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E239" s="2" t="s">
         <v>10</v>
@@ -7122,10 +7119,10 @@
     </row>
     <row r="240">
       <c r="A240" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="B240" s="2" t="s">
         <v>497</v>
-      </c>
-      <c r="B240" s="2" t="s">
-        <v>498</v>
       </c>
       <c r="C240" s="2" t="s">
         <v>8</v>
@@ -7142,10 +7139,10 @@
     </row>
     <row r="241">
       <c r="A241" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="B241" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="B241" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="C241" s="2" t="s">
         <v>8</v>
@@ -7162,10 +7159,10 @@
     </row>
     <row r="242">
       <c r="A242" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="B242" s="2" t="s">
         <v>501</v>
-      </c>
-      <c r="B242" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="C242" s="2" t="s">
         <v>8</v>
@@ -7182,10 +7179,10 @@
     </row>
     <row r="243">
       <c r="A243" s="2" t="s">
+        <v>502</v>
+      </c>
+      <c r="B243" s="2" t="s">
         <v>503</v>
-      </c>
-      <c r="B243" s="2" t="s">
-        <v>504</v>
       </c>
       <c r="C243" s="2" t="s">
         <v>8</v>
@@ -7202,10 +7199,10 @@
     </row>
     <row r="244">
       <c r="A244" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="B244" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="C244" s="2" t="s">
         <v>8</v>
@@ -7222,10 +7219,10 @@
     </row>
     <row r="245">
       <c r="A245" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="B245" s="2" t="s">
         <v>507</v>
-      </c>
-      <c r="B245" s="2" t="s">
-        <v>508</v>
       </c>
       <c r="C245" s="2" t="s">
         <v>8</v>
@@ -7242,10 +7239,10 @@
     </row>
     <row r="246">
       <c r="A246" s="2" t="s">
+        <v>508</v>
+      </c>
+      <c r="B246" s="2" t="s">
         <v>509</v>
-      </c>
-      <c r="B246" s="2" t="s">
-        <v>510</v>
       </c>
       <c r="C246" s="2" t="s">
         <v>8</v>
@@ -7262,10 +7259,10 @@
     </row>
     <row r="247">
       <c r="A247" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B247" s="2" t="s">
         <v>511</v>
-      </c>
-      <c r="B247" s="2" t="s">
-        <v>512</v>
       </c>
       <c r="C247" s="2" t="s">
         <v>8</v>
@@ -7282,13 +7279,13 @@
     </row>
     <row r="248">
       <c r="A248" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="B248" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>514</v>
-      </c>
       <c r="C248" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D248" s="2" t="s">
         <v>9</v>
@@ -7302,10 +7299,10 @@
     </row>
     <row r="249">
       <c r="A249" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="B249" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>516</v>
       </c>
       <c r="C249" s="2" t="s">
         <v>8</v>
@@ -7322,10 +7319,10 @@
     </row>
     <row r="250">
       <c r="A250" s="2" t="s">
+        <v>516</v>
+      </c>
+      <c r="B250" s="2" t="s">
         <v>517</v>
-      </c>
-      <c r="B250" s="2" t="s">
-        <v>518</v>
       </c>
       <c r="C250" s="2" t="s">
         <v>8</v>
@@ -7342,10 +7339,10 @@
     </row>
     <row r="251">
       <c r="A251" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="B251" s="2" t="s">
         <v>519</v>
-      </c>
-      <c r="B251" s="2" t="s">
-        <v>520</v>
       </c>
       <c r="C251" s="2" t="s">
         <v>8</v>
@@ -7362,10 +7359,10 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="B252" s="2" t="s">
         <v>521</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>522</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>8</v>
@@ -7382,10 +7379,10 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
+        <v>522</v>
+      </c>
+      <c r="B253" s="2" t="s">
         <v>523</v>
-      </c>
-      <c r="B253" s="2" t="s">
-        <v>524</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>8</v>
@@ -7402,13 +7399,13 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B254" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B254" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="C254" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>9</v>
@@ -7422,13 +7419,13 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="B255" s="2" t="s">
         <v>525</v>
       </c>
-      <c r="B255" s="2" t="s">
-        <v>526</v>
-      </c>
       <c r="C255" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D255" s="2" t="s">
         <v>9</v>
@@ -7442,10 +7439,10 @@
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="B256" s="2" t="s">
         <v>527</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>528</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -7462,11 +7459,11 @@
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="B257" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="B257" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
       </c>
@@ -7477,16 +7474,16 @@
         <v>10</v>
       </c>
       <c r="F257" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="B258" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="B258" s="2" t="s">
-        <v>532</v>
-      </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
       </c>
@@ -7497,16 +7494,16 @@
         <v>10</v>
       </c>
       <c r="F258" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
+        <v>532</v>
+      </c>
+      <c r="B259" s="2" t="s">
         <v>533</v>
       </c>
-      <c r="B259" s="2" t="s">
-        <v>534</v>
-      </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
       </c>
@@ -7517,16 +7514,16 @@
         <v>10</v>
       </c>
       <c r="F259" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="B260" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="B260" s="2" t="s">
-        <v>536</v>
-      </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
       </c>
@@ -7537,16 +7534,16 @@
         <v>10</v>
       </c>
       <c r="F260" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
+        <v>536</v>
+      </c>
+      <c r="B261" s="2" t="s">
         <v>537</v>
       </c>
-      <c r="B261" s="2" t="s">
-        <v>538</v>
-      </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
       </c>
@@ -7557,19 +7554,19 @@
         <v>10</v>
       </c>
       <c r="F261" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="B262" s="2" t="s">
         <v>539</v>
       </c>
-      <c r="B262" s="2" t="s">
+      <c r="C262" s="2" t="s">
         <v>540</v>
       </c>
-      <c r="C262" s="2" t="s">
-        <v>541</v>
-      </c>
       <c r="D262" s="2" t="s">
         <v>9</v>
       </c>
@@ -7577,16 +7574,16 @@
         <v>10</v>
       </c>
       <c r="F262" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
+        <v>541</v>
+      </c>
+      <c r="B263" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="B263" s="2" t="s">
-        <v>543</v>
-      </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
       </c>
@@ -7597,15 +7594,15 @@
         <v>10</v>
       </c>
       <c r="F263" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="B264" s="2" t="s">
         <v>544</v>
-      </c>
-      <c r="B264" s="2" t="s">
-        <v>545</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -7622,10 +7619,10 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
+        <v>545</v>
+      </c>
+      <c r="B265" s="2" t="s">
         <v>546</v>
-      </c>
-      <c r="B265" s="2" t="s">
-        <v>547</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -7642,10 +7639,10 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="B266" s="2" t="s">
         <v>548</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>549</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -7662,10 +7659,10 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
+        <v>549</v>
+      </c>
+      <c r="B267" s="2" t="s">
         <v>550</v>
-      </c>
-      <c r="B267" s="2" t="s">
-        <v>551</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -7682,10 +7679,10 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="B268" s="2" t="s">
         <v>552</v>
-      </c>
-      <c r="B268" s="2" t="s">
-        <v>553</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -7702,11 +7699,11 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
+        <v>553</v>
+      </c>
+      <c r="B269" s="2" t="s">
         <v>554</v>
       </c>
-      <c r="B269" s="2" t="s">
-        <v>555</v>
-      </c>
       <c r="C269" s="2" t="s">
         <v>8</v>
       </c>
@@ -7717,16 +7714,16 @@
         <v>10</v>
       </c>
       <c r="F269" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="B270" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>557</v>
-      </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
       </c>
@@ -7737,21 +7734,21 @@
         <v>10</v>
       </c>
       <c r="F270" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
+        <v>557</v>
+      </c>
+      <c r="B271" s="2" t="s">
         <v>558</v>
       </c>
-      <c r="B271" s="2" t="s">
+      <c r="C271" s="2" t="s">
+        <v>321</v>
+      </c>
+      <c r="D271" s="2" t="s">
         <v>559</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>322</v>
-      </c>
-      <c r="D271" s="2" t="s">
-        <v>560</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>10</v>
@@ -7762,10 +7759,10 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
+        <v>560</v>
+      </c>
+      <c r="B272" s="2" t="s">
         <v>561</v>
-      </c>
-      <c r="B272" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -7782,10 +7779,10 @@
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="B273" s="2" t="s">
         <v>563</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>564</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>8</v>
@@ -7802,10 +7799,10 @@
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
+        <v>564</v>
+      </c>
+      <c r="B274" s="2" t="s">
         <v>565</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>566</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -7822,14 +7819,14 @@
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="B275" s="2" t="s">
         <v>567</v>
       </c>
-      <c r="B275" s="2" t="s">
+      <c r="C275" s="2" t="s">
         <v>568</v>
       </c>
-      <c r="C275" s="2" t="s">
-        <v>569</v>
-      </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
       </c>
@@ -7837,18 +7834,18 @@
         <v>10</v>
       </c>
       <c r="F275" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="B276" s="2" t="s">
         <v>570</v>
       </c>
-      <c r="B276" s="2" t="s">
-        <v>571</v>
-      </c>
       <c r="C276" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D276" s="2" t="s">
         <v>9</v>
@@ -7857,35 +7854,35 @@
         <v>10</v>
       </c>
       <c r="F276" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B277" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F277" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D277" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E277" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F277" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C278" s="2" t="s">
         <v>8</v>
@@ -7897,15 +7894,15 @@
         <v>10</v>
       </c>
       <c r="F278" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C279" s="2" t="s">
         <v>8</v>
@@ -7917,15 +7914,15 @@
         <v>10</v>
       </c>
       <c r="F279" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C280" s="2" t="s">
         <v>8</v>
@@ -7937,19 +7934,19 @@
         <v>10</v>
       </c>
       <c r="F280" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B281" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C281" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C281" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="D281" s="2" t="s">
         <v>9</v>
       </c>
@@ -7957,18 +7954,18 @@
         <v>10</v>
       </c>
       <c r="F281" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D282" s="2" t="s">
         <v>9</v>
@@ -7977,12 +7974,12 @@
         <v>10</v>
       </c>
       <c r="F282" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>7</v>
@@ -8002,10 +7999,10 @@
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="B284" s="2" t="s">
         <v>579</v>
-      </c>
-      <c r="B284" s="2" t="s">
-        <v>580</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -8022,10 +8019,10 @@
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="B285" s="2" t="s">
         <v>581</v>
-      </c>
-      <c r="B285" s="2" t="s">
-        <v>582</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -8042,10 +8039,10 @@
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="B286" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="B286" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -8062,10 +8059,10 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="B287" s="2" t="s">
         <v>585</v>
-      </c>
-      <c r="B287" s="2" t="s">
-        <v>586</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -8082,10 +8079,10 @@
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="B288" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="B288" s="2" t="s">
-        <v>588</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -8102,10 +8099,10 @@
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="B289" s="2" t="s">
         <v>589</v>
-      </c>
-      <c r="B289" s="2" t="s">
-        <v>590</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -8122,11 +8119,11 @@
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
+        <v>590</v>
+      </c>
+      <c r="B290" s="2" t="s">
         <v>591</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>592</v>
-      </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
       </c>
@@ -8137,16 +8134,16 @@
         <v>10</v>
       </c>
       <c r="F290" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="B291" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="B291" s="2" t="s">
-        <v>594</v>
-      </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
       </c>
@@ -8157,16 +8154,16 @@
         <v>10</v>
       </c>
       <c r="F291" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="B292" s="2" t="s">
         <v>595</v>
       </c>
-      <c r="B292" s="2" t="s">
-        <v>596</v>
-      </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
       </c>
@@ -8177,16 +8174,16 @@
         <v>10</v>
       </c>
       <c r="F292" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="B293" s="2" t="s">
         <v>597</v>
       </c>
-      <c r="B293" s="2" t="s">
-        <v>598</v>
-      </c>
       <c r="C293" s="2" t="s">
         <v>8</v>
       </c>
@@ -8197,18 +8194,18 @@
         <v>10</v>
       </c>
       <c r="F293" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="B294" s="2" t="s">
         <v>599</v>
       </c>
-      <c r="B294" s="2" t="s">
-        <v>600</v>
-      </c>
       <c r="C294" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D294" s="2" t="s">
         <v>9</v>
@@ -8217,18 +8214,18 @@
         <v>10</v>
       </c>
       <c r="F294" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="B295" s="2" t="s">
         <v>601</v>
       </c>
-      <c r="B295" s="2" t="s">
-        <v>602</v>
-      </c>
       <c r="C295" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D295" s="2" t="s">
         <v>9</v>
@@ -8242,11 +8239,11 @@
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="B296" s="2" t="s">
         <v>603</v>
       </c>
-      <c r="B296" s="2" t="s">
-        <v>604</v>
-      </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
       </c>
@@ -8257,15 +8254,15 @@
         <v>10</v>
       </c>
       <c r="F296" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="B297" s="2" t="s">
         <v>605</v>
-      </c>
-      <c r="B297" s="2" t="s">
-        <v>606</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -8282,10 +8279,10 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="B298" s="2" t="s">
         <v>607</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>608</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -8302,10 +8299,10 @@
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="B299" s="2" t="s">
         <v>609</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>610</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -8322,10 +8319,10 @@
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>612</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>8</v>
@@ -8342,10 +8339,10 @@
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
+        <v>612</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>613</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>614</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>8</v>
@@ -8362,13 +8359,13 @@
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
+        <v>614</v>
+      </c>
+      <c r="B302" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="B302" s="2" t="s">
-        <v>616</v>
-      </c>
       <c r="C302" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D302" s="2" t="s">
         <v>9</v>
@@ -8382,13 +8379,13 @@
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="B303" s="2" t="s">
         <v>617</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>618</v>
-      </c>
       <c r="C303" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D303" s="2" t="s">
         <v>9</v>
@@ -8397,19 +8394,19 @@
         <v>10</v>
       </c>
       <c r="F303" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="B304" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="B304" s="2" t="s">
+      <c r="C304" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="C304" s="2" t="s">
-        <v>621</v>
-      </c>
       <c r="D304" s="2" t="s">
         <v>9</v>
       </c>
@@ -8417,15 +8414,15 @@
         <v>10</v>
       </c>
       <c r="F304" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>622</v>
-      </c>
-      <c r="B305" s="2" t="s">
-        <v>623</v>
       </c>
       <c r="C305" s="2" t="s">
         <v>8</v>
@@ -8442,30 +8439,30 @@
     </row>
     <row r="306">
       <c r="A306" s="2" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B306" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C306" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D306" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E306" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F306" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D306" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E306" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F306" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C307" s="2" t="s">
         <v>8</v>
@@ -8477,15 +8474,15 @@
         <v>10</v>
       </c>
       <c r="F307" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C308" s="2" t="s">
         <v>8</v>
@@ -8497,15 +8494,15 @@
         <v>10</v>
       </c>
       <c r="F308" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C309" s="2" t="s">
         <v>8</v>
@@ -8517,19 +8514,19 @@
         <v>10</v>
       </c>
       <c r="F309" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="B310" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C310" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C310" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="D310" s="2" t="s">
         <v>9</v>
       </c>
@@ -8537,18 +8534,18 @@
         <v>10</v>
       </c>
       <c r="F310" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" s="2" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D311" s="2" t="s">
         <v>9</v>
@@ -8557,18 +8554,18 @@
         <v>10</v>
       </c>
       <c r="F311" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="B312" s="2" t="s">
         <v>630</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>631</v>
-      </c>
       <c r="C312" s="2" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D312" s="2" t="s">
         <v>9</v>
@@ -8577,18 +8574,18 @@
         <v>10</v>
       </c>
       <c r="F312" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="B313" s="2" t="s">
         <v>632</v>
       </c>
-      <c r="B313" s="2" t="s">
-        <v>633</v>
-      </c>
       <c r="C313" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D313" s="2" t="s">
         <v>9</v>
@@ -8602,7 +8599,7 @@
     </row>
     <row r="314">
       <c r="A314" s="2" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="B314" s="2" t="s">
         <v>7</v>
@@ -8622,10 +8619,10 @@
     </row>
     <row r="315">
       <c r="A315" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="B315" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="C315" s="2" t="s">
         <v>8</v>
@@ -8642,10 +8639,10 @@
     </row>
     <row r="316">
       <c r="A316" s="2" t="s">
+        <v>636</v>
+      </c>
+      <c r="B316" s="2" t="s">
         <v>637</v>
-      </c>
-      <c r="B316" s="2" t="s">
-        <v>638</v>
       </c>
       <c r="C316" s="2" t="s">
         <v>8</v>
@@ -8662,10 +8659,10 @@
     </row>
     <row r="317">
       <c r="A317" s="2" t="s">
+        <v>638</v>
+      </c>
+      <c r="B317" s="2" t="s">
         <v>639</v>
-      </c>
-      <c r="B317" s="2" t="s">
-        <v>640</v>
       </c>
       <c r="C317" s="2" t="s">
         <v>8</v>
@@ -8682,10 +8679,10 @@
     </row>
     <row r="318">
       <c r="A318" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="B318" s="2" t="s">
         <v>641</v>
-      </c>
-      <c r="B318" s="2" t="s">
-        <v>642</v>
       </c>
       <c r="C318" s="2" t="s">
         <v>8</v>
@@ -8702,10 +8699,10 @@
     </row>
     <row r="319">
       <c r="A319" s="2" t="s">
+        <v>642</v>
+      </c>
+      <c r="B319" s="2" t="s">
         <v>643</v>
-      </c>
-      <c r="B319" s="2" t="s">
-        <v>644</v>
       </c>
       <c r="C319" s="2" t="s">
         <v>8</v>
@@ -8722,10 +8719,10 @@
     </row>
     <row r="320">
       <c r="A320" s="2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B320" s="2" t="s">
         <v>645</v>
-      </c>
-      <c r="B320" s="2" t="s">
-        <v>646</v>
       </c>
       <c r="C320" s="2" t="s">
         <v>8</v>
@@ -8742,10 +8739,10 @@
     </row>
     <row r="321">
       <c r="A321" s="2" t="s">
+        <v>646</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>647</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>648</v>
       </c>
       <c r="C321" s="2" t="s">
         <v>8</v>
@@ -8762,10 +8759,10 @@
     </row>
     <row r="322">
       <c r="A322" s="2" t="s">
+        <v>648</v>
+      </c>
+      <c r="B322" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="B322" s="2" t="s">
-        <v>650</v>
       </c>
       <c r="C322" s="2" t="s">
         <v>8</v>
@@ -8782,13 +8779,13 @@
     </row>
     <row r="323">
       <c r="A323" s="2" t="s">
+        <v>650</v>
+      </c>
+      <c r="B323" s="2" t="s">
         <v>651</v>
       </c>
-      <c r="B323" s="2" t="s">
-        <v>652</v>
-      </c>
       <c r="C323" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D323" s="2" t="s">
         <v>9</v>
@@ -8802,13 +8799,13 @@
     </row>
     <row r="324">
       <c r="A324" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="B324" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="B324" s="2" t="s">
-        <v>654</v>
-      </c>
       <c r="C324" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D324" s="2" t="s">
         <v>9</v>
@@ -8822,10 +8819,10 @@
     </row>
     <row r="325">
       <c r="A325" s="2" t="s">
+        <v>654</v>
+      </c>
+      <c r="B325" s="2" t="s">
         <v>655</v>
-      </c>
-      <c r="B325" s="2" t="s">
-        <v>656</v>
       </c>
       <c r="C325" s="2" t="s">
         <v>8</v>
@@ -8842,10 +8839,10 @@
     </row>
     <row r="326">
       <c r="A326" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="B326" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="B326" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="C326" s="2" t="s">
         <v>8</v>
@@ -8862,10 +8859,10 @@
     </row>
     <row r="327">
       <c r="A327" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="B327" s="2" t="s">
         <v>659</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>660</v>
       </c>
       <c r="C327" s="2" t="s">
         <v>8</v>
@@ -8882,10 +8879,10 @@
     </row>
     <row r="328">
       <c r="A328" s="2" t="s">
+        <v>660</v>
+      </c>
+      <c r="B328" s="2" t="s">
         <v>661</v>
-      </c>
-      <c r="B328" s="2" t="s">
-        <v>662</v>
       </c>
       <c r="C328" s="2" t="s">
         <v>8</v>
@@ -8902,10 +8899,10 @@
     </row>
     <row r="329">
       <c r="A329" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="B329" s="2" t="s">
         <v>663</v>
-      </c>
-      <c r="B329" s="2" t="s">
-        <v>664</v>
       </c>
       <c r="C329" s="2" t="s">
         <v>8</v>
@@ -8922,10 +8919,10 @@
     </row>
     <row r="330">
       <c r="A330" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="B330" s="2" t="s">
         <v>665</v>
-      </c>
-      <c r="B330" s="2" t="s">
-        <v>666</v>
       </c>
       <c r="C330" s="2" t="s">
         <v>8</v>
@@ -8942,10 +8939,10 @@
     </row>
     <row r="331">
       <c r="A331" s="2" t="s">
+        <v>666</v>
+      </c>
+      <c r="B331" s="2" t="s">
         <v>667</v>
-      </c>
-      <c r="B331" s="2" t="s">
-        <v>668</v>
       </c>
       <c r="C331" s="2" t="s">
         <v>8</v>
@@ -8962,10 +8959,10 @@
     </row>
     <row r="332">
       <c r="A332" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="B332" s="2" t="s">
         <v>669</v>
-      </c>
-      <c r="B332" s="2" t="s">
-        <v>670</v>
       </c>
       <c r="C332" s="2" t="s">
         <v>8</v>
@@ -8982,13 +8979,13 @@
     </row>
     <row r="333">
       <c r="A333" s="2" t="s">
+        <v>670</v>
+      </c>
+      <c r="B333" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="B333" s="2" t="s">
-        <v>672</v>
-      </c>
       <c r="C333" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D333" s="2" t="s">
         <v>9</v>
@@ -9002,10 +8999,10 @@
     </row>
     <row r="334">
       <c r="A334" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="B334" s="2" t="s">
         <v>673</v>
-      </c>
-      <c r="B334" s="2" t="s">
-        <v>674</v>
       </c>
       <c r="C334" s="2" t="s">
         <v>8</v>
@@ -9022,11 +9019,11 @@
     </row>
     <row r="335">
       <c r="A335" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="B335" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B335" s="2" t="s">
-        <v>676</v>
-      </c>
       <c r="C335" s="2" t="s">
         <v>8</v>
       </c>
@@ -9037,16 +9034,16 @@
         <v>10</v>
       </c>
       <c r="F335" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="B336" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="B336" s="2" t="s">
-        <v>678</v>
-      </c>
       <c r="C336" s="2" t="s">
         <v>8</v>
       </c>
@@ -9057,16 +9054,16 @@
         <v>10</v>
       </c>
       <c r="F336" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B337" s="2" t="s">
         <v>679</v>
       </c>
-      <c r="B337" s="2" t="s">
-        <v>680</v>
-      </c>
       <c r="C337" s="2" t="s">
         <v>8</v>
       </c>
@@ -9077,18 +9074,18 @@
         <v>10</v>
       </c>
       <c r="F337" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="B338" s="2" t="s">
         <v>681</v>
       </c>
-      <c r="B338" s="2" t="s">
-        <v>682</v>
-      </c>
       <c r="C338" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D338" s="2" t="s">
         <v>9</v>
@@ -9097,16 +9094,16 @@
         <v>10</v>
       </c>
       <c r="F338" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="B339" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="B339" s="2" t="s">
-        <v>684</v>
-      </c>
       <c r="C339" s="2" t="s">
         <v>8</v>
       </c>
@@ -9117,16 +9114,16 @@
         <v>10</v>
       </c>
       <c r="F339" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" s="2" t="s">
+        <v>684</v>
+      </c>
+      <c r="B340" s="2" t="s">
         <v>685</v>
       </c>
-      <c r="B340" s="2" t="s">
-        <v>686</v>
-      </c>
       <c r="C340" s="2" t="s">
         <v>8</v>
       </c>
@@ -9137,16 +9134,16 @@
         <v>10</v>
       </c>
       <c r="F340" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="B341" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="B341" s="2" t="s">
-        <v>688</v>
-      </c>
       <c r="C341" s="2" t="s">
         <v>8</v>
       </c>
@@ -9157,16 +9154,16 @@
         <v>10</v>
       </c>
       <c r="F341" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="B342" s="2" t="s">
         <v>689</v>
       </c>
-      <c r="B342" s="2" t="s">
-        <v>690</v>
-      </c>
       <c r="C342" s="2" t="s">
         <v>8</v>
       </c>
@@ -9177,16 +9174,16 @@
         <v>10</v>
       </c>
       <c r="F342" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="B343" s="2" t="s">
         <v>691</v>
       </c>
-      <c r="B343" s="2" t="s">
-        <v>692</v>
-      </c>
       <c r="C343" s="2" t="s">
         <v>8</v>
       </c>
@@ -9197,16 +9194,16 @@
         <v>10</v>
       </c>
       <c r="F343" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="B344" s="2" t="s">
         <v>693</v>
       </c>
-      <c r="B344" s="2" t="s">
-        <v>694</v>
-      </c>
       <c r="C344" s="2" t="s">
         <v>8</v>
       </c>
@@ -9217,18 +9214,18 @@
         <v>10</v>
       </c>
       <c r="F344" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B345" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="B345" s="2" t="s">
-        <v>696</v>
-      </c>
       <c r="C345" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D345" s="2" t="s">
         <v>9</v>
@@ -9237,16 +9234,16 @@
         <v>10</v>
       </c>
       <c r="F345" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="B346" s="2" t="s">
         <v>697</v>
       </c>
-      <c r="B346" s="2" t="s">
-        <v>698</v>
-      </c>
       <c r="C346" s="2" t="s">
         <v>8</v>
       </c>
@@ -9257,16 +9254,16 @@
         <v>10</v>
       </c>
       <c r="F346" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="B347" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="B347" s="2" t="s">
-        <v>700</v>
-      </c>
       <c r="C347" s="2" t="s">
         <v>8</v>
       </c>
@@ -9277,18 +9274,18 @@
         <v>10</v>
       </c>
       <c r="F347" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" s="2" t="s">
+        <v>700</v>
+      </c>
+      <c r="B348" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="B348" s="2" t="s">
-        <v>702</v>
-      </c>
       <c r="C348" s="2" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="D348" s="2" t="s">
         <v>9</v>
@@ -9297,18 +9294,18 @@
         <v>10</v>
       </c>
       <c r="F348" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="B349" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="B349" s="2" t="s">
-        <v>704</v>
-      </c>
       <c r="C349" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D349" s="2" t="s">
         <v>9</v>
@@ -9317,18 +9314,18 @@
         <v>10</v>
       </c>
       <c r="F349" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" s="2" t="s">
+        <v>704</v>
+      </c>
+      <c r="B350" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="B350" s="2" t="s">
-        <v>706</v>
-      </c>
       <c r="C350" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D350" s="2" t="s">
         <v>9</v>
@@ -9337,19 +9334,19 @@
         <v>10</v>
       </c>
       <c r="F350" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="B351" s="2" t="s">
         <v>707</v>
       </c>
-      <c r="B351" s="2" t="s">
+      <c r="C351" s="2" t="s">
         <v>708</v>
       </c>
-      <c r="C351" s="2" t="s">
-        <v>709</v>
-      </c>
       <c r="D351" s="2" t="s">
         <v>9</v>
       </c>
@@ -9357,16 +9354,16 @@
         <v>10</v>
       </c>
       <c r="F351" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" s="2" t="s">
+        <v>709</v>
+      </c>
+      <c r="B352" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="B352" s="2" t="s">
-        <v>711</v>
-      </c>
       <c r="C352" s="2" t="s">
         <v>8</v>
       </c>
@@ -9377,15 +9374,15 @@
         <v>10</v>
       </c>
       <c r="F352" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" s="2" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C353" s="2" t="s">
         <v>8</v>
@@ -9397,15 +9394,15 @@
         <v>10</v>
       </c>
       <c r="F353" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" s="2" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C354" s="2" t="s">
         <v>8</v>
@@ -9417,16 +9414,16 @@
         <v>10</v>
       </c>
       <c r="F354" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="B355" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="B355" s="2" t="s">
-        <v>715</v>
-      </c>
       <c r="C355" s="2" t="s">
         <v>8</v>
       </c>
@@ -9437,16 +9434,16 @@
         <v>10</v>
       </c>
       <c r="F355" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="B356" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="B356" s="2" t="s">
-        <v>717</v>
-      </c>
       <c r="C356" s="2" t="s">
         <v>8</v>
       </c>
@@ -9457,16 +9454,16 @@
         <v>10</v>
       </c>
       <c r="F356" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="B357" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="B357" s="2" t="s">
-        <v>719</v>
-      </c>
       <c r="C357" s="2" t="s">
         <v>8</v>
       </c>
@@ -9477,16 +9474,16 @@
         <v>10</v>
       </c>
       <c r="F357" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" s="2" t="s">
+        <v>719</v>
+      </c>
+      <c r="B358" s="2" t="s">
         <v>720</v>
       </c>
-      <c r="B358" s="2" t="s">
-        <v>721</v>
-      </c>
       <c r="C358" s="2" t="s">
         <v>8</v>
       </c>
@@ -9497,16 +9494,16 @@
         <v>10</v>
       </c>
       <c r="F358" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" s="2" t="s">
+        <v>721</v>
+      </c>
+      <c r="B359" s="2" t="s">
         <v>722</v>
       </c>
-      <c r="B359" s="2" t="s">
-        <v>723</v>
-      </c>
       <c r="C359" s="2" t="s">
         <v>8</v>
       </c>
@@ -9517,16 +9514,16 @@
         <v>10</v>
       </c>
       <c r="F359" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B360" s="2" t="s">
         <v>724</v>
       </c>
-      <c r="B360" s="2" t="s">
-        <v>725</v>
-      </c>
       <c r="C360" s="2" t="s">
         <v>8</v>
       </c>
@@ -9537,16 +9534,16 @@
         <v>10</v>
       </c>
       <c r="F360" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="B361" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="B361" s="2" t="s">
-        <v>727</v>
-      </c>
       <c r="C361" s="2" t="s">
         <v>8</v>
       </c>
@@ -9557,16 +9554,16 @@
         <v>10</v>
       </c>
       <c r="F361" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B362" s="2" t="s">
         <v>728</v>
       </c>
-      <c r="B362" s="2" t="s">
-        <v>729</v>
-      </c>
       <c r="C362" s="2" t="s">
         <v>8</v>
       </c>
@@ -9577,15 +9574,15 @@
         <v>10</v>
       </c>
       <c r="F362" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C363" s="2" t="s">
         <v>8</v>
@@ -9597,15 +9594,15 @@
         <v>10</v>
       </c>
       <c r="F363" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C364" s="2" t="s">
         <v>8</v>
@@ -9617,15 +9614,15 @@
         <v>10</v>
       </c>
       <c r="F364" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C365" s="2" t="s">
         <v>8</v>
@@ -9637,16 +9634,16 @@
         <v>10</v>
       </c>
       <c r="F365" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="B366" s="2" t="s">
         <v>733</v>
       </c>
-      <c r="B366" s="2" t="s">
-        <v>734</v>
-      </c>
       <c r="C366" s="2" t="s">
         <v>8</v>
       </c>
@@ -9657,18 +9654,18 @@
         <v>10</v>
       </c>
       <c r="F366" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" s="2" t="s">
+        <v>734</v>
+      </c>
+      <c r="B367" s="2" t="s">
         <v>735</v>
       </c>
-      <c r="B367" s="2" t="s">
-        <v>736</v>
-      </c>
       <c r="C367" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D367" s="2" t="s">
         <v>9</v>
@@ -9677,16 +9674,16 @@
         <v>10</v>
       </c>
       <c r="F367" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="B368" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="B368" s="2" t="s">
-        <v>738</v>
-      </c>
       <c r="C368" s="2" t="s">
         <v>8</v>
       </c>
@@ -9697,18 +9694,18 @@
         <v>10</v>
       </c>
       <c r="F368" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="B369" s="2" t="s">
         <v>739</v>
       </c>
-      <c r="B369" s="2" t="s">
-        <v>740</v>
-      </c>
       <c r="C369" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D369" s="2" t="s">
         <v>9</v>
@@ -9717,18 +9714,18 @@
         <v>10</v>
       </c>
       <c r="F369" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="s">
+        <v>740</v>
+      </c>
+      <c r="B370" s="2" t="s">
         <v>741</v>
       </c>
-      <c r="B370" s="2" t="s">
-        <v>742</v>
-      </c>
       <c r="C370" s="2" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="D370" s="2" t="s">
         <v>9</v>
@@ -9737,18 +9734,18 @@
         <v>10</v>
       </c>
       <c r="F370" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="B371" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="B371" s="2" t="s">
-        <v>744</v>
-      </c>
       <c r="C371" s="2" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="D371" s="2" t="s">
         <v>9</v>
@@ -9757,16 +9754,16 @@
         <v>10</v>
       </c>
       <c r="F371" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" s="2" t="s">
+        <v>744</v>
+      </c>
+      <c r="B372" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="B372" s="2" t="s">
-        <v>746</v>
-      </c>
       <c r="C372" s="2" t="s">
         <v>8</v>
       </c>
@@ -9777,35 +9774,35 @@
         <v>10</v>
       </c>
       <c r="F372" s="2" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" s="2" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="B373" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D373" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E373" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F373" s="2" t="s">
         <v>410</v>
-      </c>
-      <c r="C373" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="D373" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="E373" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F373" s="2" t="s">
-        <v>411</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" s="2" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C374" s="2" t="s">
         <v>8</v>
@@ -9817,15 +9814,15 @@
         <v>10</v>
       </c>
       <c r="F374" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="C375" s="2" t="s">
         <v>8</v>
@@ -9837,15 +9834,15 @@
         <v>10</v>
       </c>
       <c r="F375" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" s="2" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="C376" s="2" t="s">
         <v>8</v>
@@ -9857,19 +9854,19 @@
         <v>10</v>
       </c>
       <c r="F376" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B377" s="2" t="s">
+        <v>421</v>
+      </c>
+      <c r="C377" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="C377" s="2" t="s">
-        <v>423</v>
-      </c>
       <c r="D377" s="2" t="s">
         <v>9</v>
       </c>
@@ -9877,18 +9874,18 @@
         <v>10</v>
       </c>
       <c r="F377" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" s="2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D378" s="2" t="s">
         <v>9</v>
@@ -9897,7 +9894,7 @@
         <v>10</v>
       </c>
       <c r="F378" s="2" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
     </row>
   </sheetData>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -2117,7 +2117,7 @@
     <t>52155</t>
   </si>
   <si>
-    <t>Provvedimenti amministrativi di competenza dell'Autorita' consolare di riconoscimento della cittadinanza italiana jure sanguinis</t>
+    <t>Riconoscimento di cittadinanza jure sanguinis per decreto di autorita' giudiziaria</t>
   </si>
   <si>
     <t>52156</t>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -1973,7 +1973,7 @@
     <t>51112</t>
   </si>
   <si>
-    <t>Dichiarazione di volonta' d'acquisto della cittadinanza italiana di minore art.1-ter legge n.74/2025 (transitoria valida solo fino al 31 maggio 2026)</t>
+    <t>Dichiarazione di volonta' d'acquisto della cittadinanza italiana di minore art.1-ter legge n.74/2025 (transitoria valida solo fino al 31 maggio 2029)</t>
   </si>
   <si>
     <t>51201</t>
@@ -2123,7 +2123,7 @@
     <t>52156</t>
   </si>
   <si>
-    <t>Esito di accertamento per articolo 4 comma 1-bis</t>
+    <t>Esito di accertamento per articolo 4 comma 1-bis e art. 1.1 ter da consolato</t>
   </si>
   <si>
     <t>52157</t>

--- a/docs/Decodifiche/3_dec_use_case.xlsx
+++ b/docs/Decodifiche/3_dec_use_case.xlsx
@@ -1574,6 +1574,9 @@
     <t>Matrimonio con Rito Religioso Cattolico con Riconoscimento di uno o piu' figli</t>
   </si>
   <si>
+    <t>2025-01-01 00:00:00.0</t>
+  </si>
+  <si>
     <t>321411</t>
   </si>
   <si>
@@ -1872,9 +1875,6 @@
   </si>
   <si>
     <t>Trascrizione di sentenza straniera di scioglimento unione civile</t>
-  </si>
-  <si>
-    <t>2025-01-01 00:00:00.0</t>
   </si>
   <si>
     <t>449999</t>
@@ -7348,7 +7348,7 @@
         <v>8</v>
       </c>
       <c r="D251" s="2" t="s">
-        <v>9</v>
+        <v>520</v>
       </c>
       <c r="E251" s="2" t="s">
         <v>10</v>
@@ -7359,10 +7359,10 @@
     </row>
     <row r="252">
       <c r="A252" s="2" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="C252" s="2" t="s">
         <v>8</v>
@@ -7379,16 +7379,16 @@
     </row>
     <row r="253">
       <c r="A253" s="2" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="C253" s="2" t="s">
         <v>8</v>
       </c>
       <c r="D253" s="2" t="s">
-        <v>9</v>
+        <v>520</v>
       </c>
       <c r="E253" s="2" t="s">
         <v>10</v>
@@ -7399,10 +7399,10 @@
     </row>
     <row r="254">
       <c r="A254" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C254" s="2" t="s">
         <v>321</v>
@@ -7419,10 +7419,10 @@
     </row>
     <row r="255">
       <c r="A255" s="2" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="C255" s="2" t="s">
         <v>321</v>
@@ -7439,10 +7439,10 @@
     </row>
     <row r="256">
       <c r="A256" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="C256" s="2" t="s">
         <v>8</v>
@@ -7459,10 +7459,10 @@
     </row>
     <row r="257">
       <c r="A257" s="2" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="C257" s="2" t="s">
         <v>8</v>
@@ -7479,10 +7479,10 @@
     </row>
     <row r="258">
       <c r="A258" s="2" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="C258" s="2" t="s">
         <v>8</v>
@@ -7499,10 +7499,10 @@
     </row>
     <row r="259">
       <c r="A259" s="2" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="C259" s="2" t="s">
         <v>8</v>
@@ -7519,10 +7519,10 @@
     </row>
     <row r="260">
       <c r="A260" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="C260" s="2" t="s">
         <v>8</v>
@@ -7539,10 +7539,10 @@
     </row>
     <row r="261">
       <c r="A261" s="2" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="C261" s="2" t="s">
         <v>8</v>
@@ -7559,13 +7559,13 @@
     </row>
     <row r="262">
       <c r="A262" s="2" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>539</v>
+        <v>540</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>540</v>
+        <v>541</v>
       </c>
       <c r="D262" s="2" t="s">
         <v>9</v>
@@ -7579,10 +7579,10 @@
     </row>
     <row r="263">
       <c r="A263" s="2" t="s">
-        <v>541</v>
+        <v>542</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>542</v>
+        <v>543</v>
       </c>
       <c r="C263" s="2" t="s">
         <v>8</v>
@@ -7599,10 +7599,10 @@
     </row>
     <row r="264">
       <c r="A264" s="2" t="s">
-        <v>543</v>
+        <v>544</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>544</v>
+        <v>545</v>
       </c>
       <c r="C264" s="2" t="s">
         <v>8</v>
@@ -7619,10 +7619,10 @@
     </row>
     <row r="265">
       <c r="A265" s="2" t="s">
-        <v>545</v>
+        <v>546</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>546</v>
+        <v>547</v>
       </c>
       <c r="C265" s="2" t="s">
         <v>8</v>
@@ -7639,10 +7639,10 @@
     </row>
     <row r="266">
       <c r="A266" s="2" t="s">
-        <v>547</v>
+        <v>548</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>548</v>
+        <v>549</v>
       </c>
       <c r="C266" s="2" t="s">
         <v>8</v>
@@ -7659,10 +7659,10 @@
     </row>
     <row r="267">
       <c r="A267" s="2" t="s">
-        <v>549</v>
+        <v>550</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>550</v>
+        <v>551</v>
       </c>
       <c r="C267" s="2" t="s">
         <v>8</v>
@@ -7679,10 +7679,10 @@
     </row>
     <row r="268">
       <c r="A268" s="2" t="s">
-        <v>551</v>
+        <v>552</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>552</v>
+        <v>553</v>
       </c>
       <c r="C268" s="2" t="s">
         <v>8</v>
@@ -7699,10 +7699,10 @@
     </row>
     <row r="269">
       <c r="A269" s="2" t="s">
-        <v>553</v>
+        <v>554</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="C269" s="2" t="s">
         <v>8</v>
@@ -7719,10 +7719,10 @@
     </row>
     <row r="270">
       <c r="A270" s="2" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="C270" s="2" t="s">
         <v>8</v>
@@ -7739,16 +7739,16 @@
     </row>
     <row r="271">
       <c r="A271" s="2" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="C271" s="2" t="s">
         <v>321</v>
       </c>
       <c r="D271" s="2" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="E271" s="2" t="s">
         <v>10</v>
@@ -7759,10 +7759,10 @@
     </row>
     <row r="272">
       <c r="A272" s="2" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="C272" s="2" t="s">
         <v>8</v>
@@ -7779,10 +7779,10 @@
     </row>
     <row r="273">
       <c r="A273" s="2" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="C273" s="2" t="s">
         <v>8</v>
@@ -7799,10 +7799,10 @@
     </row>
     <row r="274">
       <c r="A274" s="2" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="C274" s="2" t="s">
         <v>8</v>
@@ -7819,13 +7819,13 @@
     </row>
     <row r="275">
       <c r="A275" s="2" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="D275" s="2" t="s">
         <v>9</v>
@@ -7839,10 +7839,10 @@
     </row>
     <row r="276">
       <c r="A276" s="2" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="C276" s="2" t="s">
         <v>321</v>
@@ -7859,7 +7859,7 @@
     </row>
     <row r="277">
       <c r="A277" s="2" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="B277" s="2" t="s">
         <v>409</v>
@@ -7879,7 +7879,7 @@
     </row>
     <row r="278">
       <c r="A278" s="2" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
       <c r="B278" s="2" t="s">
         <v>481</v>
@@ -7899,7 +7899,7 @@
     </row>
     <row r="279">
       <c r="A279" s="2" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="B279" s="2" t="s">
         <v>414</v>
@@ -7919,7 +7919,7 @@
     </row>
     <row r="280">
       <c r="A280" s="2" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="B280" s="2" t="s">
         <v>416</v>
@@ -7939,7 +7939,7 @@
     </row>
     <row r="281">
       <c r="A281" s="2" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="B281" s="2" t="s">
         <v>421</v>
@@ -7959,7 +7959,7 @@
     </row>
     <row r="282">
       <c r="A282" s="2" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="B282" s="2" t="s">
         <v>424</v>
@@ -7979,7 +7979,7 @@
     </row>
     <row r="283">
       <c r="A283" s="2" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="B283" s="2" t="s">
         <v>7</v>
@@ -7999,10 +7999,10 @@
     </row>
     <row r="284">
       <c r="A284" s="2" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="C284" s="2" t="s">
         <v>8</v>
@@ -8019,10 +8019,10 @@
     </row>
     <row r="285">
       <c r="A285" s="2" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="C285" s="2" t="s">
         <v>8</v>
@@ -8039,10 +8039,10 @@
     </row>
     <row r="286">
       <c r="A286" s="2" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="C286" s="2" t="s">
         <v>8</v>
@@ -8059,10 +8059,10 @@
     </row>
     <row r="287">
       <c r="A287" s="2" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="C287" s="2" t="s">
         <v>8</v>
@@ -8079,10 +8079,10 @@
     </row>
     <row r="288">
       <c r="A288" s="2" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="C288" s="2" t="s">
         <v>8</v>
@@ -8099,10 +8099,10 @@
     </row>
     <row r="289">
       <c r="A289" s="2" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="C289" s="2" t="s">
         <v>8</v>
@@ -8119,10 +8119,10 @@
     </row>
     <row r="290">
       <c r="A290" s="2" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="C290" s="2" t="s">
         <v>8</v>
@@ -8139,10 +8139,10 @@
     </row>
     <row r="291">
       <c r="A291" s="2" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="C291" s="2" t="s">
         <v>8</v>
@@ -8159,10 +8159,10 @@
     </row>
     <row r="292">
       <c r="A292" s="2" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C292" s="2" t="s">
         <v>8</v>
@@ -8179,10 +8179,10 @@
     </row>
     <row r="293">
       <c r="A293" s="2" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="C293" s="2" t="s">
         <v>8</v>
@@ -8199,10 +8199,10 @@
     </row>
     <row r="294">
       <c r="A294" s="2" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="C294" s="2" t="s">
         <v>321</v>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="295">
       <c r="A295" s="2" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="C295" s="2" t="s">
         <v>321</v>
@@ -8239,10 +8239,10 @@
     </row>
     <row r="296">
       <c r="A296" s="2" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="C296" s="2" t="s">
         <v>8</v>
@@ -8259,10 +8259,10 @@
     </row>
     <row r="297">
       <c r="A297" s="2" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="C297" s="2" t="s">
         <v>8</v>
@@ -8279,10 +8279,10 @@
     </row>
     <row r="298">
       <c r="A298" s="2" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="C298" s="2" t="s">
         <v>8</v>
@@ -8299,10 +8299,10 @@
     </row>
     <row r="299">
       <c r="A299" s="2" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="C299" s="2" t="s">
         <v>8</v>
@@ -8319,10 +8319,10 @@
     </row>
     <row r="300">
       <c r="A300" s="2" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="C300" s="2" t="s">
         <v>8</v>
@@ -8339,10 +8339,10 @@
     </row>
     <row r="301">
       <c r="A301" s="2" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C301" s="2" t="s">
         <v>8</v>
@@ -8359,10 +8359,10 @@
     </row>
     <row r="302">
       <c r="A302" s="2" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="C302" s="2" t="s">
         <v>321</v>
@@ -8379,10 +8379,10 @@
     </row>
     <row r="303">
       <c r="A303" s="2" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="C303" s="2" t="s">
         <v>339</v>
@@ -8399,13 +8399,13 @@
     </row>
     <row r="304">
       <c r="A304" s="2" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>620</v>
+        <v>520</v>
       </c>
       <c r="D304" s="2" t="s">
         <v>9</v>
